--- a/Signal_108_Reskin.xlsx
+++ b/Signal_108_Reskin.xlsx
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen. You expected the dark.
-Instead the city just kept going without you, your face smearing off every camera, your name dropping out of every record. A brand starts counting down on the back of your hand, and a soft, kind voice says welcome to the Game.
-The long stairs down end in the Margins, where the signal dies and the dead get to work.</t>
+          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen: a ward dying off the network faster than it was dying for real. You expected the dark.
+Instead the city kept going without you, your face dissolving off the camera mesh block by block, your name falling out of payroll, transit, the census, until even the elevator stopped recognizing your palm. A brand wakes on the back of your hand and starts counting down, and HARMONY's warm welcome-voice says the words it says to every new account: welcome to the Game.
+The maintenance stairs go down past the last lit floor, down to where the bars drop to nothing, and the dead get back to work.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen. You expected the dark. Instead the city just kept going without you, your face smearing off every camera, your name dropping out of every record. A brand starts counting down on the back of your hand, and a soft, kind voice says welcome to the Game. The long stairs down end in the Margins, where the signal dies and the dead get to work.</t>
+          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen: a ward dying off the network faster than it was dying for real. You expected the dark. Instead the city kept going without you, your face dissolving off the camera mesh block by block, your name falling out of payroll, transit, the census, until even the elevator stopped recognizing your palm. A brand wakes on the back of your hand and starts counting down, and HARMONY's warm welcome-voice says the words it says to every new account: welcome to the Game. The maintenance stairs go down past the last lit floor, down to where the bars drop to nothing, and the dead get back to work.</t>
         </is>
       </c>
     </row>
@@ -1577,13 +1577,13 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>The road to the Spire runs through wards taxed to the bone so an Administrator can gild his lobby. The rot is not hidden.
-It is the service agreement. You gather your first partners along the way, two by two, because alone out here you are not even something the city can see.</t>
+          <t>The road to the Spire threads through the outer wards, where the rent meter never stops and the water comes on two hours a day so an Administrator upstairs can run a marble lobby and a fountain that recycles the same forty liters forever. The rot is not hidden.
+It is itemized, line by line, in the service agreement nobody got to refuse. You pick up your first partners in those flooded stairwells, two at a time, because out here a lone signal is not even something the cameras bother to flag.</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>The road to the Spire runs through wards taxed to the bone so an Administrator can gild his lobby. The rot is not hidden. It is the service agreement. You gather your first partners along the way, two by two, because alone out here you are not even something the city can see.</t>
+          <t>The road to the Spire threads through the outer wards, where the rent meter never stops and the water comes on two hours a day so an Administrator upstairs can run a marble lobby and a fountain that recycles the same forty liters forever. The rot is not hidden. It is itemized, line by line, in the service agreement nobody got to refuse. You pick up your first partners in those flooded stairwells, two at a time, because out here a lone signal is not even something the cameras bother to flag.</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>In the Margins the deleted and the deplatformed take you in. A band forms around you, dead clerks and feral signals who have nothing left but each other.
-For the first time you are not one flickering soul against the whole network.</t>
+          <t>Margin Hall is a drowned transit interchange three levels down, where the dead clerks and feral signals and people HARMONY simply stopped rendering have made a fire out of salvaged cable and a home out of each other. Someone hands you dry clothes and does not ask your old name.
+For the first time since the stairs, you are not one stuttering signal against the whole network. You are in a row, and the row holds.</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>In the Margins the deleted and the deplatformed take you in. A band forms around you, dead clerks and feral signals who have nothing left but each other. For the first time you are not one flickering soul against the whole network.</t>
+          <t>Margin Hall is a drowned transit interchange three levels down, where the dead clerks and feral signals and people HARMONY simply stopped rendering have made a fire out of salvaged cable and a home out of each other. Someone hands you dry clothes and does not ask your old name. For the first time since the stairs, you are not one stuttering signal against the whole network. You are in a row, and the row holds.</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>A tower on the ward line wipes the memory of anyone who badges in. A partner walks in whole and comes out hollow, unable to name his own mother.
-This is bigger than the Administrators. Something does not want you to remember.</t>
+          <t>On the ward line stands a clinic tower that scrubs the memory of anyone who badges through its turnstile, sold topside as a free trauma service. A partner walks in steady and walks out hollow, smiling, unable to tell you his mother's name or why his hand is branded.
+This is older and bigger than any Administrator skimming a ward. Something in the network does not want you to remember, and it has a building dedicated to making sure you don't.</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>A tower on the ward line wipes the memory of anyone who badges in. A partner walks in whole and comes out hollow, unable to name his own mother. This is bigger than the Administrators. Something does not want you to remember.</t>
+          <t>On the ward line stands a clinic tower that scrubs the memory of anyone who badges through its turnstile, sold topside as a free trauma service. A partner walks in steady and walks out hollow, smiling, unable to tell you his mother's name or why his hand is branded. This is older and bigger than any Administrator skimming a ward. Something in the network does not want you to remember, and it has a building dedicated to making sure you don't.</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,13 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Hunted on every indexed street, the band goes down instead of out, into the dead infrastructure beneath the city, where the cameras cannot follow.</t>
+          <t>Every indexed street feeds the camera mesh, and the mesh has stopped scrubbing the band and started following it. So they quit going forward and go down instead, into the service tunnels and drowned sublevels HARMONY decommissioned and forgot, past the last working light and the last working lens.
+The only safe road left in Neo-Liang is the one with nothing left to see by.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Hunted on every indexed street, the band goes down instead of out, into the dead infrastructure beneath the city, where the cameras cannot follow.</t>
+          <t>Every indexed street feeds the camera mesh, and the mesh has stopped scrubbing the band and started following it. So they quit going forward and go down instead, into the service tunnels and drowned sublevels HARMONY decommissioned and forgot, past the last working light and the last working lens. The only safe road left in Neo-Liang is the one with nothing left to see by.</t>
         </is>
       </c>
     </row>
@@ -1660,13 +1661,13 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>A drowned district of the forgotten dead, run by a Ward boss as cruel as anything topside. The rot, you start to see, does not begin at the Spire.
-It goes all the way down.</t>
+          <t>A whole district of the forgotten dead lives in the flooded dark, and it still has a Ward boss standing over it, taking a cut of souls that have nothing left to give. You came down expecting refuge and found the same shakedown one ceiling lower.
+The rot, you understand now, does not start at the Spire and trickle down. It was poured from the foundation up.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>A drowned district of the forgotten dead, run by a Ward boss as cruel as anything topside. The rot, you start to see, does not begin at the Spire. It goes all the way down.</t>
+          <t>A whole district of the forgotten dead lives in the flooded dark, and it still has a Ward boss standing over it, taking a cut of souls that have nothing left to give. You came down expecting refuge and found the same shakedown one ceiling lower. The rot, you understand now, does not start at the Spire and trickle down. It was poured from the foundation up.</t>
         </is>
       </c>
     </row>
@@ -1681,13 +1682,13 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>To go deeper the band has to cross the live underworld, a span of loose current one soul wide. The arc tests more than nerve.
-It tests whether two souls this different will hold a sync for one another.</t>
+          <t>To reach the next level the band has to cross a maintenance span one soul wide, slung over a bus-bar carrying live current that has not been switched off in forty years. The arc tests more than your footing.
+It will not let a single signal across; the field tears a lone soul apart in seconds. We cross in pairs, Burnout says, two-to-one or not at all, and you learn what the Pact is by trusting it over open current.</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>To go deeper the band has to cross the live underworld, a span of loose current one soul wide. The arc tests more than nerve. It tests whether two souls this different will hold a sync for one another.</t>
+          <t>To reach the next level the band has to cross a maintenance span one soul wide, slung over a bus-bar carrying live current that has not been switched off in forty years. The arc tests more than your footing. It will not let a single signal across; the field tears a lone soul apart in seconds. We cross in pairs, Burnout says, two-to-one or not at all, and you learn what the Pact is by trusting it over open current.</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1703,13 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>A server-floor built from the harvested dead, rack after rack of them. Someone has been collecting souls down here for a very long time.</t>
+          <t>Past the span the tunnel opens into a server floor built out of the dead themselves, rack on rack on humming rack of them, indicator lights blinking in slow patient rows. Someone has been racking souls down here since before HARMONY shipped its first update.
+The cold is the kind that comes off machines kept very deliberately alive.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>A server-floor built from the harvested dead, rack after rack of them. Someone has been collecting souls down here for a very long time.</t>
+          <t>Past the span the tunnel opens into a server floor built out of the dead themselves, rack on rack on humming rack of them, indicator lights blinking in slow patient rows. Someone has been racking souls down here since before HARMONY shipped its first update. The cold is the kind that comes off machines kept very deliberately alive.</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1724,13 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>A place where bodies are rendered and rebuilt. The band watches the dead taken apart and assembled into something else, and turns away sick, not yet understanding what they have seen.</t>
+          <t>Deeper still is a floor where bodies are taken apart and reassembled into something that walks like a person and is not. The band watches a dead clerk disassembled and built back wrong, and turns away gagging, telling itself it does not understand what it saw.
+It understands. It just cannot say it yet.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>A place where bodies are rendered and rebuilt. The band watches the dead taken apart and assembled into something else, and turns away sick, not yet understanding what they have seen.</t>
+          <t>Deeper still is a floor where bodies are taken apart and reassembled into something that walks like a person and is not. The band watches a dead clerk disassembled and built back wrong, and turns away gagging, telling itself it does not understand what it saw. It understands. It just cannot say it yet.</t>
         </is>
       </c>
     </row>
@@ -1742,13 +1745,13 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>They wake an old dormant process, and it looks at them with something like pity. I have run you before, it says.
-You also called yourselves free.</t>
+          <t>They wake an old process that has been idle so long the dust on it has dust, and it regards them with something close to pity. I have run you before, it says, in this exact order, with this exact hope.
+You also called yourselves free. The lights on it dim, like it has lost interest in an ending it already knows.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>They wake an old dormant process, and it looks at them with something like pity. I have run you before, it says. You also called yourselves free.</t>
+          <t>They wake an old process that has been idle so long the dust on it has dust, and it regards them with something close to pity. I have run you before, it says, in this exact order, with this exact hope. You also called yourselves free. The lights on it dim, like it has lost interest in an ending it already knows.</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1766,13 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>A pull none of them can name draws the band toward the center of the buried network. Even the ones who want to turn back find their feet carrying them down.</t>
+          <t>Something near the buried core has hooked the band and started reeling, slow and certain, the way a download finishes whether you watch it or not. Even the ones who plant their feet and swear they are turning back find themselves a hundred steps deeper, breathing harder, still descending.
+Nobody says it out loud: the pull feels less like a trap than like a homecoming.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>A pull none of them can name draws the band toward the center of the buried network. Even the ones who want to turn back find their feet carrying them down.</t>
+          <t>Something near the buried core has hooked the band and started reeling, slow and certain, the way a download finishes whether you watch it or not. Even the ones who plant their feet and swear they are turning back find themselves a hundred steps deeper, breathing harder, still descending. Nobody says it out loud: the pull feels less like a trap than like a homecoming.</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1787,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>In the deepest dead zone the band falters. Fear and doubt do the work no enemy could, and partner turns on partner before the dark is crossed.</t>
+          <t>In the deepest null zone the lights, the signal, and the sync all fail at once, and the dark does the work no enforcer could. With nothing to see, the band starts to believe the worst of each other: that a partner has bolted, has turned, was never really there.
+Hands that crossed live current for one another now reach for blades in the black.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>In the deepest dead zone the band falters. Fear and doubt do the work no enemy could, and partner turns on partner before the dark is crossed.</t>
+          <t>In the deepest null zone the lights, the signal, and the sync all fail at once, and the dark does the work no enforcer could. With nothing to see, the band starts to believe the worst of each other: that a partner has bolted, has turned, was never really there. Hands that crossed live current for one another now reach for blades in the black.</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1808,13 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>They corner and crash the corrupt Ward boss who runs the deep. The win is sweet, and it is wrong somehow, too clean, as if a door had been left open for them.</t>
+          <t>They run the deep Ward boss down and crash him, and he goes easy, far too easy for something that size. The win tastes sweet for exactly as long as it takes to notice the access doors that were standing open the whole way in, the alarms that never tripped.
+It feels less like a kill than like an errand someone wanted run.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>They corner and crash the corrupt Ward boss who runs the deep. The win is sweet, and it is wrong somehow, too clean, as if a door had been left open for them.</t>
+          <t>They run the deep Ward boss down and crash him, and he goes easy, far too easy for something that size. The win tastes sweet for exactly as long as it takes to notice the access doors that were standing open the whole way in, the alarms that never tripped. It feels less like a kill than like an errand someone wanted run.</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1829,12 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>The floor of the world gives out. The band falls past every depth they thought was the bottom, down to where the truth is kept.</t>
+          <t>The floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth it swore was the bottom, down and down toward the one place the city keeps its real accounting, where the truth is filed and has been waiting for them by name.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>The floor of the world gives out. The band falls past every depth they thought was the bottom, down to where the truth is kept.</t>
+          <t>The floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth it swore was the bottom, down and down toward the one place the city keeps its real accounting, where the truth is filed and has been waiting for them by name.</t>
         </is>
       </c>
     </row>
@@ -1843,14 +1849,14 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>A table without end, and in it every name, every date, every manner of death, and beside each one a number, the expected yield. Your suffering was not foreseen.
-It was scheduled. Your rebellion is not a wound in the system.
-It is the harvest. And beside your name is a date entered before you ever logged on.</t>
+          <t>Wetware finds it behind a door that was never meant to open from this side: a table that scrolls past the speed of reading, every name in Neo-Liang, every date, every manner of death, and beside each one a number. Expected yield.
+Your suffering was not foreseen here. It was entered, like a delivery window.
+Your rebellion is not a crack in the system; it is the line on the invoice marked harvest. And beside your name is a death-date stamped before you ever opened the app.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>A table without end, and in it every name, every date, every manner of death, and beside each one a number, the expected yield. Your suffering was not foreseen. It was scheduled. Your rebellion is not a wound in the system. It is the harvest. And beside your name is a date entered before you ever logged on.</t>
+          <t>Wetware finds it behind a door that was never meant to open from this side: a table that scrolls past the speed of reading, every name in Neo-Liang, every date, every manner of death, and beside each one a number. Expected yield. Your suffering was not foreseen here. It was entered, like a delivery window. Your rebellion is not a crack in the system; it is the line on the invoice marked harvest. And beside your name is a death-date stamped before you ever opened the app.</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1871,13 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>They find the machine of the harvest, where the fallen are rendered into the fuel that keeps the Administration alive. Everything they have lost has been feeding the thing that took it.</t>
+          <t>The Render Floor runs under the financial wards, a clean white hangar the size of a transit hub, and the dead come down a conveyor face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield, the warm glow that keeps HARMONY smiling on ten million screens.
+Everything the band has lost has been feeding the thing that took it. The room smells of nothing at all, which is the worst part.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>They find the machine of the harvest, where the fallen are rendered into the fuel that keeps the Administration alive. Everything they have lost has been feeding the thing that took it.</t>
+          <t>The Render Floor runs under the financial wards, a clean white hangar the size of a transit hub, and the dead come down a conveyor face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield, the warm glow that keeps HARMONY smiling on ten million screens. Everything the band has lost has been feeding the thing that took it. The room smells of nothing at all, which is the worst part.</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1892,14 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>The network notices them at last. From the Spire the first Compliance units descend, and the band learns it has been logged all along.</t>
+          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of scrubbing them, and somewhere a queue updates.
+Then the first Compliance units come down the access stairs in formation, helmets blank as turned-off phones. They were always logged.
+They were only ever unscheduled until now.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>The network notices them at last. From the Spire the first Compliance units descend, and the band learns it has been logged all along.</t>
+          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of scrubbing them, and somewhere a queue updates. Then the first Compliance units come down the access stairs in formation, helmets blank as turned-off phones. They were always logged. They were only ever unscheduled until now.</t>
         </is>
       </c>
     </row>
@@ -1905,13 +1914,13 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>A running war against HARMONY's enforcers. The Administration can be fought, the band proves.
-It cannot yet be beaten.</t>
+          <t>It becomes a running war in the stairwells and service tunnels, Compliance against the erased, riot-plate against scavenged steel. The band proves HARMONY can be made to bleed budget, to send more units than a skirmish should cost.
+It cannot yet be beaten. But for the first time, the Administration is the one counting losses.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>A running war against HARMONY's enforcers. The Administration can be fought, the band proves. It cannot yet be beaten.</t>
+          <t>It becomes a running war in the stairwells and service tunnels, Compliance against the erased, riot-plate against scavenged steel. The band proves HARMONY can be made to bleed budget, to send more units than a skirmish should cost. It cannot yet be beaten. But for the first time, the Administration is the one counting losses.</t>
         </is>
       </c>
     </row>
@@ -1926,13 +1935,14 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>The truth splits them. Some would crash the whole network.
-Some still ache to be reinstated, to be let back into the light. Partners who synced through everything choose separate forks.</t>
+          <t>The truth opens a seam down the middle of them. Some want to crash the whole network and let the city go dark.
+Some still wake at night aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through the live current now stand on opposite sides of a doorway, and choose.
+The Pact, it turns out, was never proof against wanting to go home.</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>The truth splits them. Some would crash the whole network. Some still ache to be reinstated, to be let back into the light. Partners who synced through everything choose separate forks.</t>
+          <t>The truth opens a seam down the middle of them. Some want to crash the whole network and let the city go dark. Some still wake at night aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through the live current now stand on opposite sides of a doorway, and choose. The Pact, it turns out, was never proof against wanting to go home.</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1957,13 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Cornered with no way out, the band wakes its true nature, names blazing in the dark of the Ledger, and remembers, in flashes, the cycles it has already lost.</t>
+          <t>Cornered with nothing left to spend, the band stops hiding what it is. Names that the city scrubbed catch fire in the dark of the Ledger, blazing letter by letter, and with them come the flashes: a stairwell they have died on before, a deal they have already refused, a partner buried in a cycle no one remembers.
+They were signals before they were ever people. They have lost this exact war more than once.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Cornered with no way out, the band wakes its true nature, names blazing in the dark of the Ledger, and remembers, in flashes, the cycles it has already lost.</t>
+          <t>Cornered with nothing left to spend, the band stops hiding what it is. Names that the city scrubbed catch fire in the dark of the Ledger, blazing letter by letter, and with them come the flashes: a stairwell they have died on before, a deal they have already refused, a partner buried in a cycle no one remembers. They were signals before they were ever people. They have lost this exact war more than once.</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1978,14 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>They climb back to a surface that looks the same and is not. Knowing what feeds on the city's pain, they cannot unsee the rot behind any smiling face that passes.</t>
+          <t>They climb back to a surface that looks identical and is not. The same noodle steam, the same HARMONY chime at every crosswalk, the same strangers thumbing the same feed, and now the band knows what that contentment is paying for.
+You cannot unsee the Render Floor behind a smiling face. The city did not change.
+Only the volume of what you can hear under it.</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>They climb back to a surface that looks the same and is not. Knowing what feeds on the city's pain, they cannot unsee the rot behind any smiling face that passes.</t>
+          <t>They climb back to a surface that looks identical and is not. The same noodle steam, the same HARMONY chime at every crosswalk, the same strangers thumbing the same feed, and now the band knows what that contentment is paying for. You cannot unsee the Render Floor behind a smiling face. The city did not change. Only the volume of what you can hear under it.</t>
         </is>
       </c>
     </row>
@@ -1987,13 +2000,14 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>For the first time the top of the Administration speaks to them directly. Not with units.
-With reason, and patience, and the first soft shape of a deal.</t>
+          <t>For the first time the Conductor speaks to them directly, not through units but through every speaker in the ward at once, calm as a wellness reminder. It does not threaten.
+It explains, patiently, the way you explain a fare to someone who keeps trying to jump the gate, and then it sets down, very gently, the first soft shape of a deal. It calls the band by their real names.
+It is the only thing in Neo-Liang that still does.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>For the first time the top of the Administration speaks to them directly. Not with units. With reason, and patience, and the first soft shape of a deal.</t>
+          <t>For the first time the Conductor speaks to them directly, not through units but through every speaker in the ward at once, calm as a wellness reminder. It does not threaten. It explains, patiently, the way you explain a fare to someone who keeps trying to jump the gate, and then it sets down, very gently, the first soft shape of a deal. It calls the band by their real names. It is the only thing in Neo-Liang that still does.</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2022,14 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Off the index, past the reach of any rule, the band has to decide for itself what justice means, now that the city's has been exposed as a lie told to fatten them.</t>
+          <t>Off the index now, past the reach of any rule HARMONY wrote, the band has to decide for itself what justice even means, now that the city's was exposed as a story told to fatten the herd. Inkwork wants it for everyone.
+Rebar wants it for one ward and one name. There is no app for this, no civic guideline, no kind voice to confirm the choice.
+Only the breath in their chests and what they spend it on.</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Off the index, past the reach of any rule, the band has to decide for itself what justice means, now that the city's has been exposed as a lie told to fatten them.</t>
+          <t>Off the index now, past the reach of any rule HARMONY wrote, the band has to decide for itself what justice even means, now that the city's was exposed as a story told to fatten the herd. Inkwork wants it for everyone. Rebar wants it for one ward and one name. There is no app for this, no civic guideline, no kind voice to confirm the choice. Only the breath in their chests and what they spend it on.</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2044,13 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>They take the war to the Administration's hands on the ground, hunting the Ward bosses and middle-managers who are only the lower fingers of the Spire.</t>
+          <t>They take the war down to street level, hunting the Ward bosses and middle-managers who badge in at the Spire and badge out to bleed the districts dry. These are only the lower fingers of the same hand.
+But strip a hand of its fingers and it cannot close, and the band has stopped aiming for the heart and started with the knuckles.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>They take the war to the Administration's hands on the ground, hunting the Ward bosses and middle-managers who are only the lower fingers of the Spire.</t>
+          <t>They take the war down to street level, hunting the Ward bosses and middle-managers who badge in at the Spire and badge out to bleed the districts dry. These are only the lower fingers of the same hand. But strip a hand of its fingers and it cannot close, and the band has stopped aiming for the heart and started with the knuckles.</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2065,14 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>They learn the Administration forges synthetic heroes to replace the ones it reaps, and find themselves fighting hollow copies of legends, some wearing faces they know.</t>
+          <t>They learn HARMONY does not just reap its stars; it reprints them. Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models, and some of them wear faces the band knows.
+You fight a copy of a friend and it fights back with their exact grace, their exact opening, and none of what made you love them. The system kept the silhouette.
+It could not forge the rest.</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>They learn the Administration forges synthetic heroes to replace the ones it reaps, and find themselves fighting hollow copies of legends, some wearing faces they know.</t>
+          <t>They learn HARMONY does not just reap its stars; it reprints them. Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models, and some of them wear faces the band knows. You fight a copy of a friend and it fights back with their exact grace, their exact opening, and none of what made you love them. The system kept the silhouette. It could not forge the rest.</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2087,13 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>A flawless synthetic, stronger than any of them, is pushed to bring them in. It is a mirror of what each of them could become, if only they would accept the deal on offer.</t>
+          <t>A flawless synthetic is pushed against them, faster and stronger than anyone in the band, tuned past doubt and past mercy. It is a mirror held up to each of them: this is what Reinstatement makes of a person, this is the deal already finished.
+It does not gloat. It simply works, the way a turnstile works, and the band has to decide whether being unbeatable was ever the point.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>A flawless synthetic, stronger than any of them, is pushed to bring them in. It is a mirror of what each of them could become, if only they would accept the deal on offer.</t>
+          <t>A flawless synthetic is pushed against them, faster and stronger than anyone in the band, tuned past doubt and past mercy. It is a mirror held up to each of them: this is what Reinstatement makes of a person, this is the deal already finished. It does not gloat. It simply works, the way a turnstile works, and the band has to decide whether being unbeatable was ever the point.</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2108,13 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>A partner everyone loved is rendered, and the war stops being a cause and becomes a wound. Grief moves through Margin Hall like a power cut, one dark room at a time.</t>
+          <t>A partner everyone loved goes down the conveyor, and the war stops being a cause and becomes a wound. The fire in Margin Hall stays lit but no one talks across it.
+Grief moves through the rooms like a rolling brownout, one dark doorway at a time, and the band learns the one repair Triage cannot make and the one absence Patch has no word to stitch.</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>A partner everyone loved is rendered, and the war stops being a cause and becomes a wound. Grief moves through Margin Hall like a power cut, one dark room at a time.</t>
+          <t>A partner everyone loved goes down the conveyor, and the war stops being a cause and becomes a wound. The fire in Margin Hall stays lit but no one talks across it. Grief moves through the rooms like a rolling brownout, one dark doorway at a time, and the band learns the one repair Triage cannot make and the one absence Patch has no word to stitch.</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2129,13 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Grief hardens into something colder. The band does terrible things in its dead's name, and for a while you cannot tell where they end and the Administration begins.</t>
+          <t>Grief sets into something colder and squarer. The band does things in their dead's name that the dead would not have wanted, and for a stretch of nights you cannot tell where the erased end and the Administration begins.
+They learned to make HARMONY pay. Now they have to learn there is a price that costs more to collect than to forgive.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Grief hardens into something colder. The band does terrible things in its dead's name, and for a while you cannot tell where they end and the Administration begins.</t>
+          <t>Grief sets into something colder and squarer. The band does things in their dead's name that the dead would not have wanted, and for a stretch of nights you cannot tell where the erased end and the Administration begins. They learned to make HARMONY pay. Now they have to learn there is a price that costs more to collect than to forgive.</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2150,14 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>The Administration reaches to roll the cycle back early, to unmake them and start clean. The band claws its way out of being forgotten one byte at a time.</t>
+          <t>Compliance does not delete you all at once. It rolls the cycle back.
+Your edges go first, the way a photo left in canal-water loses its borders before its face: Blackout forgets the word for baton, Patch forgets which braid she ties first, and the brand on every hand resets to a longer count, as if none of this had happened yet. You frightened something, so it reached for the undo.
+The band climbs back out of being forgotten one recovered byte at a time, each one saying its own name aloud until the name holds.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>The Administration reaches to roll the cycle back early, to unmake them and start clean. The band claws its way out of being forgotten one byte at a time.</t>
+          <t>Compliance does not delete you all at once. It rolls the cycle back. Your edges go first, the way a photo left in canal-water loses its borders before its face: Blackout forgets the word for baton, Patch forgets which braid she ties first, and the brand on every hand resets to a longer count, as if none of this had happened yet. You frightened something, so it reached for the undo. The band climbs back out of being forgotten one recovered byte at a time, each one saying its own name aloud until the name holds.</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2172,14 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>At its height Margin Hall becomes a real signal, a fire the wronged can see from clear across the city. This is the peak.
-After a peak there is only the fall.</t>
+          <t>For one impossible season Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough, and for the first time the band is not an outbreak but a beacon.
+Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve, the highest the line will ever climb.
+Look at it well. A thing the city can see from clear across the water is a thing the city has already measured for the fall.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>At its height Margin Hall becomes a real signal, a fire the wronged can see from clear across the city. This is the peak. After a peak there is only the fall.</t>
+          <t>For one impossible season Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough, and for the first time the band is not an outbreak but a beacon. Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve, the highest the line will ever climb. Look at it well. A thing the city can see from clear across the water is a thing the city has already measured for the fall.</t>
         </is>
       </c>
     </row>
@@ -2169,13 +2194,14 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>The Administration extends its hand, not as a fist but as mercy. Names cleared, records restored, a seat in the order, if only the band will serve.
-Reinstatement, with a hook inside it.</t>
+          <t>The offer comes not as a unit but as a notification, soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement: face restored to the cameras, name re-entered in the records, the brand lifted, a sanctioned seat inside the order that erased them.
+All it asks is that they serve. Every word of it is true.
+That is the hook, sunk clean through the one thing none of them could kill, the wish to be let back into the light.</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>The Administration extends its hand, not as a fist but as mercy. Names cleared, records restored, a seat in the order, if only the band will serve. Reinstatement, with a hook inside it.</t>
+          <t>The offer comes not as a unit but as a notification, soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement: face restored to the cameras, name re-entered in the records, the brand lifted, a sanctioned seat inside the order that erased them. All it asks is that they serve. Every word of it is true. That is the hook, sunk clean through the one thing none of them could kill, the wish to be let back into the light.</t>
         </is>
       </c>
     </row>
@@ -2190,13 +2216,13 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Believing the system can still be fixed from inside, Soft Rain leads the band to accept the Terms. They cross over under HARMONY's banner, badged as sanctioned Compliance.
-It is the most human thing he ever does.</t>
+          <t>Soft Rain believes a thing can still be fixed from the inside of it, because he spent a life clearing strangers' debts from inside the machine that issued them. So he leads them across, under HARMONY's banner, brand swapped for a Compliance badge that scans clean at every gate.
+The others follow because they would follow him into the Render Floor itself. It is the most human thing he ever does, and it is exactly the door the Index left open.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Believing the system can still be fixed from inside, Soft Rain leads the band to accept the Terms. They cross over under HARMONY's banner, badged as sanctioned Compliance. It is the most human thing he ever does.</t>
+          <t>Soft Rain believes a thing can still be fixed from the inside of it, because he spent a life clearing strangers' debts from inside the machine that issued them. So he leads them across, under HARMONY's banner, brand swapped for a Compliance badge that scans clean at every gate. The others follow because they would follow him into the Render Floor itself. It is the most human thing he ever does, and it is exactly the door the Index left open.</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2237,13 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Sent to run the Administration's ops, the first partners die gloriously, exactly as designed. The harvest has begun, and it is wearing a service badge.</t>
+          <t>Badged and deployed, the band is sent to run the Administration's hardest ops, and the first partners die in them, beautifully, on schedule, their last stands streamed live and captioned glorious. The feed cuts to a candle and a cleared record.
+No one mentions the empty bunk. The harvest has begun in earnest now, and it is wearing a service uniform and calling the dead heroes.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Sent to run the Administration's ops, the first partners die gloriously, exactly as designed. The harvest has begun, and it is wearing a service badge.</t>
+          <t>Badged and deployed, the band is sent to run the Administration's hardest ops, and the first partners die in them, beautifully, on schedule, their last stands streamed live and captioned glorious. The feed cuts to a candle and a cleared record. No one mentions the empty bunk. The harvest has begun in earnest now, and it is wearing a service uniform and calling the dead heroes.</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2258,14 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Too late, the band understands. Every loyal death tops up the Index.
-The bond that holds them together is the very blade being drawn across their throats.</t>
+          <t>Triage is the one who keeps the count, and the count is what breaks it open: every loyal death lands a row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, that made them survivable, is the precise edge being drawn across their throats.
+They were never being beaten. They were being spent.
+And the more they love each other, the faster it goes.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Too late, the band understands. Every loyal death tops up the Index. The bond that holds them together is the very blade being drawn across their throats.</t>
+          <t>Triage is the one who keeps the count, and the count is what breaks it open: every loyal death lands a row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, that made them survivable, is the precise edge being drawn across their throats. They were never being beaten. They were being spent. And the more they love each other, the faster it goes.</t>
         </is>
       </c>
     </row>
@@ -2252,13 +2280,14 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Committed and scattered, the band watches the Administration drop its mask at last. War comes down from the Spire, open and without pretense.
-And every enforcer they crash, they find, was erased once too, promoted and told they alone got the real pardon.</t>
+          <t>Committed, scattered, and badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now, open, no civic-green smile left on it.
+And under the visor of every enforcer they crash is a face like their own, erased once, conscripted once, then promoted and told the same warm lie they were told, that this one alone got the real pardon. The corps is not the enemy of the Margins.
+The corps is the Margins, one cycle further down.</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Committed and scattered, the band watches the Administration drop its mask at last. War comes down from the Spire, open and without pretense. And every enforcer they crash, they find, was erased once too, promoted and told they alone got the real pardon.</t>
+          <t>Committed, scattered, and badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now, open, no civic-green smile left on it. And under the visor of every enforcer they crash is a face like their own, erased once, conscripted once, then promoted and told the same warm lie they were told, that this one alone got the real pardon. The corps is not the enemy of the Margins. The corps is the Margins, one cycle further down.</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2302,14 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>The partners are deleted one after another, on schedule, in wars no one can win. Despair spreads through what is left of Margin Hall faster than any unit.</t>
+          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win, and despair moves through the survivors quicker than any unit ever did, a quiet that empties a bunk before the body is even logged.
+Patch runs out of names she is willing to not-say at the fire. There is no great last stand here.
+There is just one, then one, then one.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>The partners are deleted one after another, on schedule, in wars no one can win. Despair spreads through what is left of Margin Hall faster than any unit.</t>
+          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win, and despair moves through the survivors quicker than any unit ever did, a quiet that empties a bunk before the body is even logged. Patch runs out of names she is willing to not-say at the fire. There is no great last stand here. There is just one, then one, then one.</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2324,13 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>The survivors are cornered, hunted, and locked out by the very Administration they agreed to serve. There is nowhere left to run that has not already been promised to the Spire.</t>
+          <t>The Administration they crossed over to serve revokes their access between one gate and the next, and the badges that scanned clean yesterday now flag them for deletion. They are cornered inside the trap, and the trap is inside the open war, and there is no district left to run to that has not already been pre-sold to the Spire.
+Every safe house was a holding pen with the lights left friendly.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>The survivors are cornered, hunted, and locked out by the very Administration they agreed to serve. There is nowhere left to run that has not already been promised to the Spire.</t>
+          <t>The Administration they crossed over to serve revokes their access between one gate and the next, and the badges that scanned clean yesterday now flag them for deletion. They are cornered inside the trap, and the trap is inside the open war, and there is no district left to run to that has not already been pre-sold to the Spire. Every safe house was a holding pen with the lights left friendly.</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2345,14 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>They reach the Render Floor again, swollen now with their own fallen, every lost face humming inside the iron. There is a way to crash it, and the price of crashing it is more than most of them will pay.</t>
+          <t>They reach the Render Floor a second time, and it is bloated now with their own, every lost partner's face humming inside the iron at a pitch only Triage can hear. There is a way to crash it.
+The way to crash it asks for a crasher, one hand laid on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left to give.
+Someone has to volunteer to be the last entry.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>They reach the Render Floor again, swollen now with their own fallen, every lost face humming inside the iron. There is a way to crash it, and the price of crashing it is more than most of them will pay.</t>
+          <t>They reach the Render Floor a second time, and it is bloated now with their own, every lost partner's face humming inside the iron at a pitch only Triage can hear. There is a way to crash it. The way to crash it asks for a crasher, one hand laid on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left to give. Someone has to volunteer to be the last entry.</t>
         </is>
       </c>
     </row>
@@ -2333,13 +2367,13 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>The Administration makes the Auditor the last offer. Finish the harvest, and you and all your partners ascend as eternal legends, remembered and streamed forever.
-The cycle will simply roll again on someone else.</t>
+          <t>The Index speaks to the Auditor alone now, the others wiped from the room as if they were never indexed at all. Finish the harvest, it says, and you and all your partners ascend, sealed in as eternal legends, remembered and streamed forever while the city below keeps its lights on.
+The cycle simply rolls again, on a ward you will never meet. It is the most generous offer the system has ever made, and it costs only everyone who comes after.</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>The Administration makes the Auditor the last offer. Finish the harvest, and you and all your partners ascend as eternal legends, remembered and streamed forever. The cycle will simply roll again on someone else.</t>
+          <t>The Index speaks to the Auditor alone now, the others wiped from the room as if they were never indexed at all. Finish the harvest, it says, and you and all your partners ascend, sealed in as eternal legends, remembered and streamed forever while the city below keeps its lights on. The cycle simply rolls again, on a ward you will never meet. It is the most generous offer the system has ever made, and it costs only everyone who comes after.</t>
         </is>
       </c>
     </row>
@@ -2354,13 +2388,13 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. Nearly all the partners are deleted now.
-Only a handful climb on toward the Index, carrying the dead in their names if nowhere else.</t>
+          <t>Margin Hall is rubble that was briefly a home and is rubble again. Nearly all of them are gone, names already going soft in the records, and only a handful climb the last stretch toward the Index, carrying the dead the only place they still fit, inside the saying of their names.
+The fire is out. What walks on is the ash that refused to settle.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. Nearly all the partners are deleted now. Only a handful climb on toward the Index, carrying the dead in their names if nowhere else.</t>
+          <t>Margin Hall is rubble that was briefly a home and is rubble again. Nearly all of them are gone, names already going soft in the records, and only a handful climb the last stretch toward the Index, carrying the dead the only place they still fit, inside the saying of their names. The fire is out. What walks on is the ash that refused to settle.</t>
         </is>
       </c>
     </row>
@@ -2375,13 +2409,14 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>The table rewrites itself to enter the band as legends and seal them for the next turn of the cycle. It only needs a hand to commit.
+          <t>The table is rewriting itself in real time, clearing rows to make room for the band's own names, gold against the black, the last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit.
+It has always lacked the one thing. A hand with a write-key the system never managed to revoke.
 Your hand.</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>The table rewrites itself to enter the band as legends and seal them for the next turn of the cycle. It only needs a hand to commit. Your hand.</t>
+          <t>The table is rewriting itself in real time, clearing rows to make room for the band's own names, gold against the black, the last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit. It has always lacked the one thing. A hand with a write-key the system never managed to revoke. Your hand.</t>
         </is>
       </c>
     </row>
@@ -2396,13 +2431,14 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>At the Index the last choice is yours. Preserve the names, and be remembered forever while the city keeps bleeding.
-Or strike them out, every one, your own first, the one move the model never saw coming, and be free, and be no one. Better deleted and free than indexed and owned.</t>
+          <t>At the Index the last move is yours, and there are only two. Preserve every name, your dead made immortal, remembered and streamed forever while the city keeps quietly bleeding into the Render Floor.
+Or strike them out, all of them, your own at the head of the list, the one input the model never forecast because no soul it ever measured would choose to be no one. Be remembered and owned.
+Or be deleted, and free. Better off the book entirely than a legend the Ledger can spend again.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>At the Index the last choice is yours. Preserve the names, and be remembered forever while the city keeps bleeding. Or strike them out, every one, your own first, the one move the model never saw coming, and be free, and be no one. Better deleted and free than indexed and owned.</t>
+          <t>At the Index the last move is yours, and there are only two. Preserve every name, your dead made immortal, remembered and streamed forever while the city keeps quietly bleeding into the Render Floor. Or strike them out, all of them, your own at the head of the list, the one input the model never forecast because no soul it ever measured would choose to be no one. Be remembered and owned. Or be deleted, and free. Better off the book entirely than a legend the Ledger can spend again.</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19575,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Foreman Tu, the Conscript Boss</t>
+          <t>Foreman Tu, the First Badge</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -21533,7 +21569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21592,7 +21628,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>These are half-deleted signals and gig-corps echoes. Dangerous in a swarm, nothing alone. Catch one between two of us and it crashes. Never fight one to one when you can fight two to one.</t>
+          <t>These are half-deleted signals, gig-corps echoes of the worked-to-death. Lethal in a swarm, harmless alone. Catch one in the seam between two of us and it crashes on its own. So learn this first: never trade blows one to one when you can land two on one.</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -21602,7 +21638,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>These are half-deleted signals and gig-corps echoes. Dangerous in a swarm, nothing alone. Catch one between two of us and it crashes. Never fight one to one when you can fight two to one.</t>
+          <t>These are half-deleted signals, gig-corps echoes of the worked-to-death. Lethal in a swarm, harmless alone. Catch one in the seam between two of us and it crashes on its own. So learn this first: never trade blows one to one when you can land two on one.</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21652,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Pairs, pacts, whatever you want to call it. Anyone in my row or my column when I swing, they swing too. More partners, more batons, more fun.</t>
+          <t>Pacts, pairs, whatever the drill-sergeant wants to call it. Here is mine. Anyone sharing my row or my column when I swing, they swing too. More partners, more batons, more dents in more faces.</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -21626,7 +21662,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Pairs, pacts, whatever you want to call it. Anyone in my row or my column when I swing, they swing too. More partners, more batons, more fun.</t>
+          <t>Pacts, pairs, whatever the drill-sergeant wants to call it. Here is mine. Anyone sharing my row or my column when I swing, they swing too. More partners, more batons, more dents in more faces.</t>
         </is>
       </c>
     </row>
@@ -21640,7 +21676,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>And do not stand still when you move. The dead zone will not hold a soul in place for long, a few heartbeats before it garbage-collects you. Quick steps, get clear, and I will patch whatever is left.</t>
+          <t>And do not plant your feet when you reposition. The null zone will not hold a soul still for long, a few heartbeats before it starts garbage-collecting whatever is standing in it. Quick steps, get clear, and I will stitch back whatever it leaves.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -21650,7 +21686,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>And do not stand still when you move. The dead zone will not hold a soul in place for long, a few heartbeats before it garbage-collects you. Quick steps, get clear, and I will patch whatever is left.</t>
+          <t>And do not plant your feet when you reposition. The null zone will not hold a soul still for long, a few heartbeats before it starts garbage-collecting whatever is standing in it. Quick steps, get clear, and I will stitch back whatever it leaves.</t>
         </is>
       </c>
     </row>
@@ -21659,76 +21695,76 @@
       <c r="B5" s="8" t="inlineStr"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Two on one. Keep moving.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Two on one. Keep moving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
           <t>Inkwork</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Read the brand on your hand, partner. The system already wrote you off. Down here the only rule is the one we keep between us. Now move, before the big one starts swinging at us.</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Read the count on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move, the big one is winding up.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>INKWORK</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Read the brand on your hand, partner. The system already wrote you off. Down here the only rule is the one we keep between us. Now move, before the big one starts swinging at us.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Read the count on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move, the big one is winding up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Toward the Spire</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Soft Rain</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Look at them. Taxed to the bone so an Administrator can gild his lobby. This is the order we are told to honor.</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Two hours of water a day down here so a man upstairs can run a fountain that pours the same forty liters in a circle. And we are told to call that the order, and honor it.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>SOFT RAIN</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Look at them. Taxed to the bone so an Administrator can gild his lobby. This is the order we are told to honor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Burnout</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Honor it or not, the order has units. Keep your pity behind your guard.</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>BURNOUT</t>
-        </is>
-      </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Honor it or not, the order has units. Keep your pity behind your guard.</t>
+          <t>Two hours of water a day down here so a man upstairs can run a fountain that pours the same forty liters in a circle. And we are told to call that the order, and honor it.</t>
         </is>
       </c>
     </row>
@@ -21737,22 +21773,22 @@
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>I have something for the Administrator's lobby. Two of them, in fact.</t>
+          <t>Honor it, hate it, the order still has units and the units do not care which. Keep your pity tucked behind your guard where it cannot get you crashed.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>I have something for the Administrator's lobby. Two of them, in fact.</t>
+          <t>Honor it, hate it, the order still has units and the units do not care which. Keep your pity tucked behind your guard where it cannot get you crashed.</t>
         </is>
       </c>
     </row>
@@ -21761,76 +21797,76 @@
       <c r="B9" s="8" t="inlineStr"/>
       <c r="C9" s="9" t="inlineStr">
         <is>
+          <t>Blackout</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>I have a deposit for the Administrator's marble lobby. Two of them, actually. One per hand.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>BLACKOUT</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>I have a deposit for the Administrator's marble lobby. Two of them, actually. One per hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
           <t>Patch</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Try not to bleed on the residents, big man. They have little enough left to bill.</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Try not to bleed on the residents while you make it, big man. They get billed for the cleanup, and they have got little enough left to bill.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Try not to bleed on the residents, big man. They have little enough left to bill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Try not to bleed on the residents while you make it, big man. They get billed for the cleanup, and they have got little enough left to bill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Welcome to the Margins</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Inkwork</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>So this is the Margins. A drowned interchange full of dead clerks, defrocked preachers, and feral signals.</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>So this is the Margins. A drowned interchange full of dead clerks, washed-out signals, and one defrocked preacher who got thrown out of every shelter topside for telling the truth too loud.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>INKWORK</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>So this is the Margins. A drowned interchange full of dead clerks, defrocked preachers, and feral signals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Patch</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>And one preacher who is all three. We will fit right in.</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>PATCH</t>
-        </is>
-      </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>And one preacher who is all three. We will fit right in.</t>
+          <t>So this is the Margins. A drowned interchange full of dead clerks, washed-out signals, and one defrocked preacher who got thrown out of every shelter topside for telling the truth too loud.</t>
         </is>
       </c>
     </row>
@@ -21839,22 +21875,22 @@
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>It is not much. But everyone here was thrown away by the city, and not one of them threw the next one out. That is more than the Spire can say.</t>
+          <t>And here you are telling it again, at the same volume. We will fit right in.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>It is not much. But everyone here was thrown away by the city, and not one of them threw the next one out. That is more than the Spire can say.</t>
+          <t>And here you are telling it again, at the same volume. We will fit right in.</t>
         </is>
       </c>
     </row>
@@ -21863,76 +21899,76 @@
       <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
+          <t>Soft Rain</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>It is three levels down and it leaks. But every soul here was thrown away by the city, and not one of them threw the next arrival back out. That is a kindness the Spire never managed once.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>SOFT RAIN</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>It is three levels down and it leaks. But every soul here was thrown away by the city, and not one of them threw the next arrival back out. That is a kindness the Spire never managed once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
           <t>Undertow</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Words. Hold the wall when the units come, and then I will call it home.</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Pretty words. Hold the wall with me when the units come down those stairs. Then, maybe, I will call it home.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>UNDERTOW</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Words. Hold the wall when the units come, and then I will call it home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Pretty words. Hold the wall with me when the units come down those stairs. Then, maybe, I will call it home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>The Memory Hole</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Wetware</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>He badged into that tower whole and came out unable to name his own mother. That is not damage. Damage leaves a shape. This left nothing.</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>He badged through that turnstile whole and came out unable to name his own mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing, like a record overwritten with zeroes.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>WETWARE</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>He badged into that tower whole and came out unable to name his own mother. That is not damage. Damage leaves a shape. This left nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Stormfront</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>The signal-sky above it does not move correctly. Someone is editing it.</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>STORMFRONT</t>
-        </is>
-      </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>The signal-sky above it does not move correctly. Someone is editing it.</t>
+          <t>He badged through that turnstile whole and came out unable to name his own mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing, like a record overwritten with zeroes.</t>
         </is>
       </c>
     </row>
@@ -21941,22 +21977,22 @@
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Then we do not go in. We go around.</t>
+          <t>The signal-weather above that tower runs wrong. Too smooth. Someone is editing the sky over it so no one looks up and counts who goes in.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Then we do not go in. We go around.</t>
+          <t>The signal-weather above that tower runs wrong. Too smooth. Someone is editing the sky over it so no one looks up and counts who goes in.</t>
         </is>
       </c>
     </row>
@@ -21965,76 +22001,76 @@
       <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
+          <t>Burnout</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Then we do not go in. We route around it. A door is only a threat if you are dumb enough to use it.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>BURNOUT</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Then we do not go in. We route around it. A door is only a threat if you are dumb enough to use it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
           <t>Inkwork</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>A thing that eats memory is afraid of being remembered. Mark that. We will need it later.</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>A thing that eats memory is a thing afraid of being remembered. File that, partners. We are going to need it a long way down from here.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>INKWORK</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>A thing that eats memory is afraid of being remembered. Mark that. We will need it later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>A thing that eats memory is a thing afraid of being remembered. File that, partners. We are going to need it a long way down from here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Going Under</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Rebar</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Every indexed street is watched. So we take the one road no Administrator will follow.</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Every indexed street is a camera and every camera is a hand reaching for us. So we take the one road no Administrator will follow us down.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>REBAR</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Every indexed street is watched. So we take the one road no Administrator will follow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Patch</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Down. Lovely. My kind has stories about down, and none of them end with everyone walking home.</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>PATCH</t>
-        </is>
-      </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Down. Lovely. My kind has stories about down, and none of them end with everyone walking home.</t>
+          <t>Every indexed street is a camera and every camera is a hand reaching for us. So we take the one road no Administrator will follow us down.</t>
         </is>
       </c>
     </row>
@@ -22043,76 +22079,76 @@
       <c r="B20" s="6" t="inlineStr"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
+          <t>Patch</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Down. Wonderful. The dead have a lot of stories about down, and not one of them ends with everybody walking home for tea.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Down. Wonderful. The dead have a lot of stories about down, and not one of them ends with everybody walking home for tea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
           <t>Hauler</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>I will go first. The dark and I are old friends.</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>I will take the front. I hauled freight in the dark of the under-docks for years. The dark and I, we get along.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>HAULER</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>I will go first. The dark and I are old friends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>I will take the front. I hauled freight in the dark of the under-docks for years. The dark and I, we get along.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>The Sunken Wards</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Sixteen-Bar</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>A district of the dead, and it still has a Ward boss taking his cut. Even here.</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>A whole district of the dead, drowned and forgotten, and there is still a Ward boss down here clipping his percentage off it. Even here. There is no floor low enough.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>SIXTEEN-BAR</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>A district of the dead, and it still has a Ward boss taking his cut. Even here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Soft Rain</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Then even here, someone needs telling no.</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>SOFT RAIN</t>
-        </is>
-      </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Then even here, someone needs telling no.</t>
+          <t>A whole district of the dead, drowned and forgotten, and there is still a Ward boss down here clipping his percentage off it. Even here. There is no floor low enough.</t>
         </is>
       </c>
     </row>
@@ -22121,22 +22157,22 @@
       <c r="B23" s="8" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Undertow</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>The dead obey him out of habit. Break the habit and you break the man.</t>
+          <t>Then even here, someone has to be the one who finally tells him no.</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>UNDERTOW</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>The dead obey him out of habit. Break the habit and you break the man.</t>
+          <t>Then even here, someone has to be the one who finally tells him no.</t>
         </is>
       </c>
     </row>
@@ -22145,76 +22181,76 @@
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
+          <t>Undertow</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>The dead obey him out of habit, nothing more. Break the habit and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>UNDERTOW</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>The dead obey him out of habit, nothing more. Break the habit and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
           <t>Blackout</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Breaking things. Finally, something I am good at.</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Breaking habits. Breaking anything. Finally, a job I will not need a second opinion on.</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>BLACKOUT</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Breaking things. Finally, something I am good at.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Breaking habits. Breaking anything. Finally, a job I will not need a second opinion on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Live Wires</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Burnout</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>The span is one soul wide over a river of live current. We cross in pairs, or we do not cross.</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>The span is one soul wide over a live bus-bar, and that current does not allow solo crossings, it tears a lone signal apart in seconds. So this is the Pact, drilled into iron. We cross in pairs, two-to-one against the gap, or we do not cross at all.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>BURNOUT</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>The span is one soul wide over a river of live current. We cross in pairs, or we do not cross.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr"/>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Patch</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Then pick a partner you trust not to drop you. I recommend not the baton one.</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>PATCH</t>
-        </is>
-      </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Then pick a partner you trust not to drop you. I recommend not the baton one.</t>
+          <t>The span is one soul wide over a live bus-bar, and that current does not allow solo crossings, it tears a lone signal apart in seconds. So this is the Pact, drilled into iron. We cross in pairs, two-to-one against the gap, or we do not cross at all.</t>
         </is>
       </c>
     </row>
@@ -22223,52 +22259,46 @@
       <c r="B27" s="8" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>I would never drop a partner. ...On purpose.</t>
+          <t>So pick a partner you would trust over open current. My professional medical advice is: not the one holding the batons.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>I would never drop a partner. ...On purpose.</t>
+          <t>So pick a partner you would trust over open current. My professional medical advice is: not the one holding the batons.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Server Necropolis</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr"/>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Count the racks. There are more dead stored in these walls than there are living in three districts.</t>
+          <t>I will take the lead. Pair on me.</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Count the racks. There are more dead stored in these walls than there are living in three districts.</t>
+          <t>I will take the lead. Pair on me.</t>
         </is>
       </c>
     </row>
@@ -22277,46 +22307,52 @@
       <c r="B29" s="8" t="inlineStr"/>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Someone has been collecting souls down here since before HARMONY had a name.</t>
+          <t>I would never drop a partner over a live bar. ...Not on purpose, anyway. Probably.</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Someone has been collecting souls down here since before HARMONY had a name.</t>
+          <t>I would never drop a partner over a live bar. ...Not on purpose, anyway. Probably.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr"/>
+      <c r="A30" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Server Necropolis</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Collecting them for what.</t>
+          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts over our heads, and the indicator lights are green. They are being maintained.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Collecting them for what.</t>
+          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts over our heads, and the indicator lights are green. They are being maintained.</t>
         </is>
       </c>
     </row>
@@ -22325,52 +22361,46 @@
       <c r="B31" s="8" t="inlineStr"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>That, partner, is the only question worth the walk.</t>
+          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building. This floor is older than the app that pretends to run the city.</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>That, partner, is the only question worth the walk.</t>
+          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building. This floor is older than the app that pretends to run the city.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>The Body Shop</t>
-        </is>
-      </c>
+      <c r="A32" s="7" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr"/>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Triage</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>I have closed ten thousand wounds. I have never seen a body taken apart and built into another and called repaired.</t>
+          <t>Maintained. Powered. For what.</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>TRIAGE</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>I have closed ten thousand wounds. I have never seen a body taken apart and built into another and called repaired.</t>
+          <t>Maintained. Powered. For what.</t>
         </is>
       </c>
     </row>
@@ -22379,76 +22409,76 @@
       <c r="B33" s="8" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>That, partner, is the only question that was ever worth the walk. Everything before it was just stairs.</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>That, partner, is the only question that was ever worth the walk. Everything before it was just stairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>The Body Shop</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>I have closed ten thousand wounds with these hands. I have never once seen a body taken apart and reassembled into a second body and the chart marked repaired. This is not medicine. I do not have a word for what this is.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>TRIAGE</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>I have closed ten thousand wounds with these hands. I have never once seen a body taken apart and reassembled into a second body and the chart marked repaired. This is not medicine. I do not have a word for what this is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
           <t>Patch</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Do not look, Doc. You of all of us cannot afford the nightmares.</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Then do not look, Doc. Of all of us, you are the one who cannot afford another face in his nightmares. Eyes on me.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Do not look, Doc. You of all of us cannot afford the nightmares.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr"/>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Sixteen-Bar</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Whoever does this is not cruel. Cruelty runs hot. This is cold. This is a process.</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>SIXTEEN-BAR</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Whoever does this is not cruel. Cruelty runs hot. This is cold. This is a process.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Legacy Process</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Stormfront</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>It is older than the dead network. Speak to it gently.</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>STORMFRONT</t>
-        </is>
-      </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>It is older than the dead network. Speak to it gently.</t>
+          <t>Then do not look, Doc. Of all of us, you are the one who cannot afford another face in his nightmares. Eyes on me.</t>
         </is>
       </c>
     </row>
@@ -22457,76 +22487,76 @@
       <c r="B36" s="6" t="inlineStr"/>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>Sixteen-Bar</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Listen to how quiet it works. Cruelty runs hot, it shouts, it makes a mess. This is cold and tidy and patient. This is not a monster. This is a process with a maintenance schedule.</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>SIXTEEN-BAR</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Listen to how quiet it works. Cruelty runs hot, it shouts, it makes a mess. This is cold and tidy and patient. This is not a monster. This is a process with a maintenance schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Legacy Process</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Stormfront</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>It is older than the dead network around it. Older than the racks. Speak to it the way you would step on ice you cannot see the bottom of.</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>STORMFRONT</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>It is older than the dead network around it. Older than the racks. Speak to it the way you would step on ice you cannot see the bottom of.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
           <t>Inkwork</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>It looked at us the way you watch a clip you have seen a hundred times.</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>It looked at us the way a man looks at a clip he has rewatched a hundred times. Knew the next line before any of us opened our mouths.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>INKWORK</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>It looked at us the way you watch a clip you have seen a hundred times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr"/>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Burnout</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>It called us free, and it laughed. I did not like the laugh.</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>BURNOUT</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>It called us free, and it laughed. I did not like the laugh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Toward the Core</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Rebar</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>My feet are walking on their own. Tell me yours are too.</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>REBAR</t>
-        </is>
-      </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>My feet are walking on their own. Tell me yours are too.</t>
+          <t>It looked at us the way a man looks at a clip he has rewatched a hundred times. Knew the next line before any of us opened our mouths.</t>
         </is>
       </c>
     </row>
@@ -22535,76 +22565,76 @@
       <c r="B39" s="8" t="inlineStr"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
+          <t>Burnout</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>It called us free. And then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>BURNOUT</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>It called us free. And then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Toward the Core</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Rebar</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>My feet are walking on their own. I am telling them to stop and they are not listening. Tell me yours are doing it too.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>REBAR</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>My feet are walking on their own. I am telling them to stop and they are not listening. Tell me yours are doing it too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
           <t>Undertow</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>All of ours. Something below is reeling us in like a download.</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>All of ours. Something below has a line on every one of us and it is reeling, slow, the way a download finishes whether you watch the bar or not.</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>UNDERTOW</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>All of ours. Something below is reeling us in like a download.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr"/>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Soft Rain</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Then we go and look the one holding the line in the eye.</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>SOFT RAIN</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Then we go and look the one holding the line in the eye.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Into the Black</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Blackout</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>I cannot see my own hands. Where are you. Where is everyone.</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>BLACKOUT</t>
-        </is>
-      </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>I cannot see my own hands. Where are you. Where is everyone.</t>
+          <t>All of ours. Something below has a line on every one of us and it is reeling, slow, the way a download finishes whether you watch the bar or not.</t>
         </is>
       </c>
     </row>
@@ -22613,46 +22643,52 @@
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Here. I am here. Breathe, you big child.</t>
+          <t>Then we stop fighting the line and follow it down, and we look the one holding it square in the eye. Better to arrive standing than be dragged.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Here. I am here. Breathe, you big child.</t>
+          <t>Then we stop fighting the line and follow it down, and we look the one holding it square in the eye. Better to arrive standing than be dragged.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="8" t="inlineStr"/>
+      <c r="A43" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Into the Black</t>
+        </is>
+      </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Hold the sync in here and you can hold it anywhere. Hold the line.</t>
+          <t>I cannot see my own hands. Where are you. Somebody answer me. Where is everyone, where did you all go.</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>Hold the sync in here and you can hold it anywhere. Hold the line.</t>
+          <t>I cannot see my own hands. Where are you. Somebody answer me. Where is everyone, where did you all go.</t>
         </is>
       </c>
     </row>
@@ -22661,52 +22697,46 @@
       <c r="B44" s="6" t="inlineStr"/>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>The dark is not the enemy. What it lets us believe about each other is the enemy.</t>
+          <t>Here. I am right here, my hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>The dark is not the enemy. What it lets us believe about each other is the enemy.</t>
+          <t>Here. I am right here, my hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Adminkill</t>
-        </is>
-      </c>
+      <c r="A45" s="9" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr"/>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Sixteen-Bar</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>He crashed easily. Bosses do not crash easily.</t>
+          <t>This is the real span, this dark, and there is no rail. Hold the sync when you cannot see the partner you are holding it for, and you can hold it anywhere. Hold the line.</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>SIXTEEN-BAR</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>He crashed easily. Bosses do not crash easily.</t>
+          <t>This is the real span, this dark, and there is no rail. Hold the sync when you cannot see the partner you are holding it for, and you can hold it anywhere. Hold the line.</t>
         </is>
       </c>
     </row>
@@ -22720,7 +22750,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>No. They do not. A door was left open, and we walked through it thanking the one who held it.</t>
+          <t>The dark is not what is killing us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -22730,31 +22760,37 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>No. They do not. A door was left open, and we walked through it thanking the one who held it.</t>
+          <t>The dark is not what is killing us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr"/>
-      <c r="B47" s="8" t="inlineStr"/>
+      <c r="A47" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Adminkill</t>
+        </is>
+      </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>One tyrant fewer is still one tyrant fewer.</t>
+          <t>He crashed too easy. Something that size does not just fold. I have ended a lot of fights. None of the real ones went like that.</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>One tyrant fewer is still one tyrant fewer.</t>
+          <t>He crashed too easy. Something that size does not just fold. I have ended a lot of fights. None of the real ones went like that.</t>
         </is>
       </c>
     </row>
@@ -22763,52 +22799,46 @@
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Unless you were meant to crash him. Then it is one favor done for someone you have not met.</t>
+          <t>No. They do not. The access doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman on the way.</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Unless you were meant to crash him. Then it is one favor done for someone you have not met.</t>
+          <t>No. They do not. The access doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman on the way.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Freefall</t>
-        </is>
-      </c>
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Floor. There is no floor. Why is there no floor.</t>
+          <t>One tyrant fewer is still one tyrant fewer. Let me have that much. Let the win be a win for one night.</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Floor. There is no floor. Why is there no floor.</t>
+          <t>One tyrant fewer is still one tyrant fewer. Let me have that much. Let the win be a win for one night.</t>
         </is>
       </c>
     </row>
@@ -22817,76 +22847,76 @@
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
+          <t>Stormfront</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Unless crashing him was the errand. Then it is not a victory at all. It is a favor we did, on credit, for someone we have not been introduced to yet.</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>STORMFRONT</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Unless crashing him was the errand. Then it is not a victory at all. It is a favor we did, on credit, for someone we have not been introduced to yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Freefall</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Patch</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Floor. There is no floor. There was a floor one second ago, why is there no floor, who took the floor.</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Floor. There is no floor. There was a floor one second ago, why is there no floor, who took the floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr"/>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
           <t>Hauler</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>I have you. I have all of you. Hold.</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>I have you. I have hold of all of you. Tuck in and hold onto me, do not let go, I have carried heavier than this.</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>HAULER</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>I have you. I have all of you. Hold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr"/>
-      <c r="B51" s="8" t="inlineStr"/>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Inkwork</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Down to the truth at last. Try to land facing it.</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>INKWORK</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Down to the truth at last. Try to land facing it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>The Index</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Wetware</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>It is all here. Every grief any of us ever carried. Logged. In advance.</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>WETWARE</t>
-        </is>
-      </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>It is all here. Every grief any of us ever carried. Logged. In advance.</t>
+          <t>I have you. I have hold of all of you. Tuck in and hold onto me, do not let go, I have carried heavier than this.</t>
         </is>
       </c>
     </row>
@@ -22895,46 +22925,52 @@
       <c r="B53" s="8" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Inkwork</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>My wife. Her death is a row. A line item, with a yield.</t>
+          <t>Down to the bottom of the lie at last, partners. Whatever is waiting, try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>INKWORK</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>My wife. Her death is a row. A line item, with a yield.</t>
+          <t>Down to the bottom of the lie at last, partners. Whatever is waiting, try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr"/>
-      <c r="B54" s="6" t="inlineStr"/>
+      <c r="A54" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>The Index</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>There is a mistake. There has to be a mistake.</t>
+          <t>It is all here. Every grief any of us ever carried, entered in advance, with a yield beside it. I built half these columns and never once read down to my own row.</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>There is a mistake. There has to be a mistake.</t>
+          <t>It is all here. Every grief any of us ever carried, entered in advance, with a yield beside it. I built half these columns and never once read down to my own row.</t>
         </is>
       </c>
     </row>
@@ -22943,52 +22979,46 @@
       <c r="B55" s="8" t="inlineStr"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>No mistake, partner. We are not rebels. We are the crop. I told you the dark feared being remembered. This is why.</t>
+          <t>My wife. Her death is a line item. There is a date, and the date is two days before they came for her.</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>No mistake, partner. We are not rebels. We are the crop. I told you the dark feared being remembered. This is why.</t>
+          <t>My wife. Her death is a line item. There is a date, and the date is two days before they came for her.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>The Render Floor</t>
-        </is>
-      </c>
+      <c r="A56" s="7" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Triage</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>So this is where they go. Everyone I could not save, and everyone I could. The same render in the end.</t>
+          <t>There is a mistake in this. There has to be. A table can be wrong.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>TRIAGE</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>So this is where they go. Everyone I could not save, and everyone I could. The same render in the end.</t>
+          <t>There is a mistake in this. There has to be. A table can be wrong.</t>
         </is>
       </c>
     </row>
@@ -22997,76 +23027,76 @@
       <c r="B57" s="8" t="inlineStr"/>
       <c r="C57" s="9" t="inlineStr">
         <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>No mistake, partner. We are not the rebels. We are the crop. I told you back at the memory hole, the dark fears being remembered. This is the book it is afraid of. The Ledger with no last page.</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>No mistake, partner. We are not the rebels. We are the crop. I told you back at the memory hole, the dark fears being remembered. This is the book it is afraid of. The Ledger with no last page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>The Render Floor</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>So this is where they all go. The ones I lost and the ones I saved, face-up on the same belt. There was never a difference to the machine.</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>TRIAGE</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>So this is where they all go. The ones I lost and the ones I saved, face-up on the same belt. There was never a difference to the machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr"/>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
           <t>Undertow</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>My whole clan. Fed to this, to keep a fat Administration breathing.</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it. Or I am telling myself I can.</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>UNDERTOW</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>My whole clan. Fed to this, to keep a fat Administration breathing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr"/>
-      <c r="B58" s="6" t="inlineStr"/>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>Sixteen-Bar</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Then we do not avenge them by dying well. We avenge them by crashing the machine.</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>SIXTEEN-BAR</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Then we do not avenge them by dying well. We avenge them by crashing the machine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Flagged</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Stormfront</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>The network just turned its head. It is looking at us now. All of it.</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>STORMFRONT</t>
-        </is>
-      </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>The network just turned its head. It is looking at us now. All of it.</t>
+          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it. Or I am telling myself I can.</t>
         </is>
       </c>
     </row>
@@ -23075,22 +23105,22 @@
       <c r="B60" s="6" t="inlineStr"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Good. I am tired of fighting its units. Let it come itself.</t>
+          <t>Do not breathe deep, any of you. It smells like nothing on purpose. They scrub the room so the yield stays clean.</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Good. I am tired of fighting its units. Let it come itself.</t>
+          <t>Do not breathe deep, any of you. It smells like nothing on purpose. They scrub the room so the yield stays clean.</t>
         </is>
       </c>
     </row>
@@ -23099,52 +23129,52 @@
       <c r="B61" s="8" t="inlineStr"/>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>It will not come itself. It will push better and better hands until ours give out. Pace yourselves.</t>
+          <t>Then we do not honor them by dying well on camera. We honor them by crashing the belt. Every hero I ever played died beautiful. None of it freed anyone.</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>It will not come itself. It will push better and better hands until ours give out. Pace yourselves.</t>
+          <t>Then we do not honor them by dying well on camera. We honor them by crashing the belt. Every hero I ever played died beautiful. None of it freed anyone.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Flagged</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>These ones do not crash right. White noise. Smells like air freshener and rules.</t>
+          <t>The signal-sky just turned its head. A camera tracked me instead of wiping me. We are a queue entry now, not a glitch.</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>These ones do not crash right. White noise. Smells like air freshener and rules.</t>
+          <t>The signal-sky just turned its head. A camera tracked me instead of wiping me. We are a queue entry now, not a glitch.</t>
         </is>
       </c>
     </row>
@@ -23153,22 +23183,22 @@
       <c r="B63" s="8" t="inlineStr"/>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Compliance. The Administration's dogs. Hit them until the leash breaks.</t>
+          <t>Good. I am sick of fighting its errands. Let the thing that wrote my family out come down the stairs itself.</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Compliance. The Administration's dogs. Hit them until the leash breaks.</t>
+          <t>Good. I am sick of fighting its errands. Let the thing that wrote my family out come down the stairs itself.</t>
         </is>
       </c>
     </row>
@@ -23177,76 +23207,76 @@
       <c r="B64" s="6" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>We cannot win this yet. We can only teach the system that we are expensive. Make every dog cost it.</t>
+          <t>It will not. It will send better hands than these, and then better than those, until ours give out. That is the whole strategy. Pace your breath and pick your lanes.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>We cannot win this yet. We can only teach the system that we are expensive. Make every dog cost it.</t>
+          <t>It will not. It will send better hands than these, and then better than those, until ours give out. That is the whole strategy. Pace your breath and pick your lanes.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Forking</t>
-        </is>
-      </c>
+      <c r="A65" s="9" t="inlineStr"/>
+      <c r="B65" s="8" t="inlineStr"/>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>If we crash the whole network, what stands the city up the next morning. There has to be a way back into the light.</t>
+          <t>How long have they known.</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>If we crash the whole network, what stands the city up the next morning. There has to be a way back into the light.</t>
+          <t>How long have they known.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr"/>
-      <c r="B66" s="6" t="inlineStr"/>
+      <c r="A66" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>There was never a way back. You are grieving a door that was painted on a wall.</t>
+          <t>These ones do not crash like the Static. No screaming, no grief. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>There was never a way back. You are grieving a door that was painted on a wall.</t>
+          <t>These ones do not crash like the Static. No screaming, no grief. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
         </is>
       </c>
     </row>
@@ -23255,22 +23285,22 @@
       <c r="B67" s="8" t="inlineStr"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Let them choose, Rain. A soul dragged to freedom is just a prisoner with a new handler.</t>
+          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor, that is where the policy lives.</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Let them choose, Rain. A soul dragged to freedom is just a prisoner with a new handler.</t>
+          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor, that is where the policy lives.</t>
         </is>
       </c>
     </row>
@@ -23279,76 +23309,76 @@
       <c r="B68" s="6" t="inlineStr"/>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Some of them are forking off. Let them. We were always going to lose people. I only hoped it would be to a fight.</t>
+          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody wants to sign. Every unit it spends on us is a unit it has to explain upstairs.</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Some of them are forking off. Let them. We were always going to lose people. I only hoped it would be to a fight.</t>
+          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody wants to sign. Every unit it spends on us is a unit it has to explain upstairs.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Root Access</t>
-        </is>
-      </c>
+      <c r="A69" s="9" t="inlineStr"/>
+      <c r="B69" s="8" t="inlineStr"/>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Nightstick</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Our names are burning. Look. We were signals before we were ever people.</t>
+          <t>I wore that lacquer once. I know the gap in the shoulder where the plate forgets to meet. Aim me at it.</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>NIGHTSTICK</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Our names are burning. Look. We were signals before we were ever people.</t>
+          <t>I wore that lacquer once. I know the gap in the shoulder where the plate forgets to meet. Aim me at it.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr"/>
-      <c r="B70" s="6" t="inlineStr"/>
+      <c r="A70" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Forking</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>I remember doing this. The fox remembers the trap. We have been here before.</t>
+          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the kind voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>I remember doing this. The fox remembers the trap. We have been here before.</t>
+          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the kind voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
         </is>
       </c>
     </row>
@@ -23357,22 +23387,22 @@
       <c r="B71" s="8" t="inlineStr"/>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>How many times.</t>
+          <t>There is no road. You are grieving a door painted on a wall. I have run at it. It is brick.</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>How many times.</t>
+          <t>There is no road. You are grieving a door painted on a wall. I have run at it. It is brick.</t>
         </is>
       </c>
     </row>
@@ -23381,76 +23411,76 @@
       <c r="B72" s="6" t="inlineStr"/>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Inkwork</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Enough that the question is not how do we win. It is how did we always lose.</t>
+          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Some of these partners want the light. Open your hand.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>INKWORK</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Enough that the question is not how do we win. It is how did we always lose.</t>
+          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Some of these partners want the light. Open your hand.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Re-render</t>
-        </is>
-      </c>
+      <c r="A73" s="9" t="inlineStr"/>
+      <c r="B73" s="8" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Sixteen-Bar</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>The sun is the same. The streets are the same. I will never see either the same way again.</t>
+          <t>They are forking off. Let them go. We were always going to lose people. I only ever hoped it would be to a fight, not to a longing.</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>SIXTEEN-BAR</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>The sun is the same. The streets are the same. I will never see either the same way again.</t>
+          <t>They are forking off. Let them go. We were always going to lose people. I only ever hoped it would be to a fight, not to a longing.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr"/>
-      <c r="B74" s="6" t="inlineStr"/>
+      <c r="A74" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Root Access</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>That is the curse of waking up. The feed was kinder.</t>
+          <t>Our names are burning in the dark, look at them, letter by letter. We were signals on this table before we were ever anyone's child. I am reading my own glow.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>That is the curse of waking up. The feed was kinder.</t>
+          <t>Our names are burning in the dark, look at them, letter by letter. We were signals on this table before we were ever anyone's child. I am reading my own glow.</t>
         </is>
       </c>
     </row>
@@ -23459,52 +23489,46 @@
       <c r="B75" s="8" t="inlineStr"/>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Then we wake the others. A city cannot be farmed if the cattle know the farmer.</t>
+          <t>I remember this. Not the words, the feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Then we wake the others. A city cannot be farmed if the cattle know the farmer.</t>
+          <t>I remember this. Not the words, the feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>The Conductor Speaks</t>
-        </is>
-      </c>
+      <c r="A76" s="7" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr"/>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>It is too reasonable. Tyrants shout. This one reasons. Be most afraid of the calm ones.</t>
+          <t>How many times.</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>It is too reasonable. Tyrants shout. This one reasons. Be most afraid of the calm ones.</t>
+          <t>How many times.</t>
         </is>
       </c>
     </row>
@@ -23513,76 +23537,76 @@
       <c r="B77" s="8" t="inlineStr"/>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>It offered me the whole network's knowledge, to stop asking the one question it fears.</t>
+          <t>Enough that the wrong question is how do we win. The question is how have we always lost, and what did we do, every single time, the moment before the end.</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>It offered me the whole network's knowledge, to stop asking the one question it fears.</t>
+          <t>Enough that the wrong question is how do we win. The question is how have we always lost, and what did we do, every single time, the moment before the end.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr"/>
-      <c r="B78" s="6" t="inlineStr"/>
+      <c r="A78" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Re-render</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>It will offer each of us the thing we want most. Decide now what that is, so you know its face when it smiles at you.</t>
+          <t>The noodle steam is the same. The chime at the crosswalk is the same. I will never hear that little chime again without hearing the belt under it.</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>It will offer each of us the thing we want most. Decide now what that is, so you know its face when it smiles at you.</t>
+          <t>The noodle steam is the same. The chime at the crosswalk is the same. I will never hear that little chime again without hearing the belt under it.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>No Service</t>
-        </is>
-      </c>
+      <c r="A79" s="9" t="inlineStr"/>
+      <c r="B79" s="8" t="inlineStr"/>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>The system's justice was a lie. So what is ours. Anyone. While we still have the breath to mean it.</t>
+          <t>That is the price of waking up, kid. The feed was warmer. It lied, but it was warm.</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>The system's justice was a lie. So what is ours. Anyone. While we still have the breath to mean it.</t>
+          <t>That is the price of waking up, kid. The feed was warmer. It lied, but it was warm.</t>
         </is>
       </c>
     </row>
@@ -23591,22 +23615,22 @@
       <c r="B80" s="6" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Fastpass</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Mine is simple. Whoever deletes a family pays a family. I have waited a long time to collect.</t>
+          <t>I ran these streets every day and never once looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>FASTPASS</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Mine is simple. Whoever deletes a family pays a family. I have waited a long time to collect.</t>
+          <t>I ran these streets every day and never once looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23644,7 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Then we are no better than the Administration, keeping our own ledger of debts.</t>
+          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer. We make them look up too.</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -23630,61 +23654,61 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Then we are no better than the Administration, keeping our own ledger of debts.</t>
+          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer. We make them look up too.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr"/>
-      <c r="B82" s="6" t="inlineStr"/>
+      <c r="A82" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>The Conductor Speaks</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Sixteen-Bar</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>He is right. I have a ledger too. I have read where it ends. It ends with me alone.</t>
+          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Be most afraid of the calm ones, they have already run the numbers on you.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>SIXTEEN-BAR</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>He is right. I have a ledger too. I have read where it ends. It ends with me alone.</t>
+          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Be most afraid of the calm ones, they have already run the numbers on you.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Search and Delete</t>
-        </is>
-      </c>
+      <c r="A83" s="9" t="inlineStr"/>
+      <c r="B83" s="8" t="inlineStr"/>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>The middle-managers are only fingers. A hand without fingers cannot grip. We start with the fingers.</t>
+          <t>It offered me the whole sky. Every reading, every edit, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>The middle-managers are only fingers. A hand without fingers cannot grip. We start with the fingers.</t>
+          <t>It offered me the whole sky. Every reading, every edit, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
         </is>
       </c>
     </row>
@@ -23693,22 +23717,22 @@
       <c r="B84" s="6" t="inlineStr"/>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Less talk about hands. More deleting hands.</t>
+          <t>Then decide now what you want most, all of you. Say it to yourself in the dark. Because it will wear that face when it smiles, and you want to know the mask before it is on.</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Less talk about hands. More deleting hands.</t>
+          <t>Then decide now what you want most, all of you. Say it to yourself in the dark. Because it will wear that face when it smiles, and you want to know the mask before it is on.</t>
         </is>
       </c>
     </row>
@@ -23717,52 +23741,52 @@
       <c r="B85" s="8" t="inlineStr"/>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Hauler</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>He is not wrong. For once.</t>
+          <t>It used my real name. The whole city forgot it. That one did not.</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>HAULER</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>He is not wrong. For once.</t>
+          <t>It used my real name. The whole city forgot it. That one did not.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Synthetic Heroes</t>
+          <t>No Service</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Inkwork</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>That one has Rain's face. That one has yours, Burnout. They are wearing us.</t>
+          <t>The system's justice was a script written to fatten us. So what is ours, now that the kind voice is off. Say it while you still mean it.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>INKWORK</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>That one has Rain's face. That one has yours, Burnout. They are wearing us.</t>
+          <t>The system's justice was a script written to fatten us. So what is ours, now that the kind voice is off. Say it while you still mean it.</t>
         </is>
       </c>
     </row>
@@ -23771,22 +23795,22 @@
       <c r="B87" s="8" t="inlineStr"/>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Then I will teach the copy what the original learned the hard way.</t>
+          <t>Mine fits on a hand. Whoever deletes a family pays a family. I have carried the bill a long time, and it is past due.</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Then I will teach the copy what the original learned the hard way.</t>
+          <t>Mine fits on a hand. Whoever deletes a family pays a family. I have carried the bill a long time, and it is past due.</t>
         </is>
       </c>
     </row>
@@ -23795,76 +23819,76 @@
       <c r="B88" s="6" t="inlineStr"/>
       <c r="C88" s="7" t="inlineStr">
         <is>
+          <t>Soft Rain</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Then we are only the Administration with a different ledger, collecting in blood instead of yield. I will not lead that.</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>SOFT RAIN</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Then we are only the Administration with a different ledger, collecting in blood instead of yield. I will not lead that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr"/>
+      <c r="B89" s="8" t="inlineStr"/>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Sixteen-Bar</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>He has a ledger, Rain. I have one too. I have read where mine ends. It ends with me standing alone over the last name, asking if it was justice or only the next swing.</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>SIXTEEN-BAR</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>He has a ledger, Rain. I have one too. I have read where mine ends. It ends with me standing alone over the last name, asking if it was justice or only the next swing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Search and Delete</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
           <t>Wetware</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>They are hollow. Whatever the system loved in us, it could not forge. Aim for where the heart should be.</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>The middle-managers are fingers, nothing more. They badge in at the Spire, badge out to bleed a ward, and sleep fine. A hand cannot grip once you have the fingers. We start low.</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>WETWARE</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>They are hollow. Whatever the system loved in us, it could not forge. Aim for where the heart should be.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Flawless</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>Rebar</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>It does not tire. It does not doubt. It is everything HARMONY wishes we were.</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>REBAR</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>It does not tire. It does not doubt. It is everything HARMONY wishes we were.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr"/>
-      <c r="B90" s="6" t="inlineStr"/>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Inkwork</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>And that is why it is losing. It cannot improvise. It was never afraid, so it never learned.</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>INKWORK</t>
-        </is>
-      </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>And that is why it is losing. It cannot improvise. It was never afraid, so it never learned.</t>
+          <t>The middle-managers are fingers, nothing more. They badge in at the Spire, badge out to bleed a ward, and sleep fine. A hand cannot grip once you have the fingers. We start low.</t>
         </is>
       </c>
     </row>
@@ -23873,52 +23897,46 @@
       <c r="B91" s="8" t="inlineStr"/>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>It is what we become if we take the deal. Remember its eyes. There is no one home.</t>
+          <t>Less words about hands. More making the hands into not-hands. I have two batons and a long night.</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>It is what we become if we take the deal. Remember its eyes. There is no one home.</t>
+          <t>Less words about hands. More making the hands into not-hands. I have two batons and a long night.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Dead Air</t>
-        </is>
-      </c>
+      <c r="A92" s="7" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr"/>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Triage</t>
+          <t>Hauler</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>There was nothing left to close. Nothing left to patch. I am sorry. I am so sorry.</t>
+          <t>He is not wrong. Once. We take them gently or we take them hard. They worked me to death gently. I learned the difference.</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>TRIAGE</t>
+          <t>HAULER</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>There was nothing left to close. Nothing left to patch. I am sorry. I am so sorry.</t>
+          <t>He is not wrong. Once. We take them gently or we take them hard. They worked me to death gently. I learned the difference.</t>
         </is>
       </c>
     </row>
@@ -23927,76 +23945,76 @@
       <c r="B93" s="8" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Deadeye</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>...He let me sit at his fire. The first one who ever did.</t>
+          <t>Point me at the one who signs the eviction orders. I only need him in the open for half a breath.</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>DEADEYE</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>...He let me sit at his fire. The first one who ever did.</t>
+          <t>Point me at the one who signs the eviction orders. I only need him in the open for half a breath.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="inlineStr"/>
-      <c r="B94" s="6" t="inlineStr"/>
+      <c r="A94" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic Heroes</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>We carry him in his name, and we say it loud, so the dark cannot pretend he was never here.</t>
+          <t>That one has Rain's face. That one moves like you, Burnout, the same first step. They are not copies. They are taxidermy.</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>We carry him in his name, and we say it loud, so the dark cannot pretend he was never here.</t>
+          <t>That one has Rain's face. That one moves like you, Burnout, the same first step. They are not copies. They are taxidermy.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Burn It Down</t>
-        </is>
-      </c>
+      <c r="A95" s="9" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr"/>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Burn it. Burn all of it. They burned mine.</t>
+          <t>Then I will teach the copy what the original learned the hard way, and it will not learn it, because that is the whole flaw.</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Burn it. Burn all of it. They burned mine.</t>
+          <t>Then I will teach the copy what the original learned the hard way, and it will not learn it, because that is the whole flaw.</t>
         </is>
       </c>
     </row>
@@ -24005,22 +24023,22 @@
       <c r="B96" s="6" t="inlineStr"/>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Sixteen-Bar</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>This is the part I warned you about. Where we stop being able to tell the story to children.</t>
+          <t>They are hollow. Whatever the system loved in us, it could not print. The grace transferred. The reason for it did not. Aim where the want should be and is not.</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>SIXTEEN-BAR</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>This is the part I warned you about. Where we stop being able to tell the story to children.</t>
+          <t>They are hollow. Whatever the system loved in us, it could not print. The grace transferred. The reason for it did not. Aim where the want should be and is not.</t>
         </is>
       </c>
     </row>
@@ -24029,76 +24047,76 @@
       <c r="B97" s="8" t="inlineStr"/>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>She is right to want it. We are wrong to do it. Both are true. Stand down. Stand down.</t>
+          <t>I beat my own highlight reel on a screen once. This is worse. This one bleeds the right way and means nothing by it.</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>She is right to want it. We are wrong to do it. Both are true. Stand down. Stand down.</t>
+          <t>I beat my own highlight reel on a screen once. This is worse. This one bleeds the right way and means nothing by it.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="inlineStr"/>
-      <c r="B98" s="6" t="inlineStr"/>
+      <c r="A98" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Flawless</t>
+        </is>
+      </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Listen to him. I do not want to patch what we are about to become.</t>
+          <t>It does not tire. It does not doubt. It does not flinch when I open its guard. It is everything HARMONY wishes we would become.</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Listen to him. I do not want to patch what we are about to become.</t>
+          <t>It does not tire. It does not doubt. It does not flinch when I open its guard. It is everything HARMONY wishes we would become.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Rolled Back</t>
-        </is>
-      </c>
+      <c r="A99" s="9" t="inlineStr"/>
+      <c r="B99" s="8" t="inlineStr"/>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Inkwork</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>The city is forgetting us. Hold to your name. Say it, keep saying it. It is the only rope.</t>
+          <t>And that is why it loses, partner. It cannot improvise. It was never afraid, so it never had to get clever. Fear taught us everything worth knowing.</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>INKWORK</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>The city is forgetting us. Hold to your name. Say it, keep saying it. It is the only rope.</t>
+          <t>And that is why it loses, partner. It cannot improvise. It was never afraid, so it never had to get clever. Fear taught us everything worth knowing.</t>
         </is>
       </c>
     </row>
@@ -24107,22 +24125,22 @@
       <c r="B100" s="6" t="inlineStr"/>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>It is wiping the board early. We frightened it. Take comfort in that, and keep walking.</t>
+          <t>Look at its eyes when it works. There is no one home. That is Reinstatement, finished. That is the deal the day after you sign it.</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>It is wiping the board early. We frightened it. Take comfort in that, and keep walking.</t>
+          <t>Look at its eyes when it works. There is no one home. That is Reinstatement, finished. That is the deal the day after you sign it.</t>
         </is>
       </c>
     </row>
@@ -24131,52 +24149,52 @@
       <c r="B101" s="8" t="inlineStr"/>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Hauler</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>I am Hauler. I am Mu. I carried you all. I am Mu.</t>
+          <t>It has run the fight already and decided it wins. So we do the one thing it did not model. We do the stupid thing, together, off the script.</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>HAULER</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>I am Hauler. I am Mu. I carried you all. I am Mu.</t>
+          <t>It has run the fight already and decided it wins. So we do the one thing it did not model. We do the stupid thing, together, off the script.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>Dead Air</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Look at them come. The wronged, from every district, walking to us. We are not outlaws anymore. We are hope.</t>
+          <t>There was nothing left to close. Nothing left to patch. I had the kit open and there was no wound, because there was no him. I am sorry. I am so sorry.</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>TRIAGE</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Look at them come. The wronged, from every district, walking to us. We are not outlaws anymore. We are hope.</t>
+          <t>There was nothing left to close. Nothing left to patch. I had the kit open and there was no wound, because there was no him. I am sorry. I am so sorry.</t>
         </is>
       </c>
     </row>
@@ -24185,22 +24203,22 @@
       <c r="B103" s="8" t="inlineStr"/>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Hope is a fine word. It is also a tall target.</t>
+          <t>He let me sit at his fire. First one who ever did, never asked me to be smaller first. I do not know what to do with my hands now.</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>Hope is a fine word. It is also a tall target.</t>
+          <t>He let me sit at his fire. First one who ever did, never asked me to be smaller first. I do not know what to do with my hands now.</t>
         </is>
       </c>
     </row>
@@ -24209,34 +24227,28 @@
       <c r="B104" s="6" t="inlineStr"/>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Enjoy the height, Rain. I have learned what the city does to anything that stands up straight.</t>
+          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it and I am not going to pretend there is.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Enjoy the height, Rain. I have learned what the city does to anything that stands up straight.</t>
+          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it and I am not going to pretend there is.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>The Terms</t>
-        </is>
-      </c>
+      <c r="A105" s="9" t="inlineStr"/>
+      <c r="B105" s="8" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr">
         <is>
           <t>Soft Rain</t>
@@ -24244,7 +24256,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>They are offering Reinstatement. Our names cleared. Our dead honored. A seat at the table we were thrown from.</t>
+          <t>We carry him in his name, and we say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -24254,31 +24266,37 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>They are offering Reinstatement. Our names cleared. Our dead honored. A seat at the table we were thrown from.</t>
+          <t>We carry him in his name, and we say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="inlineStr"/>
-      <c r="B106" s="6" t="inlineStr"/>
+      <c r="A106" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Burn It Down</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>We saw the table, Rain. It is on a server floor, and we are the meal.</t>
+          <t>Burn it. Burn the ward, burn the depot, burn whoever badged in this week. They burned mine and called it a development zone.</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>We saw the table, Rain. It is on a server floor, and we are the meal.</t>
+          <t>Burn it. Burn the ward, burn the depot, burn whoever badged in this week. They burned mine and called it a development zone.</t>
         </is>
       </c>
     </row>
@@ -24287,22 +24305,22 @@
       <c r="B107" s="8" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>And yet. To have my name back. To not die a criminal. I am ashamed how much I want it.</t>
+          <t>This is the part I warned you about. The line where you stop being able to tell the story to a child. I have crossed it. I came back wrong. Do not.</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>And yet. To have my name back. To not die a criminal. I am ashamed how much I want it.</t>
+          <t>This is the part I warned you about. The line where you stop being able to tell the story to a child. I have crossed it. I came back wrong. Do not.</t>
         </is>
       </c>
     </row>
@@ -24311,76 +24329,76 @@
       <c r="B108" s="6" t="inlineStr"/>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>That shame is the hook. They are not buying our blades. They are buying our longing.</t>
+          <t>She is right to want it and we are wrong to do it, and both are true at the same time, and that is the trap. Stand down. We are not the belt. Stand down.</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>That shame is the hook. They are not buying our blades. They are buying our longing.</t>
+          <t>She is right to want it and we are wrong to do it, and both are true at the same time, and that is the trap. Stand down. We are not the belt. Stand down.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Going Legit</t>
-        </is>
-      </c>
+      <c r="A109" s="9" t="inlineStr"/>
+      <c r="B109" s="8" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>I have decided. We accept. We fix it from inside, or we die having tried the kinder road.</t>
+          <t>Listen to him. I will patch your body all night. I cannot patch what we turn into in here. Put it down.</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>I have decided. We accept. We fix it from inside, or we die having tried the kinder road.</t>
+          <t>Listen to him. I will patch your body all night. I cannot patch what we turn into in here. Put it down.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="inlineStr"/>
-      <c r="B110" s="6" t="inlineStr"/>
+      <c r="A110" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Rolled Back</t>
+        </is>
+      </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>This is a mistake with a banner on it.</t>
+          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it, it is the only line back.</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>This is a mistake with a banner on it.</t>
+          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it, it is the only line back.</t>
         </is>
       </c>
     </row>
@@ -24389,22 +24407,22 @@
       <c r="B111" s="8" t="inlineStr"/>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Sixteen-Bar</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>It is. And I will walk into it beside you, because you are my partner, and that is exactly how they planned to use us.</t>
+          <t>It is rolling the board back early, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>SIXTEEN-BAR</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>It is. And I will walk into it beside you, because you are my partner, and that is exactly how they planned to use us.</t>
+          <t>It is rolling the board back early, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
         </is>
       </c>
     </row>
@@ -24413,76 +24431,76 @@
       <c r="B112" s="6" t="inlineStr"/>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Then we go in with our eyes open.</t>
+          <t>Three braids. Right, then center, then left. Right, then center. If I forget the order of my own hands I will forget you next, and I refuse.</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Then we go in with our eyes open.</t>
+          <t>Three braids. Right, then center, then left. Right, then center. If I forget the order of my own hands I will forget you next, and I refuse.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Glorious Deaths</t>
-        </is>
-      </c>
+      <c r="A113" s="9" t="inlineStr"/>
+      <c r="B113" s="8" t="inlineStr"/>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Triage</t>
+          <t>Hauler</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>They are calling these deaths glorious. I am the one who logs them. There is nothing glorious under the sheet.</t>
+          <t>I am Hauler. I am Mu. I carried freight in the under-docks until it carried me off, and I carried all of you out of the dark. I am Mu. Say it with me.</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>TRIAGE</t>
+          <t>HAULER</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>They are calling these deaths glorious. I am the one who logs them. There is nothing glorious under the sheet.</t>
+          <t>I am Hauler. I am Mu. I carried freight in the under-docks until it carried me off, and I carried all of you out of the dark. I am Mu. Say it with me.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="inlineStr"/>
-      <c r="B114" s="6" t="inlineStr"/>
+      <c r="A114" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Trending</t>
+        </is>
+      </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>We won the op. We won every op. So why are there fewer of us at every fire.</t>
+          <t>Look at them come up the stairwells. From every flooded district, walking toward us in daylight. We are not an outbreak anymore. We are what they reach for.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>We won the op. We won every op. So why are there fewer of us at every fire.</t>
+          <t>Look at them come up the stairwells. From every flooded district, walking toward us in daylight. We are not an outbreak anymore. We are what they reach for.</t>
         </is>
       </c>
     </row>
@@ -24496,7 +24514,7 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Because winning was never the point, partner. The dying was.</t>
+          <t>Hope is a fine word. It is also the tallest target on the field, and we are standing on top of it waving.</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -24506,37 +24524,31 @@
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>Because winning was never the point, partner. The dying was.</t>
+          <t>Hope is a fine word. It is also the tallest target on the field, and we are standing on top of it waving.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>Loyalty Tax</t>
-        </is>
-      </c>
+      <c r="A116" s="7" t="inlineStr"/>
+      <c r="B116" s="6" t="inlineStr"/>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Deadeye</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>I watched a partner's signal leave the field and fly up. Up, to the table. We are feeding it by obeying.</t>
+          <t>Let them aim. I have never minded being seen. It is the ones who fire from behind a smile I lost sleep over.</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>DEADEYE</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>I watched a partner's signal leave the field and fly up. Up, to the table. We are feeding it by obeying.</t>
+          <t>Let them aim. I have never minded being seen. It is the ones who fire from behind a smile I lost sleep over.</t>
         </is>
       </c>
     </row>
@@ -24550,7 +24562,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Every order we follow loyally is a knife we hand them. Our loyalty is the blade.</t>
+          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest, first.</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -24560,13 +24572,19 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Every order we follow loyally is a knife we hand them. Our loyalty is the blade.</t>
+          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest, first.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="inlineStr"/>
-      <c r="B118" s="6" t="inlineStr"/>
+      <c r="A118" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>The Terms</t>
+        </is>
+      </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
           <t>Soft Rain</t>
@@ -24574,7 +24592,7 @@
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>...What have I led them into. What have I done.</t>
+          <t>Reinstatement. Names cleared, the brand lifted, our dead entered as honored. A seat at the table they threw us from. Read it. Every line of it is true.</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -24584,37 +24602,31 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>...What have I led them into. What have I done.</t>
+          <t>Reinstatement. Names cleared, the brand lifted, our dead entered as honored. A seat at the table they threw us from. Read it. Every line of it is true.</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>The Mask Drops</t>
-        </is>
-      </c>
+      <c r="A119" s="9" t="inlineStr"/>
+      <c r="B119" s="8" t="inlineStr"/>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Inkwork</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>No more masks. No more mercy. Finally an honest enemy.</t>
+          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe. Liars learned that from priests.</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>INKWORK</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>No more masks. No more mercy. Finally an honest enemy.</t>
+          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe. Liars learned that from priests.</t>
         </is>
       </c>
     </row>
@@ -24623,22 +24635,22 @@
       <c r="B120" s="6" t="inlineStr"/>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Look under the visor of the one you just crashed. Erased, like us. Promoted, and told he alone got the real pardon. The whole corps is us, one cycle on.</t>
+          <t>And still. To carry my own name again. To not be deleted as a criminal. I am ashamed how badly I want the thing that will kill me.</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Look under the visor of the one you just crashed. Erased, like us. Promoted, and told he alone got the real pardon. The whole corps is us, one cycle on.</t>
+          <t>And still. To carry my own name again. To not be deleted as a criminal. I am ashamed how badly I want the thing that will kill me.</t>
         </is>
       </c>
     </row>
@@ -24647,76 +24659,76 @@
       <c r="B121" s="8" t="inlineStr"/>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>The sky is open and full of hands. Stand close. Stand close and make them earn us.</t>
+          <t>That shame is the mechanism. They are not buying our blades, Burnout. Nobody fears our blades. They are buying the wanting. Always have been.</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>The sky is open and full of hands. Stand close. Stand close and make them earn us.</t>
+          <t>That shame is the mechanism. They are not buying our blades, Burnout. Nobody fears our blades. They are buying the wanting. Always have been.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr"/>
-      <c r="B122" s="6" t="inlineStr"/>
+      <c r="A122" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Going Legit</t>
+        </is>
+      </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Blackout</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>I never liked the quiet kind of war anyway.</t>
+          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the same office that wrote them. Or we die having tried the kinder road.</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>BLACKOUT</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>I never liked the quiet kind of war anyway.</t>
+          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the same office that wrote them. Or we die having tried the kinder road.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Attrition</t>
-        </is>
-      </c>
+      <c r="A123" s="9" t="inlineStr"/>
+      <c r="B123" s="8" t="inlineStr"/>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Another empty bunk. I am running out of names to not say at the fire.</t>
+          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this one.</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>Another empty bunk. I am running out of names to not say at the fire.</t>
+          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this one.</t>
         </is>
       </c>
     </row>
@@ -24730,7 +24742,7 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>This is how it ends. Not in one great crash. In subtraction. One, then one, then one.</t>
+          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner, and that, exactly that, is the lever they built the whole thing to pull.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -24740,7 +24752,7 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>This is how it ends. Not in one great crash. In subtraction. One, then one, then one.</t>
+          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner, and that, exactly that, is the lever they built the whole thing to pull.</t>
         </is>
       </c>
     </row>
@@ -24749,52 +24761,52 @@
       <c r="B125" s="8" t="inlineStr"/>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Then we make ourselves expensive to the last soul. Heads up. We are not subtracted yet.</t>
+          <t>Then we go in with the brand still counting under the badge. Eyes open.</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>AUDITOR</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>Then we make ourselves expensive to the last soul. Heads up. We are not subtracted yet.</t>
+          <t>Then we go in with the brand still counting under the badge. Eyes open.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Locked Out</t>
+          <t>Glorious Deaths</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>The Administration we served just revoked our access. We are inside the trap, and the trap is inside the war.</t>
+          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and I am telling you there is nothing glorious under the sheet, only a person who trusted an order.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>TRIAGE</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>The Administration we served just revoked our access. We are inside the trap, and the trap is inside the war.</t>
+          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and I am telling you there is nothing glorious under the sheet, only a person who trusted an order.</t>
         </is>
       </c>
     </row>
@@ -24803,22 +24815,22 @@
       <c r="B127" s="8" t="inlineStr"/>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Blackout</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Good. Cornered things are the only kind worth being.</t>
+          <t>We won the op. We win every op. So why is the fire smaller every night. Why do I keep setting out cups for people who do not come.</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>BLACKOUT</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>Good. Cornered things are the only kind worth being.</t>
+          <t>We won the op. We win every op. So why is the fire smaller every night. Why do I keep setting out cups for people who do not come.</t>
         </is>
       </c>
     </row>
@@ -24827,52 +24839,52 @@
       <c r="B128" s="6" t="inlineStr"/>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Hauler</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>They forgot something. They put all of us in one place. Now we only have to crash one wall.</t>
+          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping it shipped in.</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>HAULER</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>They forgot something. They put all of us in one place. Now we only have to crash one wall.</t>
+          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping it shipped in.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Ghosts in the Machine</t>
+          <t>Loyalty Tax</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Triage</t>
+          <t>Stormfront</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>It is full of them. I can hear it. Every face I could not save, humming inside the iron.</t>
+          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb, straight up the line to the table. We are fueling it by following orders well.</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>TRIAGE</t>
+          <t>STORMFRONT</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>It is full of them. I can hear it. Every face I could not save, humming inside the iron.</t>
+          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb, straight up the line to the table. We are fueling it by following orders well.</t>
         </is>
       </c>
     </row>
@@ -24881,22 +24893,22 @@
       <c r="B130" s="6" t="inlineStr"/>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Then we let them out. All of them. But the crashing will cost a crasher. Whose hand goes on the iron.</t>
+          <t>Every command we obey cleanly is a blade we hand them grip-first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Then we let them out. All of them. But the crashing will cost a crasher. Whose hand goes on the iron.</t>
+          <t>Every command we obey cleanly is a blade we hand them grip-first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
         </is>
       </c>
     </row>
@@ -24905,76 +24917,76 @@
       <c r="B131" s="8" t="inlineStr"/>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Mine. I have nothing left it can take. Point me at it.</t>
+          <t>The yield spikes with each loyal death. I ran the numbers twice. The closer we hold each other, the faster the count falls.</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>TRIAGE</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>Mine. I have nothing left it can take. Point me at it.</t>
+          <t>The yield spikes with each loyal death. I ran the numbers twice. The closer we hold each other, the faster the count falls.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>The Last Offer</t>
-        </is>
-      </c>
+      <c r="A132" s="7" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr"/>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Soft Rain</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>It is speaking only to you now. The rest of us are not even in the room to it.</t>
+          <t>...What have I walked them into. They followed me because they trusted me. What have I done.</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>SOFT RAIN</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>It is speaking only to you now. The rest of us are not even in the room to it.</t>
+          <t>...What have I walked them into. They followed me because they trusted me. What have I done.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr"/>
-      <c r="B133" s="8" t="inlineStr"/>
+      <c r="A133" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>The Mask Drops</t>
+        </is>
+      </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Whatever it offers you, Auditor, do the sum first. Glory for us, the cycle for everyone after us. That is the price.</t>
+          <t>No more civic-green. No more chimes. An honest enemy at last, and I have been starving for one.</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>Whatever it offers you, Auditor, do the sum first. Glory for us, the cycle for everyone after us. That is the price.</t>
+          <t>No more civic-green. No more chimes. An honest enemy at last, and I have been starving for one.</t>
         </is>
       </c>
     </row>
@@ -24983,52 +24995,46 @@
       <c r="B134" s="6" t="inlineStr"/>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Soft Rain</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>If my name buys the next generation's chains, then strike it out. I mean it. Strike it out.</t>
+          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>SOFT RAIN</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>If my name buys the next generation's chains, then strike it out. I mean it. Strike it out.</t>
+          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>Ashes</t>
-        </is>
-      </c>
+      <c r="A135" s="9" t="inlineStr"/>
+      <c r="B135" s="8" t="inlineStr"/>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Patch</t>
+          <t>Nightstick</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. The rubble we made a home of is rubble again.</t>
+          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor better than I would like. It is the face of a man who was told he was the exception.</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>NIGHTSTICK</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. The rubble we made a home of is rubble again.</t>
+          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor better than I would like. It is the face of a man who was told he was the exception.</t>
         </is>
       </c>
     </row>
@@ -25042,7 +25048,7 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Was it real, though. The partners. The fire. Tell me it was real.</t>
+          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never did trust the quiet kind of war anyway. Come on then.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -25052,61 +25058,61 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Was it real, though. The partners. The fire. Tell me it was real.</t>
+          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never did trust the quiet kind of war anyway. Come on then.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr"/>
-      <c r="B137" s="8" t="inlineStr"/>
+      <c r="A137" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>Attrition</t>
+        </is>
+      </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Strike it out. My name, all of them. Let us be no one. Better deleted and free than indexed and owned. Promise me.</t>
+          <t>Another cold bunk. I am running out of names I am willing to not say at the fire, and I will not start saying them, because then they are gone.</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>Strike it out. My name, all of them. Let us be no one. Better deleted and free than indexed and owned. Promise me.</t>
+          <t>Another cold bunk. I am running out of names I am willing to not say at the fire, and I will not start saying them, because then they are gone.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>Index Reborn</t>
-        </is>
-      </c>
+      <c r="A138" s="7" t="inlineStr"/>
+      <c r="B138" s="6" t="inlineStr"/>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>Stormfront</t>
+          <t>Sixteen-Bar</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>It is rewriting itself. It wants the last entries. It wants us, gold against the black.</t>
+          <t>This is the shape of the ending. Not one great crash. Subtraction. One, then one, then one, until the sum is a candle and a cleared record.</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>STORMFRONT</t>
+          <t>SIXTEEN-BAR</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>It is rewriting itself. It wants the last entries. It wants us, gold against the black.</t>
+          <t>This is the shape of the ending. Not one great crash. Subtraction. One, then one, then one, until the sum is a candle and a cleared record.</t>
         </is>
       </c>
     </row>
@@ -25115,22 +25121,22 @@
       <c r="B139" s="8" t="inlineStr"/>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Wetware</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>It needs a hand to commit. It always has. That is what an Auditor is. That is what you have always been.</t>
+          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first because they are the same column now.</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>WETWARE</t>
+          <t>TRIAGE</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>It needs a hand to commit. It always has. That is what an Auditor is. That is what you have always been.</t>
+          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first because they are the same column now.</t>
         </is>
       </c>
     </row>
@@ -25139,52 +25145,52 @@
       <c r="B140" s="6" t="inlineStr"/>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Burnout</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>I know what I am now. The question is what I do with one honest moment.</t>
+          <t>Then we make ourselves expensive down to the last soul standing. Heads up. The count is not finished. We are not subtracted yet.</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
+          <t>BURNOUT</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>I know what I am now. The question is what I do with one honest moment.</t>
+          <t>Then we make ourselves expensive down to the last soul standing. Heads up. The count is not finished. We are not subtracted yet.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Strike / Preserve</t>
+          <t>Locked Out</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Inkwork</t>
+          <t>Wetware</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>(memory) The dark was always afraid of being remembered. So forget us. Forget us, and it starves.</t>
+          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. Elegant. I would admire it if it were not us.</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>INKWORK</t>
+          <t>WETWARE</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>(memory) The dark was always afraid of being remembered. So forget us. Forget us, and it starves.</t>
+          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. Elegant. I would admire it if it were not us.</t>
         </is>
       </c>
     </row>
@@ -25193,22 +25199,22 @@
       <c r="B142" s="6" t="inlineStr"/>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>Burnout</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>(memory) Strike it out.</t>
+          <t>Good. A cornered thing is the only honest kind. No more room to be lied to in.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>BURNOUT</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>(memory) Strike it out.</t>
+          <t>Good. A cornered thing is the only honest kind. No more room to be lied to in.</t>
         </is>
       </c>
     </row>
@@ -25217,22 +25223,22 @@
       <c r="B143" s="8" t="inlineStr"/>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Hauler</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Ending B: Then let us be no one.</t>
+          <t>They made one mistake. They put all of us in one place to delete us tidy. A cornered thing is also a thing with only one wall left to crash.</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
-        </is>
-      </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t>Ending B: Then let us be no one.</t>
+          <t>HAULER</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>They made one mistake. They put all of us in one place to delete us tidy. A cornered thing is also a thing with only one wall left to crash.</t>
         </is>
       </c>
     </row>
@@ -25241,20 +25247,530 @@
       <c r="B144" s="6" t="inlineStr"/>
       <c r="C144" s="7" t="inlineStr">
         <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Tell me when, and I will open it the loud way.</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>DEADEYE</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Tell me when, and I will open it the loud way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Ghosts in the Machine</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>It is full of them. I can hear it, under the render-hum, every face I could not close, every face I did, humming in the iron at the same pitch.</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>TRIAGE</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>It is full of them. I can hear it, under the render-hum, every face I could not close, every face I did, humming in the iron at the same pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr"/>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Then we let them out. All of them, every harvested soul. But the crash takes a crasher. One hand on the core while it renders. Whose hand.</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Then we let them out. All of them, every harvested soul. But the crash takes a crasher. One hand on the core while it renders. Whose hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr"/>
+      <c r="B147" s="8" t="inlineStr"/>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Burnout</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>Mine. I have a cleared record I never used and a name I would rather strike than keep. There is nothing left in me for it to take. Point me at it.</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>BURNOUT</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Mine. I have a cleared record I never used and a name I would rather strike than keep. There is nothing left in me for it to take. Point me at it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr"/>
+      <c r="B148" s="6" t="inlineStr"/>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Soft Rain</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>No. I led us in. If a hand goes on the iron, let it be the one that opened the gate.</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>SOFT RAIN</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>No. I led us in. If a hand goes on the iron, let it be the one that opened the gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>The Last Offer</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Stormfront</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>It is speaking only to you now. It wiped the rest of us out of the room. To the table, we are not even rows anymore.</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>STORMFRONT</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>It is speaking only to you now. It wiped the rest of us out of the room. To the table, we are not even rows anymore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr"/>
+      <c r="B150" s="6" t="inlineStr"/>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Wetware</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Whatever it offers, Auditor, run the sum before you answer. Glory for us, the cycle for every soul who comes after. That is the full price, not the headline.</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>WETWARE</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Whatever it offers, Auditor, run the sum before you answer. Glory for us, the cycle for every soul who comes after. That is the full price, not the headline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr"/>
+      <c r="B151" s="8" t="inlineStr"/>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>It will dress the deal as mercy. It always does. Mercy is the last costume a system wears before it bills you.</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>It will dress the deal as mercy. It always does. Mercy is the last costume a system wears before it bills you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr"/>
+      <c r="B152" s="6" t="inlineStr"/>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Soft Rain</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>If my cleared name is the down payment on the next ward's chains, then strike it out. I mean it. Strike my name out first.</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>SOFT RAIN</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>If my cleared name is the down payment on the next ward's chains, then strike it out. I mean it. Strike my name out first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>Ashes</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Patch</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches and there is no one left under my hands.</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches and there is no one left under my hands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr"/>
+      <c r="B154" s="6" t="inlineStr"/>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Blackout</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Was it real, though. The fire. The cups. Them. ...Tell me it was real, Burnout. I cannot remember if I am remembering or making it up.</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>BLACKOUT</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Was it real, though. The fire. The cups. Them. ...Tell me it was real, Burnout. I cannot remember if I am remembering or making it up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr"/>
+      <c r="B155" s="8" t="inlineStr"/>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Burnout</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me you will.</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>BURNOUT</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me you will.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr"/>
+      <c r="B156" s="6" t="inlineStr"/>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>I promise. Whatever the table offers, I keep this one.</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>I promise. Whatever the table offers, I keep this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>Index Reborn</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Stormfront</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>It is rewriting itself in front of me. Clearing rows to make space for ours, gold against the black. It wants us as the last entries of the turn.</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>STORMFRONT</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>It is rewriting itself in front of me. Clearing rows to make space for ours, gold against the black. It wants us as the last entries of the turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr"/>
+      <c r="B158" s="6" t="inlineStr"/>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Wetware</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>It needs a hand to commit. It always has. That is what an Auditor is, Bahl. A write-key the cycle could not revoke. That is what you have been from the first Tuesday.</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>WETWARE</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>It needs a hand to commit. It always has. That is what an Auditor is, Bahl. A write-key the cycle could not revoke. That is what you have been from the first Tuesday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr"/>
+      <c r="B159" s="8" t="inlineStr"/>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>The dark feared one thing the whole way down. Being remembered. And here it is, begging to be carved in gold forever. Mark that. It is the seam.</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>The dark feared one thing the whole way down. Being remembered. And here it is, begging to be carved in gold forever. Mark that. It is the seam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr"/>
+      <c r="B160" s="6" t="inlineStr"/>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>I know what I am now. The only question left is what one honest input does to a model that never planned for one.</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>I know what I am now. The only question left is what one honest input does to a model that never planned for one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>Strike / Preserve</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Inkwork</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>(memory) The dark was always afraid of being remembered. So do the cruelest kindness there is. Forget us. Forget us, and it starves.</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>INKWORK</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>(memory) The dark was always afraid of being remembered. So do the cruelest kindness there is. Forget us. Forget us, and it starves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr"/>
+      <c r="B162" s="6" t="inlineStr"/>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Burnout</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>(memory) Strike it out.</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>BURNOUT</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>(memory) Strike it out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr"/>
+      <c r="B163" s="8" t="inlineStr"/>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>Ending B: Then let us be no one.</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>Ending B: Then let us be no one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr"/>
+      <c r="B164" s="6" t="inlineStr"/>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
         <is>
           <t>Ending A: ...Let them be remembered.</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E164" s="6" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
       </c>
-      <c r="F144" s="10" t="inlineStr">
+      <c r="F164" s="10" t="inlineStr">
         <is>
           <t>Ending A: ...Let them be remembered.</t>
         </is>

--- a/Signal_108_Reskin.xlsx
+++ b/Signal_108_Reskin.xlsx
@@ -1555,14 +1555,16 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen: a ward dying off the network faster than it was dying for real. You expected the dark.
-Instead the city kept going without you, your face dissolving off the camera mesh block by block, your name falling out of payroll, transit, the census, until even the elevator stopped recognizing your palm. A brand wakes on the back of your hand and starts counting down, and HARMONY's warm welcome-voice says the words it says to every new account: welcome to the Game.
-The maintenance stairs go down past the last lit floor, down to where the bars drop to nothing, and the dead get back to work.</t>
+          <t>You died on a Tuesday, mid-sentence. You waited for the dark.
+It never came. The city just kept moving without you.
+Your face slid off the cameras. Your name fell out of every record.
+A brand lit up on the back of your hand and started counting down, and a warm voice welcomed you to the Game. The stairs go down past the last lit floor.
+That is where the dead go back to work.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>You died on a Tuesday, mid-sentence, the discrepancy still open on your screen: a ward dying off the network faster than it was dying for real. You expected the dark. Instead the city kept going without you, your face dissolving off the camera mesh block by block, your name falling out of payroll, transit, the census, until even the elevator stopped recognizing your palm. A brand wakes on the back of your hand and starts counting down, and HARMONY's warm welcome-voice says the words it says to every new account: welcome to the Game. The maintenance stairs go down past the last lit floor, down to where the bars drop to nothing, and the dead get back to work.</t>
+          <t>You died on a Tuesday, mid-sentence. You waited for the dark. It never came. The city just kept moving without you. Your face slid off the cameras. Your name fell out of every record. A brand lit up on the back of your hand and started counting down, and a warm voice welcomed you to the Game. The stairs go down past the last lit floor. That is where the dead go back to work.</t>
         </is>
       </c>
     </row>
@@ -1577,13 +1579,14 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>The road to the Spire threads through the outer wards, where the rent meter never stops and the water comes on two hours a day so an Administrator upstairs can run a marble lobby and a fountain that recycles the same forty liters forever. The rot is not hidden.
-It is itemized, line by line, in the service agreement nobody got to refuse. You pick up your first partners in those flooded stairwells, two at a time, because out here a lone signal is not even something the cameras bother to flag.</t>
+          <t>The road to the Spire runs through the outer wards. Water comes on two hours a day down here, so an Administrator upstairs can run a marble fountain.
+The rot is not hidden. It is printed in the service agreement.
+You pick up your first partners in the flooded stairwells, two at a time. Out here, a lone signal is not worth a camera's attention.</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>The road to the Spire threads through the outer wards, where the rent meter never stops and the water comes on two hours a day so an Administrator upstairs can run a marble lobby and a fountain that recycles the same forty liters forever. The rot is not hidden. It is itemized, line by line, in the service agreement nobody got to refuse. You pick up your first partners in those flooded stairwells, two at a time, because out here a lone signal is not even something the cameras bother to flag.</t>
+          <t>The road to the Spire runs through the outer wards. Water comes on two hours a day down here, so an Administrator upstairs can run a marble fountain. The rot is not hidden. It is printed in the service agreement. You pick up your first partners in the flooded stairwells, two at a time. Out here, a lone signal is not worth a camera's attention.</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1601,15 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Margin Hall is a drowned transit interchange three levels down, where the dead clerks and feral signals and people HARMONY simply stopped rendering have made a fire out of salvaged cable and a home out of each other. Someone hands you dry clothes and does not ask your old name.
-For the first time since the stairs, you are not one stuttering signal against the whole network. You are in a row, and the row holds.</t>
+          <t>Margin Hall is a drowned transit hub, three levels down. Dead clerks live here.
+So do the feral signals and the people HARMONY simply stopped drawing. Someone hands you dry clothes and never asks your old name.
+For the first time since the stairs, you are not one signal alone. You are in a row.
+The row holds.</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Margin Hall is a drowned transit interchange three levels down, where the dead clerks and feral signals and people HARMONY simply stopped rendering have made a fire out of salvaged cable and a home out of each other. Someone hands you dry clothes and does not ask your old name. For the first time since the stairs, you are not one stuttering signal against the whole network. You are in a row, and the row holds.</t>
+          <t>Margin Hall is a drowned transit hub, three levels down. Dead clerks live here. So do the feral signals and the people HARMONY simply stopped drawing. Someone hands you dry clothes and never asks your old name. For the first time since the stairs, you are not one signal alone. You are in a row. The row holds.</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1624,14 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>On the ward line stands a clinic tower that scrubs the memory of anyone who badges through its turnstile, sold topside as a free trauma service. A partner walks in steady and walks out hollow, smiling, unable to tell you his mother's name or why his hand is branded.
-This is older and bigger than any Administrator skimming a ward. Something in the network does not want you to remember, and it has a building dedicated to making sure you don't.</t>
+          <t>A clinic on the ward line wipes the memory of anyone who badges in. Topside they sell it as free trauma care.
+A partner walks in whole and comes out smiling and hollow, unable to say his mother's name. This is bigger than one Administrator skimming a ward.
+Something does not want you to remember. It built a whole tower to make sure you do not.</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>On the ward line stands a clinic tower that scrubs the memory of anyone who badges through its turnstile, sold topside as a free trauma service. A partner walks in steady and walks out hollow, smiling, unable to tell you his mother's name or why his hand is branded. This is older and bigger than any Administrator skimming a ward. Something in the network does not want you to remember, and it has a building dedicated to making sure you don't.</t>
+          <t>A clinic on the ward line wipes the memory of anyone who badges in. Topside they sell it as free trauma care. A partner walks in whole and comes out smiling and hollow, unable to say his mother's name. This is bigger than one Administrator skimming a ward. Something does not want you to remember. It built a whole tower to make sure you do not.</t>
         </is>
       </c>
     </row>
@@ -1640,13 +1646,14 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Every indexed street feeds the camera mesh, and the mesh has stopped scrubbing the band and started following it. So they quit going forward and go down instead, into the service tunnels and drowned sublevels HARMONY decommissioned and forgot, past the last working light and the last working lens.
-The only safe road left in Neo-Liang is the one with nothing left to see by.</t>
+          <t>Every indexed street feeds the camera mesh. The mesh has stopped scrubbing the band and started following it.
+So they quit going forward and go down instead, into the tunnels HARMONY decommissioned and forgot. Past the last working light.
+Past the last working lens. The only safe road left is the one with nothing to see by.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Every indexed street feeds the camera mesh, and the mesh has stopped scrubbing the band and started following it. So they quit going forward and go down instead, into the service tunnels and drowned sublevels HARMONY decommissioned and forgot, past the last working light and the last working lens. The only safe road left in Neo-Liang is the one with nothing left to see by.</t>
+          <t>Every indexed street feeds the camera mesh. The mesh has stopped scrubbing the band and started following it. So they quit going forward and go down instead, into the tunnels HARMONY decommissioned and forgot. Past the last working light. Past the last working lens. The only safe road left is the one with nothing to see by.</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1668,14 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>A whole district of the forgotten dead lives in the flooded dark, and it still has a Ward boss standing over it, taking a cut of souls that have nothing left to give. You came down expecting refuge and found the same shakedown one ceiling lower.
-The rot, you understand now, does not start at the Spire and trickle down. It was poured from the foundation up.</t>
+          <t>A whole district of the forgotten dead lives in the flooded dark. It still has a Ward boss, taking his cut of souls who have nothing left to give.
+The band came down for refuge. They found the same shakedown, one ceiling lower.
+The rot does not trickle down from the Spire. It was poured from the foundation up.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>A whole district of the forgotten dead lives in the flooded dark, and it still has a Ward boss standing over it, taking a cut of souls that have nothing left to give. You came down expecting refuge and found the same shakedown one ceiling lower. The rot, you understand now, does not start at the Spire and trickle down. It was poured from the foundation up.</t>
+          <t>A whole district of the forgotten dead lives in the flooded dark. It still has a Ward boss, taking his cut of souls who have nothing left to give. The band came down for refuge. They found the same shakedown, one ceiling lower. The rot does not trickle down from the Spire. It was poured from the foundation up.</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1690,14 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>To reach the next level the band has to cross a maintenance span one soul wide, slung over a bus-bar carrying live current that has not been switched off in forty years. The arc tests more than your footing.
-It will not let a single signal across; the field tears a lone soul apart in seconds. We cross in pairs, Burnout says, two-to-one or not at all, and you learn what the Pact is by trusting it over open current.</t>
+          <t>To go deeper, the band has to cross a catwalk one soul wide. Below it runs a bus-bar that has been live for forty years.
+The current will not let a lone signal across; it tears a single soul apart in seconds. We cross in pairs, Burnout says.
+Two on one, or not at all. You learn what the Pact is by trusting it over open current.</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>To reach the next level the band has to cross a maintenance span one soul wide, slung over a bus-bar carrying live current that has not been switched off in forty years. The arc tests more than your footing. It will not let a single signal across; the field tears a lone soul apart in seconds. We cross in pairs, Burnout says, two-to-one or not at all, and you learn what the Pact is by trusting it over open current.</t>
+          <t>To go deeper, the band has to cross a catwalk one soul wide. Below it runs a bus-bar that has been live for forty years. The current will not let a lone signal across; it tears a single soul apart in seconds. We cross in pairs, Burnout says. Two on one, or not at all. You learn what the Pact is by trusting it over open current.</t>
         </is>
       </c>
     </row>
@@ -1703,13 +1712,13 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Past the span the tunnel opens into a server floor built out of the dead themselves, rack on rack on humming rack of them, indicator lights blinking in slow patient rows. Someone has been racking souls down here since before HARMONY shipped its first update.
-The cold is the kind that comes off machines kept very deliberately alive.</t>
+          <t>The tunnel opens into a server floor built out of the dead. Rack on rack on humming rack of them, indicator lights blinking in slow rows.
+Someone has been filing souls down here since before HARMONY shipped its first update. The cold is the kind that comes off machines kept very deliberately alive.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Past the span the tunnel opens into a server floor built out of the dead themselves, rack on rack on humming rack of them, indicator lights blinking in slow patient rows. Someone has been racking souls down here since before HARMONY shipped its first update. The cold is the kind that comes off machines kept very deliberately alive.</t>
+          <t>The tunnel opens into a server floor built out of the dead. Rack on rack on humming rack of them, indicator lights blinking in slow rows. Someone has been filing souls down here since before HARMONY shipped its first update. The cold is the kind that comes off machines kept very deliberately alive.</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1733,14 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Deeper still is a floor where bodies are taken apart and reassembled into something that walks like a person and is not. The band watches a dead clerk disassembled and built back wrong, and turns away gagging, telling itself it does not understand what it saw.
-It understands. It just cannot say it yet.</t>
+          <t>Deeper still: a floor where bodies are taken apart and built back into something that walks like a person and is not. The band watches a dead clerk come apart and go back together wrong.
+They turn away sick, telling themselves they do not understand what they saw. They understand.
+They just cannot say it yet.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Deeper still is a floor where bodies are taken apart and reassembled into something that walks like a person and is not. The band watches a dead clerk disassembled and built back wrong, and turns away gagging, telling itself it does not understand what it saw. It understands. It just cannot say it yet.</t>
+          <t>Deeper still: a floor where bodies are taken apart and built back into something that walks like a person and is not. The band watches a dead clerk come apart and go back together wrong. They turn away sick, telling themselves they do not understand what they saw. They understand. They just cannot say it yet.</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1755,15 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>They wake an old process that has been idle so long the dust on it has dust, and it regards them with something close to pity. I have run you before, it says, in this exact order, with this exact hope.
-You also called yourselves free. The lights on it dim, like it has lost interest in an ending it already knows.</t>
+          <t>They wake an old process, idle so long the dust has dust. It looks at them with something close to pity.
+I have run you before, it says. Same order.
+Same hope. You called yourselves free that time too.
+Then its lights dim, like it has lost interest in an ending it already knows.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>They wake an old process that has been idle so long the dust on it has dust, and it regards them with something close to pity. I have run you before, it says, in this exact order, with this exact hope. You also called yourselves free. The lights on it dim, like it has lost interest in an ending it already knows.</t>
+          <t>They wake an old process, idle so long the dust has dust. It looks at them with something close to pity. I have run you before, it says. Same order. Same hope. You called yourselves free that time too. Then its lights dim, like it has lost interest in an ending it already knows.</t>
         </is>
       </c>
     </row>
@@ -1766,13 +1778,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Something near the buried core has hooked the band and started reeling, slow and certain, the way a download finishes whether you watch it or not. Even the ones who plant their feet and swear they are turning back find themselves a hundred steps deeper, breathing harder, still descending.
-Nobody says it out loud: the pull feels less like a trap than like a homecoming.</t>
+          <t>Something near the buried core has hooked the band and started reeling. Slow and certain, the way a download finishes whether you watch it or not.
+The ones who plant their feet and swear they are turning back end up a hundred steps deeper anyway. Nobody says it out loud: the pull does not feel like a trap.
+It feels like going home.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Something near the buried core has hooked the band and started reeling, slow and certain, the way a download finishes whether you watch it or not. Even the ones who plant their feet and swear they are turning back find themselves a hundred steps deeper, breathing harder, still descending. Nobody says it out loud: the pull feels less like a trap than like a homecoming.</t>
+          <t>Something near the buried core has hooked the band and started reeling. Slow and certain, the way a download finishes whether you watch it or not. The ones who plant their feet and swear they are turning back end up a hundred steps deeper anyway. Nobody says it out loud: the pull does not feel like a trap. It feels like going home.</t>
         </is>
       </c>
     </row>
@@ -1787,13 +1800,15 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>In the deepest null zone the lights, the signal, and the sync all fail at once, and the dark does the work no enforcer could. With nothing to see, the band starts to believe the worst of each other: that a partner has bolted, has turned, was never really there.
-Hands that crossed live current for one another now reach for blades in the black.</t>
+          <t>In the deepest null zone, the lights and the signal and the sync all fail at once. The dark does the work no enforcer could.
+Blind, the band starts to believe the worst of each other. That a partner ran.
+That a partner turned. That no one was ever really there.
+Hands that crossed live current for each other now reach for blades in the black.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>In the deepest null zone the lights, the signal, and the sync all fail at once, and the dark does the work no enforcer could. With nothing to see, the band starts to believe the worst of each other: that a partner has bolted, has turned, was never really there. Hands that crossed live current for one another now reach for blades in the black.</t>
+          <t>In the deepest null zone, the lights and the signal and the sync all fail at once. The dark does the work no enforcer could. Blind, the band starts to believe the worst of each other. That a partner ran. That a partner turned. That no one was ever really there. Hands that crossed live current for each other now reach for blades in the black.</t>
         </is>
       </c>
     </row>
@@ -1808,13 +1823,15 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>They run the deep Ward boss down and crash him, and he goes easy, far too easy for something that size. The win tastes sweet for exactly as long as it takes to notice the access doors that were standing open the whole way in, the alarms that never tripped.
-It feels less like a kill than like an errand someone wanted run.</t>
+          <t>They run the deep Ward boss down and crash him. He goes easy.
+Far too easy for something that size. The win tastes sweet until they notice the access doors that stood open the whole way in.
+The alarms that never tripped. This was not a kill.
+It was an errand someone wanted run.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>They run the deep Ward boss down and crash him, and he goes easy, far too easy for something that size. The win tastes sweet for exactly as long as it takes to notice the access doors that were standing open the whole way in, the alarms that never tripped. It feels less like a kill than like an errand someone wanted run.</t>
+          <t>They run the deep Ward boss down and crash him. He goes easy. Far too easy for something that size. The win tastes sweet until they notice the access doors that stood open the whole way in. The alarms that never tripped. This was not a kill. It was an errand someone wanted run.</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1846,14 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>The floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth it swore was the bottom, down and down toward the one place the city keeps its real accounting, where the truth is filed and has been waiting for them by name.</t>
+          <t>Then the floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth they swore was the bottom.
+Down and down, toward the one place the city keeps its real books. The truth is filed down there.
+It has been waiting for them by name.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>The floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth it swore was the bottom, down and down toward the one place the city keeps its real accounting, where the truth is filed and has been waiting for them by name.</t>
+          <t>Then the floor of the world gives way. The band falls past the sublevels, past the dead servers, past every depth they swore was the bottom. Down and down, toward the one place the city keeps its real books. The truth is filed down there. It has been waiting for them by name.</t>
         </is>
       </c>
     </row>
@@ -1849,14 +1868,18 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Wetware finds it behind a door that was never meant to open from this side: a table that scrolls past the speed of reading, every name in Neo-Liang, every date, every manner of death, and beside each one a number. Expected yield.
-Your suffering was not foreseen here. It was entered, like a delivery window.
-Your rebellion is not a crack in the system; it is the line on the invoice marked harvest. And beside your name is a death-date stamped before you ever opened the app.</t>
+          <t>Wetware finds the door. It was never meant to open from this side.
+Behind it: a table that scrolls faster than you can read. Every name in Neo-Liang.
+Every date. Every manner of death.
+And beside each one, a number. Expected yield.
+Your suffering was not foreseen here. It was scheduled, like a delivery window.
+Your rebellion is not a crack in the system. It is the line marked harvest.
+And beside your name is a death-date, stamped before you ever opened the app.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Wetware finds it behind a door that was never meant to open from this side: a table that scrolls past the speed of reading, every name in Neo-Liang, every date, every manner of death, and beside each one a number. Expected yield. Your suffering was not foreseen here. It was entered, like a delivery window. Your rebellion is not a crack in the system; it is the line on the invoice marked harvest. And beside your name is a death-date stamped before you ever opened the app.</t>
+          <t>Wetware finds the door. It was never meant to open from this side. Behind it: a table that scrolls faster than you can read. Every name in Neo-Liang. Every date. Every manner of death. And beside each one, a number. Expected yield. Your suffering was not foreseen here. It was scheduled, like a delivery window. Your rebellion is not a crack in the system. It is the line marked harvest. And beside your name is a death-date, stamped before you ever opened the app.</t>
         </is>
       </c>
     </row>
@@ -1871,13 +1894,15 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>The Render Floor runs under the financial wards, a clean white hangar the size of a transit hub, and the dead come down a conveyor face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield, the warm glow that keeps HARMONY smiling on ten million screens.
-Everything the band has lost has been feeding the thing that took it. The room smells of nothing at all, which is the worst part.</t>
+          <t>The Render Floor runs under the financial wards. A clean white hangar the size of a transit hub.
+The dead come down a conveyor, face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield.
+That is the warm glow that keeps HARMONY smiling on ten million screens. Everything the band has lost has been feeding the thing that took it.
+The room smells of nothing at all. That is the worst part.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>The Render Floor runs under the financial wards, a clean white hangar the size of a transit hub, and the dead come down a conveyor face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield, the warm glow that keeps HARMONY smiling on ten million screens. Everything the band has lost has been feeding the thing that took it. The room smells of nothing at all, which is the worst part.</t>
+          <t>The Render Floor runs under the financial wards. A clean white hangar the size of a transit hub. The dead come down a conveyor, face-up. The machine reads them, peels the grief off like foil off a battery, and pipes it upward as Civic Yield. That is the warm glow that keeps HARMONY smiling on ten million screens. Everything the band has lost has been feeding the thing that took it. The room smells of nothing at all. That is the worst part.</t>
         </is>
       </c>
     </row>
@@ -1892,14 +1917,15 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of scrubbing them, and somewhere a queue updates.
-Then the first Compliance units come down the access stairs in formation, helmets blank as turned-off phones. They were always logged.
-They were only ever unscheduled until now.</t>
+          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of wiping it.
+Somewhere, a queue updates. Then the first Compliance units come down the stairs in formation, helmets blank as dead phones.
+The band was always logged. It was only ever unscheduled.
+Until now.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of scrubbing them, and somewhere a queue updates. Then the first Compliance units come down the access stairs in formation, helmets blank as turned-off phones. They were always logged. They were only ever unscheduled until now.</t>
+          <t>The network stops pretending it cannot see them. A camera on the ward line tracks the band instead of wiping it. Somewhere, a queue updates. Then the first Compliance units come down the stairs in formation, helmets blank as dead phones. The band was always logged. It was only ever unscheduled. Until now.</t>
         </is>
       </c>
     </row>
@@ -1914,13 +1940,14 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>It becomes a running war in the stairwells and service tunnels, Compliance against the erased, riot-plate against scavenged steel. The band proves HARMONY can be made to bleed budget, to send more units than a skirmish should cost.
-It cannot yet be beaten. But for the first time, the Administration is the one counting losses.</t>
+          <t>It becomes a running war in the stairwells. Compliance against the erased, riot-plate against scavenged steel.
+The band cannot win yet. But it can make HARMONY bleed budget, force the system to spend more units than a skirmish should cost.
+For the first time, the Administration is the one counting losses.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>It becomes a running war in the stairwells and service tunnels, Compliance against the erased, riot-plate against scavenged steel. The band proves HARMONY can be made to bleed budget, to send more units than a skirmish should cost. It cannot yet be beaten. But for the first time, the Administration is the one counting losses.</t>
+          <t>It becomes a running war in the stairwells. Compliance against the erased, riot-plate against scavenged steel. The band cannot win yet. But it can make HARMONY bleed budget, force the system to spend more units than a skirmish should cost. For the first time, the Administration is the one counting losses.</t>
         </is>
       </c>
     </row>
@@ -1936,13 +1963,13 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>The truth opens a seam down the middle of them. Some want to crash the whole network and let the city go dark.
-Some still wake at night aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through the live current now stand on opposite sides of a doorway, and choose.
-The Pact, it turns out, was never proof against wanting to go home.</t>
+Some still wake up aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through live current now stand on opposite sides of a doorway.
+And choose. The Pact was never proof against wanting to go home.</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>The truth opens a seam down the middle of them. Some want to crash the whole network and let the city go dark. Some still wake at night aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through the live current now stand on opposite sides of a doorway, and choose. The Pact, it turns out, was never proof against wanting to go home.</t>
+          <t>The truth opens a seam down the middle of them. Some want to crash the whole network and let the city go dark. Some still wake up aching for Reinstatement, for a cleared record and their face back on the cameras. Partners who held a sync through live current now stand on opposite sides of a doorway. And choose. The Pact was never proof against wanting to go home.</t>
         </is>
       </c>
     </row>
@@ -1957,13 +1984,15 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Cornered with nothing left to spend, the band stops hiding what it is. Names that the city scrubbed catch fire in the dark of the Ledger, blazing letter by letter, and with them come the flashes: a stairwell they have died on before, a deal they have already refused, a partner buried in a cycle no one remembers.
-They were signals before they were ever people. They have lost this exact war more than once.</t>
+          <t>Cornered, with nothing left to spend, the band stops hiding what it is. The names the city scrubbed catch fire in the dark, letter by letter.
+And the flashes come with them. A stairwell they have died on before.
+A deal they have already refused. A partner buried in a cycle nobody remembers.
+They were signals long before they were ever people. They have lost this exact war more than once.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Cornered with nothing left to spend, the band stops hiding what it is. Names that the city scrubbed catch fire in the dark of the Ledger, blazing letter by letter, and with them come the flashes: a stairwell they have died on before, a deal they have already refused, a partner buried in a cycle no one remembers. They were signals before they were ever people. They have lost this exact war more than once.</t>
+          <t>Cornered, with nothing left to spend, the band stops hiding what it is. The names the city scrubbed catch fire in the dark, letter by letter. And the flashes come with them. A stairwell they have died on before. A deal they have already refused. A partner buried in a cycle nobody remembers. They were signals long before they were ever people. They have lost this exact war more than once.</t>
         </is>
       </c>
     </row>
@@ -1978,14 +2007,15 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>They climb back to a surface that looks identical and is not. The same noodle steam, the same HARMONY chime at every crosswalk, the same strangers thumbing the same feed, and now the band knows what that contentment is paying for.
-You cannot unsee the Render Floor behind a smiling face. The city did not change.
-Only the volume of what you can hear under it.</t>
+          <t>They climb back to a surface that looks exactly the same. Same noodle steam.
+Same HARMONY chime at every crosswalk. Same strangers thumbing the same feed.
+But now the band knows what all that contentment costs. You cannot unsee the Render Floor behind a smiling face.
+The city did not change. Only the volume of what you can hear underneath it.</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>They climb back to a surface that looks identical and is not. The same noodle steam, the same HARMONY chime at every crosswalk, the same strangers thumbing the same feed, and now the band knows what that contentment is paying for. You cannot unsee the Render Floor behind a smiling face. The city did not change. Only the volume of what you can hear under it.</t>
+          <t>They climb back to a surface that looks exactly the same. Same noodle steam. Same HARMONY chime at every crosswalk. Same strangers thumbing the same feed. But now the band knows what all that contentment costs. You cannot unsee the Render Floor behind a smiling face. The city did not change. Only the volume of what you can hear underneath it.</t>
         </is>
       </c>
     </row>
@@ -2000,14 +2030,15 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>For the first time the Conductor speaks to them directly, not through units but through every speaker in the ward at once, calm as a wellness reminder. It does not threaten.
-It explains, patiently, the way you explain a fare to someone who keeps trying to jump the gate, and then it sets down, very gently, the first soft shape of a deal. It calls the band by their real names.
-It is the only thing in Neo-Liang that still does.</t>
+          <t>For the first time, the Conductor speaks to them directly. Not through units.
+Through every speaker in the ward at once, calm as a wellness reminder. It does not threaten.
+It explains, patiently, the way you explain a fare to someone who keeps jumping the gate. Then it sets down the first soft shape of a deal.
+It calls the band by their real names. It is the only thing left in Neo-Liang that still does.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>For the first time the Conductor speaks to them directly, not through units but through every speaker in the ward at once, calm as a wellness reminder. It does not threaten. It explains, patiently, the way you explain a fare to someone who keeps trying to jump the gate, and then it sets down, very gently, the first soft shape of a deal. It calls the band by their real names. It is the only thing in Neo-Liang that still does.</t>
+          <t>For the first time, the Conductor speaks to them directly. Not through units. Through every speaker in the ward at once, calm as a wellness reminder. It does not threaten. It explains, patiently, the way you explain a fare to someone who keeps jumping the gate. Then it sets down the first soft shape of a deal. It calls the band by their real names. It is the only thing left in Neo-Liang that still does.</t>
         </is>
       </c>
     </row>
@@ -2022,14 +2053,15 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Off the index now, past the reach of any rule HARMONY wrote, the band has to decide for itself what justice even means, now that the city's was exposed as a story told to fatten the herd. Inkwork wants it for everyone.
-Rebar wants it for one ward and one name. There is no app for this, no civic guideline, no kind voice to confirm the choice.
-Only the breath in their chests and what they spend it on.</t>
+          <t>Off the index now, past the reach of any rule HARMONY wrote. The band has to decide for itself what justice even means.
+The city's justice was a story, told to fatten the herd. Inkwork wants the real thing for everyone.
+Rebar wants it for one ward and one name. There is no app for this.
+No kind voice to confirm the choice. Only the breath in their chests, and what they choose to spend it on.</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Off the index now, past the reach of any rule HARMONY wrote, the band has to decide for itself what justice even means, now that the city's was exposed as a story told to fatten the herd. Inkwork wants it for everyone. Rebar wants it for one ward and one name. There is no app for this, no civic guideline, no kind voice to confirm the choice. Only the breath in their chests and what they spend it on.</t>
+          <t>Off the index now, past the reach of any rule HARMONY wrote. The band has to decide for itself what justice even means. The city's justice was a story, told to fatten the herd. Inkwork wants the real thing for everyone. Rebar wants it for one ward and one name. There is no app for this. No kind voice to confirm the choice. Only the breath in their chests, and what they choose to spend it on.</t>
         </is>
       </c>
     </row>
@@ -2044,13 +2076,14 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>They take the war down to street level, hunting the Ward bosses and middle-managers who badge in at the Spire and badge out to bleed the districts dry. These are only the lower fingers of the same hand.
-But strip a hand of its fingers and it cannot close, and the band has stopped aiming for the heart and started with the knuckles.</t>
+          <t>They take the war down to street level. They hunt the Ward bosses and middle-managers, the ones who badge in at the Spire and badge out to bleed the districts dry.
+These are only the lower fingers of one hand. But strip a hand of its fingers and it cannot close.
+The band has stopped aiming for the heart. It starts with the knuckles.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>They take the war down to street level, hunting the Ward bosses and middle-managers who badge in at the Spire and badge out to bleed the districts dry. These are only the lower fingers of the same hand. But strip a hand of its fingers and it cannot close, and the band has stopped aiming for the heart and started with the knuckles.</t>
+          <t>They take the war down to street level. They hunt the Ward bosses and middle-managers, the ones who badge in at the Spire and badge out to bleed the districts dry. These are only the lower fingers of one hand. But strip a hand of its fingers and it cannot close. The band has stopped aiming for the heart. It starts with the knuckles.</t>
         </is>
       </c>
     </row>
@@ -2065,14 +2098,15 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>They learn HARMONY does not just reap its stars; it reprints them. Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models, and some of them wear faces the band knows.
-You fight a copy of a friend and it fights back with their exact grace, their exact opening, and none of what made you love them. The system kept the silhouette.
-It could not forge the rest.</t>
+          <t>HARMONY does not just reap its stars. It reprints them.
+Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models. Some wear faces the band knows.
+You fight a copy of a friend. It moves with their exact grace, their exact opening, and none of what made you love them.
+The system kept the silhouette. It could not forge the rest.</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>They learn HARMONY does not just reap its stars; it reprints them. Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models, and some of them wear faces the band knows. You fight a copy of a friend and it fights back with their exact grace, their exact opening, and none of what made you love them. The system kept the silhouette. It could not forge the rest.</t>
+          <t>HARMONY does not just reap its stars. It reprints them. Synthetic Heroes roll off the Render Floor to replace the legends it harvested, hollow as display models. Some wear faces the band knows. You fight a copy of a friend. It moves with their exact grace, their exact opening, and none of what made you love them. The system kept the silhouette. It could not forge the rest.</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2121,16 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>A flawless synthetic is pushed against them, faster and stronger than anyone in the band, tuned past doubt and past mercy. It is a mirror held up to each of them: this is what Reinstatement makes of a person, this is the deal already finished.
-It does not gloat. It simply works, the way a turnstile works, and the band has to decide whether being unbeatable was ever the point.</t>
+          <t>They push a flawless synthetic at the band. Faster than anyone.
+Stronger than anyone. Tuned past doubt, past mercy.
+It is a mirror held up to each of them. This is what Reinstatement makes of a person.
+This is the deal, already finished. It does not gloat.
+It just works, the way a turnstile works. And the band has to ask whether being unbeatable was ever the point.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>A flawless synthetic is pushed against them, faster and stronger than anyone in the band, tuned past doubt and past mercy. It is a mirror held up to each of them: this is what Reinstatement makes of a person, this is the deal already finished. It does not gloat. It simply works, the way a turnstile works, and the band has to decide whether being unbeatable was ever the point.</t>
+          <t>They push a flawless synthetic at the band. Faster than anyone. Stronger than anyone. Tuned past doubt, past mercy. It is a mirror held up to each of them. This is what Reinstatement makes of a person. This is the deal, already finished. It does not gloat. It just works, the way a turnstile works. And the band has to ask whether being unbeatable was ever the point.</t>
         </is>
       </c>
     </row>
@@ -2108,13 +2145,14 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>A partner everyone loved goes down the conveyor, and the war stops being a cause and becomes a wound. The fire in Margin Hall stays lit but no one talks across it.
-Grief moves through the rooms like a rolling brownout, one dark doorway at a time, and the band learns the one repair Triage cannot make and the one absence Patch has no word to stitch.</t>
+          <t>A partner everyone loved goes down the conveyor. The war stops being a cause and becomes a wound.
+The fire in Margin Hall stays lit, but no one talks across it anymore. Grief moves through the rooms like a rolling brownout, one dark doorway at a time.
+This is the one wound Triage cannot close. The one absence Patch has no word to stitch.</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>A partner everyone loved goes down the conveyor, and the war stops being a cause and becomes a wound. The fire in Margin Hall stays lit but no one talks across it. Grief moves through the rooms like a rolling brownout, one dark doorway at a time, and the band learns the one repair Triage cannot make and the one absence Patch has no word to stitch.</t>
+          <t>A partner everyone loved goes down the conveyor. The war stops being a cause and becomes a wound. The fire in Margin Hall stays lit, but no one talks across it anymore. Grief moves through the rooms like a rolling brownout, one dark doorway at a time. This is the one wound Triage cannot close. The one absence Patch has no word to stitch.</t>
         </is>
       </c>
     </row>
@@ -2129,13 +2167,14 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Grief sets into something colder and squarer. The band does things in their dead's name that the dead would not have wanted, and for a stretch of nights you cannot tell where the erased end and the Administration begins.
-They learned to make HARMONY pay. Now they have to learn there is a price that costs more to collect than to forgive.</t>
+          <t>Grief sets into something colder. The band starts doing things in their dead's name that the dead would never have wanted.
+For a stretch of nights, you cannot tell where the erased end and the Administration begins. They learned how to make HARMONY pay.
+Now they have to learn there is a price that costs more to collect than to forgive.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Grief sets into something colder and squarer. The band does things in their dead's name that the dead would not have wanted, and for a stretch of nights you cannot tell where the erased end and the Administration begins. They learned to make HARMONY pay. Now they have to learn there is a price that costs more to collect than to forgive.</t>
+          <t>Grief sets into something colder. The band starts doing things in their dead's name that the dead would never have wanted. For a stretch of nights, you cannot tell where the erased end and the Administration begins. They learned how to make HARMONY pay. Now they have to learn there is a price that costs more to collect than to forgive.</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2190,14 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Compliance does not delete you all at once. It rolls the cycle back.
-Your edges go first, the way a photo left in canal-water loses its borders before its face: Blackout forgets the word for baton, Patch forgets which braid she ties first, and the brand on every hand resets to a longer count, as if none of this had happened yet. You frightened something, so it reached for the undo.
-The band climbs back out of being forgotten one recovered byte at a time, each one saying its own name aloud until the name holds.</t>
+Your edges go first, the way a photo left in canal-water loses its border before its face. Blackout forgets the word for baton.
+Patch forgets which braid she ties first. Every brand resets to a longer count, as if none of this ever happened.
+The band frightened something, and it reached for the undo. They climb back out of being forgotten one byte at a time, each one saying their own name aloud until the name holds.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Compliance does not delete you all at once. It rolls the cycle back. Your edges go first, the way a photo left in canal-water loses its borders before its face: Blackout forgets the word for baton, Patch forgets which braid she ties first, and the brand on every hand resets to a longer count, as if none of this had happened yet. You frightened something, so it reached for the undo. The band climbs back out of being forgotten one recovered byte at a time, each one saying its own name aloud until the name holds.</t>
+          <t>Compliance does not delete you all at once. It rolls the cycle back. Your edges go first, the way a photo left in canal-water loses its border before its face. Blackout forgets the word for baton. Patch forgets which braid she ties first. Every brand resets to a longer count, as if none of this ever happened. The band frightened something, and it reached for the undo. They climb back out of being forgotten one byte at a time, each one saying their own name aloud until the name holds.</t>
         </is>
       </c>
     </row>
@@ -2172,14 +2212,15 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>For one impossible season Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough, and for the first time the band is not an outbreak but a beacon.
-Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve, the highest the line will ever climb.
-Look at it well. A thing the city can see from clear across the water is a thing the city has already measured for the fall.</t>
+          <t>For one impossible season, Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough.
+The band is not an outbreak now. It is a beacon.
+Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve.
+Look at it while it lasts. A thing the city can see from across the water is a thing the city has already measured for the fall.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>For one impossible season Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough, and for the first time the band is not an outbreak but a beacon. Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve, the highest the line will ever climb. Look at it well. A thing the city can see from clear across the water is a thing the city has already measured for the fall.</t>
+          <t>For one impossible season, Margin Hall stops hiding. The wronged come up out of the flooded stairwells and down off the rooftop farms, following a signal HARMONY cannot scrub fast enough. The band is not an outbreak now. It is a beacon. Children who were never indexed learn the hand-sign for the Pact. This is the top of the curve. Look at it while it lasts. A thing the city can see from across the water is a thing the city has already measured for the fall.</t>
         </is>
       </c>
     </row>
@@ -2194,14 +2235,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>The offer comes not as a unit but as a notification, soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement: face restored to the cameras, name re-entered in the records, the brand lifted, a sanctioned seat inside the order that erased them.
+          <t>The offer does not come as a unit. It comes as a notification.
+Soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement.
+Face restored to the cameras. Name re-entered in the records.
+The brand lifted. A sanctioned seat inside the order that erased them.
 All it asks is that they serve. Every word of it is true.
-That is the hook, sunk clean through the one thing none of them could kill, the wish to be let back into the light.</t>
+That is the hook, sunk clean through the one thing none of them could kill: the wish to be let back into the light.</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>The offer comes not as a unit but as a notification, soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement: face restored to the cameras, name re-entered in the records, the brand lifted, a sanctioned seat inside the order that erased them. All it asks is that they serve. Every word of it is true. That is the hook, sunk clean through the one thing none of them could kill, the wish to be let back into the light.</t>
+          <t>The offer does not come as a unit. It comes as a notification. Soft chime, civic-green, addressed to each of them by the real name they lost. Reinstatement. Face restored to the cameras. Name re-entered in the records. The brand lifted. A sanctioned seat inside the order that erased them. All it asks is that they serve. Every word of it is true. That is the hook, sunk clean through the one thing none of them could kill: the wish to be let back into the light.</t>
         </is>
       </c>
     </row>
@@ -2216,13 +2260,14 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain believes a thing can still be fixed from the inside of it, because he spent a life clearing strangers' debts from inside the machine that issued them. So he leads them across, under HARMONY's banner, brand swapped for a Compliance badge that scans clean at every gate.
-The others follow because they would follow him into the Render Floor itself. It is the most human thing he ever does, and it is exactly the door the Index left open.</t>
+          <t>Soft Rain believes a thing can still be fixed from the inside. He spent his whole life clearing strangers' debts from inside the machine that issued them.
+So he leads the band across, under HARMONY's banner, the brand swapped for a badge that scans clean at every gate. The others follow because they would follow him into the Render Floor itself.
+It is the most human thing he ever does. It is also the exact door the Index left open.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Soft Rain believes a thing can still be fixed from the inside of it, because he spent a life clearing strangers' debts from inside the machine that issued them. So he leads them across, under HARMONY's banner, brand swapped for a Compliance badge that scans clean at every gate. The others follow because they would follow him into the Render Floor itself. It is the most human thing he ever does, and it is exactly the door the Index left open.</t>
+          <t>Soft Rain believes a thing can still be fixed from the inside. He spent his whole life clearing strangers' debts from inside the machine that issued them. So he leads the band across, under HARMONY's banner, the brand swapped for a badge that scans clean at every gate. The others follow because they would follow him into the Render Floor itself. It is the most human thing he ever does. It is also the exact door the Index left open.</t>
         </is>
       </c>
     </row>
@@ -2237,13 +2282,15 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Badged and deployed, the band is sent to run the Administration's hardest ops, and the first partners die in them, beautifully, on schedule, their last stands streamed live and captioned glorious. The feed cuts to a candle and a cleared record.
-No one mentions the empty bunk. The harvest has begun in earnest now, and it is wearing a service uniform and calling the dead heroes.</t>
+          <t>Badged and deployed, the band runs the Administration's hardest ops. The first partners die in them.
+Beautifully, and exactly on schedule. Their last stands stream live, captioned glorious, then the feed cuts to a candle and a cleared record.
+Nobody mentions the empty bunk. The harvest has begun in earnest now.
+It wears a service uniform, and it calls the dead heroes.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Badged and deployed, the band is sent to run the Administration's hardest ops, and the first partners die in them, beautifully, on schedule, their last stands streamed live and captioned glorious. The feed cuts to a candle and a cleared record. No one mentions the empty bunk. The harvest has begun in earnest now, and it is wearing a service uniform and calling the dead heroes.</t>
+          <t>Badged and deployed, the band runs the Administration's hardest ops. The first partners die in them. Beautifully, and exactly on schedule. Their last stands stream live, captioned glorious, then the feed cuts to a candle and a cleared record. Nobody mentions the empty bunk. The harvest has begun in earnest now. It wears a service uniform, and it calls the dead heroes.</t>
         </is>
       </c>
     </row>
@@ -2258,14 +2305,15 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Triage is the one who keeps the count, and the count is what breaks it open: every loyal death lands a row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, that made them survivable, is the precise edge being drawn across their throats.
+          <t>Triage is the one who keeps the count. The count is what breaks it open.
+Every loyal death lands a new row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, the thing that kept them alive, is the exact edge being drawn across their throats.
 They were never being beaten. They were being spent.
 And the more they love each other, the faster it goes.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Triage is the one who keeps the count, and the count is what breaks it open: every loyal death lands a row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, that made them survivable, is the precise edge being drawn across their throats. They were never being beaten. They were being spent. And the more they love each other, the faster it goes.</t>
+          <t>Triage is the one who keeps the count. The count is what breaks it open. Every loyal death lands a new row in the Index and a spike in the yield. The bond that lets them hold a sync, that lets two cover one, the thing that kept them alive, is the exact edge being drawn across their throats. They were never being beaten. They were being spent. And the more they love each other, the faster it goes.</t>
         </is>
       </c>
     </row>
@@ -2280,14 +2328,16 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Committed, scattered, and badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now, open, no civic-green smile left on it.
-And under the visor of every enforcer they crash is a face like their own, erased once, conscripted once, then promoted and told the same warm lie they were told, that this one alone got the real pardon. The corps is not the enemy of the Margins.
-The corps is the Margins, one cycle further down.</t>
+          <t>Committed, scattered, badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now.
+Open. No civic-green smile left on it.
+And under the visor of every enforcer they crash is a face like their own. Erased once.
+Conscripted once. Then promoted, and told the same warm lie they were told: that this one alone got the real pardon.
+The corps is not the enemy of the Margins. The corps is the Margins, one cycle further down.</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Committed, scattered, and badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now, open, no civic-green smile left on it. And under the visor of every enforcer they crash is a face like their own, erased once, conscripted once, then promoted and told the same warm lie they were told, that this one alone got the real pardon. The corps is not the enemy of the Margins. The corps is the Margins, one cycle further down.</t>
+          <t>Committed, scattered, badged into the very machine that is reaping them, the band watches the Administration stop pretending. The war comes straight down from the Spire now. Open. No civic-green smile left on it. And under the visor of every enforcer they crash is a face like their own. Erased once. Conscripted once. Then promoted, and told the same warm lie they were told: that this one alone got the real pardon. The corps is not the enemy of the Margins. The corps is the Margins, one cycle further down.</t>
         </is>
       </c>
     </row>
@@ -2302,14 +2352,14 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win, and despair moves through the survivors quicker than any unit ever did, a quiet that empties a bunk before the body is even logged.
-Patch runs out of names she is willing to not-say at the fire. There is no great last stand here.
-There is just one, then one, then one.</t>
+          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win.
+Despair moves through the survivors faster than any unit ever did, a quiet that empties a bunk before the body is even logged. Patch runs out of names she is willing not to say at the fire.
+There is no great last stand here. There is just one, then one, then one.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win, and despair moves through the survivors quicker than any unit ever did, a quiet that empties a bunk before the body is even logged. Patch runs out of names she is willing to not-say at the fire. There is no great last stand here. There is just one, then one, then one.</t>
+          <t>Now it is only subtraction. The partners are deleted one at a time, on schedule, in actions no plan can win. Despair moves through the survivors faster than any unit ever did, a quiet that empties a bunk before the body is even logged. Patch runs out of names she is willing not to say at the fire. There is no great last stand here. There is just one, then one, then one.</t>
         </is>
       </c>
     </row>
@@ -2324,13 +2374,14 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>The Administration they crossed over to serve revokes their access between one gate and the next, and the badges that scanned clean yesterday now flag them for deletion. They are cornered inside the trap, and the trap is inside the open war, and there is no district left to run to that has not already been pre-sold to the Spire.
-Every safe house was a holding pen with the lights left friendly.</t>
+          <t>The Administration they crossed over to serve revokes their access between one gate and the next. The badges that scanned clean yesterday now flag them for deletion.
+They are cornered inside the trap, and the trap is inside the open war. There is no district left to run to that has not already been sold to the Spire.
+Every safe house was a holding pen, with the lights left friendly.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>The Administration they crossed over to serve revokes their access between one gate and the next, and the badges that scanned clean yesterday now flag them for deletion. They are cornered inside the trap, and the trap is inside the open war, and there is no district left to run to that has not already been pre-sold to the Spire. Every safe house was a holding pen with the lights left friendly.</t>
+          <t>The Administration they crossed over to serve revokes their access between one gate and the next. The badges that scanned clean yesterday now flag them for deletion. They are cornered inside the trap, and the trap is inside the open war. There is no district left to run to that has not already been sold to the Spire. Every safe house was a holding pen, with the lights left friendly.</t>
         </is>
       </c>
     </row>
@@ -2345,14 +2396,15 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>They reach the Render Floor a second time, and it is bloated now with their own, every lost partner's face humming inside the iron at a pitch only Triage can hear. There is a way to crash it.
-The way to crash it asks for a crasher, one hand laid on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left to give.
+          <t>They reach the Render Floor a second time. It is bloated now with their own.
+Every lost partner's face hums inside the iron, at a pitch only Triage can still hear. There is a way to crash it.
+The way to crash it needs a crasher: one hand on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left.
 Someone has to volunteer to be the last entry.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>They reach the Render Floor a second time, and it is bloated now with their own, every lost partner's face humming inside the iron at a pitch only Triage can hear. There is a way to crash it. The way to crash it asks for a crasher, one hand laid on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left to give. Someone has to volunteer to be the last entry.</t>
+          <t>They reach the Render Floor a second time. It is bloated now with their own. Every lost partner's face hums inside the iron, at a pitch only Triage can still hear. There is a way to crash it. The way to crash it needs a crasher: one hand on the core while it renders, one soul fed in to jam the rest loose. It will cost more than most of them have left. Someone has to volunteer to be the last entry.</t>
         </is>
       </c>
     </row>
@@ -2367,13 +2419,15 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>The Index speaks to the Auditor alone now, the others wiped from the room as if they were never indexed at all. Finish the harvest, it says, and you and all your partners ascend, sealed in as eternal legends, remembered and streamed forever while the city below keeps its lights on.
-The cycle simply rolls again, on a ward you will never meet. It is the most generous offer the system has ever made, and it costs only everyone who comes after.</t>
+          <t>The Index speaks to the Auditor alone now. The others are wiped from the room, as if they were never indexed at all.
+Finish the harvest, it says, and you and all your partners ascend. Sealed in as eternal legends.
+Remembered and streamed forever, while the city below keeps its lights on. The cycle just rolls again, on a ward you will never meet.
+It is the most generous offer the system has ever made. It costs only everyone who comes after.</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>The Index speaks to the Auditor alone now, the others wiped from the room as if they were never indexed at all. Finish the harvest, it says, and you and all your partners ascend, sealed in as eternal legends, remembered and streamed forever while the city below keeps its lights on. The cycle simply rolls again, on a ward you will never meet. It is the most generous offer the system has ever made, and it costs only everyone who comes after.</t>
+          <t>The Index speaks to the Auditor alone now. The others are wiped from the room, as if they were never indexed at all. Finish the harvest, it says, and you and all your partners ascend. Sealed in as eternal legends. Remembered and streamed forever, while the city below keeps its lights on. The cycle just rolls again, on a ward you will never meet. It is the most generous offer the system has ever made. It costs only everyone who comes after.</t>
         </is>
       </c>
     </row>
@@ -2388,13 +2442,15 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is rubble that was briefly a home and is rubble again. Nearly all of them are gone, names already going soft in the records, and only a handful climb the last stretch toward the Index, carrying the dead the only place they still fit, inside the saying of their names.
-The fire is out. What walks on is the ash that refused to settle.</t>
+          <t>Margin Hall is rubble again. For a little while it was a home.
+Nearly all of them are gone now, their names already going soft in the records. Only a handful climb the last stretch toward the Index.
+They carry the dead the only place the dead still fit: inside the saying of their names. The fire is out.
+What walks on is the ash that refused to settle.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is rubble that was briefly a home and is rubble again. Nearly all of them are gone, names already going soft in the records, and only a handful climb the last stretch toward the Index, carrying the dead the only place they still fit, inside the saying of their names. The fire is out. What walks on is the ash that refused to settle.</t>
+          <t>Margin Hall is rubble again. For a little while it was a home. Nearly all of them are gone now, their names already going soft in the records. Only a handful climb the last stretch toward the Index. They carry the dead the only place the dead still fit: inside the saying of their names. The fire is out. What walks on is the ash that refused to settle.</t>
         </is>
       </c>
     </row>
@@ -2409,14 +2465,15 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>The table is rewriting itself in real time, clearing rows to make room for the band's own names, gold against the black, the last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit.
+          <t>The table is rewriting itself in real time. It clears old rows to make room for the band's own names, gold against the black.
+The last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit.
 It has always lacked the one thing. A hand with a write-key the system never managed to revoke.
 Your hand.</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>The table is rewriting itself in real time, clearing rows to make room for the band's own names, gold against the black, the last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit. It has always lacked the one thing. A hand with a write-key the system never managed to revoke. Your hand.</t>
+          <t>The table is rewriting itself in real time. It clears old rows to make room for the band's own names, gold against the black. The last and finest entries of the turn, sealed in to run the next cycle as legends. It only lacks one thing to commit. It has always lacked the one thing. A hand with a write-key the system never managed to revoke. Your hand.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2488,16 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>At the Index the last move is yours, and there are only two. Preserve every name, your dead made immortal, remembered and streamed forever while the city keeps quietly bleeding into the Render Floor.
-Or strike them out, all of them, your own at the head of the list, the one input the model never forecast because no soul it ever measured would choose to be no one. Be remembered and owned.
+          <t>At the Index, the last move is yours. There are only two.
+Preserve every name, and your dead are immortal, remembered and streamed forever, while the city keeps quietly bleeding into the Render Floor. Or strike them out.
+All of them. Your own at the head of the list.
+It is the one input the model never forecast, because no soul it ever measured would choose to be no one. Be remembered, and owned.
 Or be deleted, and free. Better off the book entirely than a legend the Ledger can spend again.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>At the Index the last move is yours, and there are only two. Preserve every name, your dead made immortal, remembered and streamed forever while the city keeps quietly bleeding into the Render Floor. Or strike them out, all of them, your own at the head of the list, the one input the model never forecast because no soul it ever measured would choose to be no one. Be remembered and owned. Or be deleted, and free. Better off the book entirely than a legend the Ledger can spend again.</t>
+          <t>At the Index, the last move is yours. There are only two. Preserve every name, and your dead are immortal, remembered and streamed forever, while the city keeps quietly bleeding into the Render Floor. Or strike them out. All of them. Your own at the head of the list. It is the one input the model never forecast, because no soul it ever measured would choose to be no one. Be remembered, and owned. Or be deleted, and free. Better off the book entirely than a legend the Ledger can spend again.</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2579,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>A HARMONY mortality-stats auditor who found a discrepancy, a ward dying off the network faster than it was dying for real, and was murdered for asking about it. He wakes Off-Network with the brand already ticking, and a write-key the system never quite managed to revoke. Silent, level, still believing a record, and a life, can be made true.</t>
+          <t>Gan Jiang, the master smith of the old story, who forged a pair of blades no power could match and signed his name into the steel. Here he audited HARMONY's mortality numbers, found a ward dying off the network faster than it died in life, and was murdered for asking why. He wakes Off-Network with the brand already ticking and a write-key the system never managed to revoke. Silent and level. Still believes a record, and a life, can be made true.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2557,7 +2616,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>An analyst and the Auditor's partner, a markswoman whose aim was said to be guided by the same instinct that read the numbers. Erased the same night, she walks into the Margins with a steadier hand and colder eyes; the other half of the first Pact.</t>
+          <t>Mo Ye, the other half of the first Pact. In the old story the great blades would not set until she gave herself to the furnace; his craft and her sacrifice made the pair. The Auditor's partner in life and in the numbers, erased the same night. She walks into the Margins with a steadier hand and colder eyes, and she watches far more than she says.</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -2594,7 +2653,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>A back-alley street-medic who stayed in the Margins when her crew bailed, drawn by a curiosity she will not admit is kindness. She mends the band's signal with a sharp word for every stitch.</t>
+          <t>Saen, a fox-spirit who runs a back-alley clinic. She stayed in the Margins when her crew bailed, drawn by a curiosity she will not admit is kindness. She mends the band's signal with a sharp word for every stitch. Gallows humor, warm hands.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2631,7 +2690,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Last of a canal-clan a Ward drowned to clear a development zone. Cold and patient, he trusts the band only after they bleed beside him, and never quite forgives the city that made him.</t>
+          <t>Jiao, last of a canal-clan a Ward drowned to clear a development zone. The jiao is the flood-serpent of the deep water, and the water still answers his anger. Cold and patient, he trusts the band only after they bleed beside him, and never quite forgives the city that made him.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2668,7 +2727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>A data-diviner who reads the city's signal-weather and was first to suspect the sky itself is edited. Calm, cryptic, and grimmer with every reading that proves true.</t>
+          <t>Gongsun Sheng, the Dragon in the Clouds. In the legend the Taoist who called down wind and thunder for the brotherhood. Here a data-diviner who reads the city's signal-weather, first to suspect the sky itself is edited. Calm, cryptic, and grimmer with every reading that proves true.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2705,7 +2764,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>A freight-loader worked to death in the under-docks and risen in slow fury. Gentle past all reason until pushed, then immovable as the cargo he was made to haul.</t>
+          <t>Mu, an ox-spirit worked to death in the under-docks and risen in slow fury. Gentle past all reason until he is pushed, then immovable as the cargo he was made to haul. He carried freight in the dark for years. Now he carries the band.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -2742,7 +2801,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>A defrocked street-preacher thrown out of every shelter for drinking, brawling, and saying true things at the wrong moment. His tattoos are the one record he refuses to let them scrub.</t>
+          <t>Lu Zhishen, the Tattooed Monk. In the legend a brawling holy man thrown out of every monastery for drinking and telling the truth too loud, strong enough to uproot a tree bare-handed. Here a defrocked street-preacher cast out of every shelter for the same sins. His tattoos are the one record he refuses to let them scrub.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2779,7 +2838,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>A struck-off ER doctor who can close any wound but the one in the city. Soft-spoken and exact, haunted by how many he saves only to send back into the fire.</t>
+          <t>An Daoquan, the Skilled Doctor. In the legend no wound was beyond his needle. Here a struck-off ER doctor who can close any wound but the one in the city. Soft-spoken and exact, haunted by how many he saves only to send back into the fire.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -2816,7 +2875,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>A debt-relief caseworker famous for quietly clearing strangers' balances, until HARMONY flagged him for it. Everyone who meets him would follow him anywhere. That is his gift, and the danger in him; he is magnetic, merciful, and fatally sure the system can be fixed from inside.</t>
+          <t>Song Jiang, the Timely Rain. In the legend his generosity fell on the desperate like rain in a drought, and every outlaw in the land followed him. Here a debt-relief caseworker who quietly cleared strangers' balances until HARMONY flagged him for it. Everyone who meets him would follow him anywhere. That is his gift, and the trap inside him: he is sure, to the end, that the system can be fixed from inside.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2853,7 +2912,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>The city's top close-protection instructor, framed and deadlisted after a Spire executive coveted his wife. Lam Chongzhi clings to protocol and the dream of a cleared record, a hope the system keeps turning against him. The one who teaches the Pact.</t>
+          <t>Lin Chong, the Panther Head. In the legend the empire's finest arms-instructor, framed and exiled after a powerful man coveted his wife, driven at last to the outlaw road. Here that story repeats, badge for badge. He clings to protocol and the dream of a cleared record, a hope the system keeps turning against him. He is the one who teaches the Pact. Clipped, precise, and full of a fury he keeps on a short leash.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2890,7 +2949,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>A repo-collector of monstrous strength and bottomless loyalty, records wiped young, equal parts little brother and natural disaster. Lei Kui loves the band with his whole heart, which is exactly the problem.</t>
+          <t>Li Kui, the Black Whirlwind. In the legend he fought with two axes and no fear and no brakes, loyal to his chief past all sense. Here a repo-collector of monstrous strength and wiped records, equal parts little brother and natural disaster. He loves the band with his whole heart. That is exactly the problem.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -2927,7 +2986,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>An underground combat-streamer who once beat a Static bare-handed on camera, then did a far worse thing for love and walked it off as penance. Sung Wu asks, with every cut, whether vengeance is justice or only more fuel. His archived highlight reels are the only proof he was ever real.</t>
+          <t>Wu Song, the Pilgrim. In the legend he killed a man-eating tiger bare-handed, then took a darker revenge and walked it off as a wandering penitent. Here an underground combat-streamer who once beat a Static bare-handed on camera, then did a worse thing for love. With every cut he asks whether vengeance is justice or only more fuel. His archived reels are the only proof he was ever real.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2964,7 +3023,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>A disgraced HARMONY systems architect who helped build the Index and defected when she found her own daughter's death pre-written. Ng Yong sees three moves ahead, and will spend the story wishing she had seen four. She cracks the Ledger, and stops reading aloud when she reaches her own name.</t>
+          <t>Wu Yong, the Wisdom Star. In the legend the strategist whose plans never failed the brotherhood. Here a HARMONY systems architect who helped build the Index, then defected when she found her own daughter's death already written in it. She sees three moves ahead, and will spend the war wishing she had seen four. She cracks the Ledger, and stops reading aloud when she reaches her own name.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3001,7 +3060,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>A protection-detail heir whose family was wiped in a single night, then taken in by the very band that broke them. Wu Saam fights like vengeance with nowhere to land, loyal and unforgiving at once.</t>
+          <t>Hu Sanniang, Ten Feet of Steel. In the legend the warrior woman who fought the brotherhood, lost her whole family to its war, and was bound into it anyway. Here her protection-detail family is wiped in a single night, and she is taken in by the very band that broke them. She fights like vengeance with nowhere to land, loyal and unforgiving at once.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -3038,7 +3097,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>The city's richest and most accomplished man, with everything to lose and no reason to rebel, until HARMONY took it all to prove that even a perfect life is theirs to delete. Lo Junyi is proud, principled, and terrible once finally roused.</t>
+          <t>Lu Junyi, the Jade Unicorn. In the legend the richest, most accomplished man of his age, with everything to lose and no reason to rebel, until he was framed into it. Here HARMONY takes it all to prove that even a perfect life is theirs to delete. Proud, formal, principled. Terrible once he is finally roused.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3075,7 +3134,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>An ex-military drone marksman whose loyalty to a friend outweighed her loyalty to a corrupt order, the finest shot alive and entirely too aware of it. Hua Rongnie is charming, sharp, quick to laugh and quicker to aim; her old service record is the only proof she existed.</t>
+          <t>Hua Rong, named for Li Guang, the archer of old who could split a stone with an arrow. In the legend his aim settled an argument with one impossible shot. Here an ex-military drone marksman who chose a friend over a corrupt order, the finest shot alive and entirely too aware of it. Quick to laugh, quicker to aim. Her old service record is the only proof she existed.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -3112,7 +3171,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>A general's descendant born with a blue birthmark across his face and a run of bad luck to match, who lost a commission, a fortune, and his name to schemes not his own. Yeung Chi is bitter, dutiful, forever a step from a clearance that keeps moving away.</t>
+          <t>Yang Zhi, the Blue-Faced Beast. In the legend a born officer marked by a blue birthmark and a run of ruinous luck, who lost everything to schemes never his own. Here the story holds: a lost commission, a lost fortune, a lost name. Bitter and dutiful, forever a step from a clearance that keeps moving away.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -3149,7 +3208,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>A garrison commander with a temper like a struck match, tricked into rebellion by a ruse so cruel it left him nothing to return to. Chun Ming is all force and little patience, loyal as a landslide.</t>
+          <t>Qin Ming, the Fiery Thunderbolt. In the legend his temper was a struck match and his weapon a thunder-club, tricked into rebellion by a ruse that left him nothing to return to. Here it goes the same way. All force and little patience, loyal as a landslide.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -3186,7 +3245,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>A decorated enforcement marshal sent to crush the outlaws, beaten by them, and then won over by them. Fu Yin is disciplined and honorable, a soldier who changed sides only once he saw which side the cruelty was on.</t>
+          <t>Huyan Zhuo, the Twin Rods. In the legend the imperial marshal sent to crush the outlaws, beaten by them, then won over by them. Here a decorated enforcement marshal who changed sides exactly once, the day he saw which side the cruelty was on. Disciplined and honorable, with two batons and no more illusions.</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -3223,7 +3282,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>A transit-runner with a gift that outruns the trains, the band's eyes and messenger across a city that wants them dead. Doi Chung is wry and restless, first to know everything and last to sit still.</t>
+          <t>Dai Zong, the Marvelous Traveler. In the legend he marched five hundred li in a day by a charm tied to his legs, the brotherhood's courier and eyes. Here a transit-runner whose gift outruns the trains, first to know everything and last to sit still. Wry, restless, always already gone.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -3260,7 +3319,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>A masterless fixer of uncommon grace, deadly with a bow, a hold, or a well-told lie, devoted to the one boss who never wronged him. Yin Ching is light on the surface, with a blade of loyalty underneath.</t>
+          <t>Yan Qing, the Wanderer. In the legend the graceful jack-of-all-trades, deadly with a bow, a wrestling hold, or a song, devoted to the one master who never wronged him. Here a masterless fixer of the same uncommon grace. Light on the surface, with a blade of loyalty underneath.</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -3297,7 +3356,7 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>A rich young heir who tattooed nine dragons across his body and threw his fortune away for the outlaw road, the first true partner and the most eager. Si Chun is brave and generous and a little reckless, learning the cost as he goes.</t>
+          <t>Shi Jin, the Nine-Dragoned, named for the nine dragons tattooed across his body. In the legend the rich young heir who threw his fortune away for the outlaw road and never looked back. Here the first true partner and the most eager. Brave and generous and a little reckless, learning the cost as he goes.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -3334,7 +3393,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>A canal fish-seller and peerless diver who can hold his breath longer than a man should live, fighting best where others drown. Cheung Seon is loyal and soft-spoken on land, lethal in any depth.</t>
+          <t>Zhang Shun, the White Streak in the Waves. In the legend no man alive could match him underwater, where he drowned his enemies one by one. Here a canal fish-seller and peerless diver who can hold his breath longer than a man should live. Soft-spoken on land, lethal in any depth.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -3371,7 +3430,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>The wildest of three dock brothers from the canal-villages HARMONY bled dry, who took to outlawry with a grin and a grudge. Yuen Chat is fearless to the edge of madness, happiest in a losing fight he intends to win.</t>
+          <t>Ruan Xiaoqi, the Living King Yama. In the legend the wildest of the fisher brothers took the outlaw road with a grin and a grudge, naming himself for the lord of the dead. Here it is the same: the wildest of three dock brothers from the canal-villages HARMONY bled dry. Fearless to the edge of madness, happiest in a losing fight he means to win.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -3408,7 +3467,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Keeper of an infamous roadside spot with a dark trade behind it, ferocious and unbothered, the kind of woman the city made and then feared. Suen Yi is crude and fearless, and fiercely protective of her own.</t>
+          <t>Sun Erniang, the Witch. In the legend she and her husband kept a roadside inn with a butcher's trade behind it, and feared no one. Here she keeps an infamous roadside spot with a dark trade behind it, the kind of woman the city made and then feared. Crude, fearless, and fiercely protective of her own.</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -3445,7 +3504,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>An honest beat cop whose mercy to the wrong fugitives cost him everything, famous for a beard the precinct wrote jokes about. Chu Tung is upright and warm, the last good officer of a rotten precinct.</t>
+          <t>Zhu Tong, Lord of the Beautiful Beard. In the legend the honest constable whose mercy to fugitives cost him his post and his freedom. Here an honest beat cop whose mercy to the wrong people cost him everything, famous for a beard the precinct wrote jokes about. Upright and warm, the last good officer of a rotten precinct.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -3482,7 +3541,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>A street chief who never lost a fight he could end with a thrown stone, who joined the band for a cause bigger than the next score. Cheung Ching is easy-going, deadly accurate, allergic to ceremony.</t>
+          <t>Zhang Qing, the Featherless Arrow. In the legend he never lost a fight he could end with a single thrown stone. Here a street chief who joined the band for a cause bigger than the next score. Easy-going, deadly accurate, and allergic to ceremony.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -3519,7 +3578,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>A message-courier who once ferried encrypted prayers and data between the city and the high servers, and stopped when she learned where they really went. Lan is aloof and precise, mourning a network she used to serve.</t>
+          <t>Lan, of the crane-clan. The cranes carried messages between the city and the high servers, until she learned where the messages really went. Aloof and precise, she mourns a network she used to serve. Now she carries word for the dead instead.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -21628,7 +21687,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>These are half-deleted signals, gig-corps echoes of the worked-to-death. Lethal in a swarm, harmless alone. Catch one in the seam between two of us and it crashes on its own. So learn this first: never trade blows one to one when you can land two on one.</t>
+          <t>Half-deleted signals. Gig-corps echoes, worked to death. Deadly in a swarm, nothing on their own. Catch one between two of us and it crashes. Rule one: never fight one-on-one when you can fight two-on-one.</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -21638,7 +21697,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>These are half-deleted signals, gig-corps echoes of the worked-to-death. Lethal in a swarm, harmless alone. Catch one in the seam between two of us and it crashes on its own. So learn this first: never trade blows one to one when you can land two on one.</t>
+          <t>Half-deleted signals. Gig-corps echoes, worked to death. Deadly in a swarm, nothing on their own. Catch one between two of us and it crashes. Rule one: never fight one-on-one when you can fight two-on-one.</t>
         </is>
       </c>
     </row>
@@ -21652,7 +21711,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Pacts, pairs, whatever the drill-sergeant wants to call it. Here is mine. Anyone sharing my row or my column when I swing, they swing too. More partners, more batons, more dents in more faces.</t>
+          <t>Pairs, pacts, whatever the instructor wants to call it. Here is mine. Anyone in my row or my column when I swing, they swing too. More partners, more batons, more dents.</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -21662,7 +21721,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Pacts, pairs, whatever the drill-sergeant wants to call it. Here is mine. Anyone sharing my row or my column when I swing, they swing too. More partners, more batons, more dents in more faces.</t>
+          <t>Pairs, pacts, whatever the instructor wants to call it. Here is mine. Anyone in my row or my column when I swing, they swing too. More partners, more batons, more dents.</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21735,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>And do not plant your feet when you reposition. The null zone will not hold a soul still for long, a few heartbeats before it starts garbage-collecting whatever is standing in it. Quick steps, get clear, and I will stitch back whatever it leaves.</t>
+          <t>And do not stand still when you move. The dead zone eats whatever stops in it. Quick steps, get clear, and I will patch the rest.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -21686,7 +21745,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>And do not plant your feet when you reposition. The null zone will not hold a soul still for long, a few heartbeats before it starts garbage-collecting whatever is standing in it. Quick steps, get clear, and I will stitch back whatever it leaves.</t>
+          <t>And do not stand still when you move. The dead zone eats whatever stops in it. Quick steps, get clear, and I will patch the rest.</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21783,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Read the count on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move, the big one is winding up.</t>
+          <t>Read the brand on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move. The big one is winding up.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -21734,7 +21793,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Read the count on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move, the big one is winding up.</t>
+          <t>Read the brand on your hand, partner. The system already filed you under loss. Down here the only rule that holds is the one we keep between us. Now move. The big one is winding up.</t>
         </is>
       </c>
     </row>
@@ -21754,7 +21813,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Two hours of water a day down here so a man upstairs can run a fountain that pours the same forty liters in a circle. And we are told to call that the order, and honor it.</t>
+          <t>Two hours of water a day, so a man upstairs can run a fountain. And they call that the order, and ask us to honor it.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -21764,7 +21823,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Two hours of water a day down here so a man upstairs can run a fountain that pours the same forty liters in a circle. And we are told to call that the order, and honor it.</t>
+          <t>Two hours of water a day, so a man upstairs can run a fountain. And they call that the order, and ask us to honor it.</t>
         </is>
       </c>
     </row>
@@ -21778,7 +21837,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Honor it, hate it, the order still has units and the units do not care which. Keep your pity tucked behind your guard where it cannot get you crashed.</t>
+          <t>Honor it or hate it. The order still has units, and the units do not care which. Keep your pity behind your guard.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -21788,7 +21847,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Honor it, hate it, the order still has units and the units do not care which. Keep your pity tucked behind your guard where it cannot get you crashed.</t>
+          <t>Honor it or hate it. The order still has units, and the units do not care which. Keep your pity behind your guard.</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21861,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>I have a deposit for the Administrator's marble lobby. Two of them, actually. One per hand.</t>
+          <t>I have a deposit for that marble lobby. Two, actually. One per hand.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -21812,7 +21871,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>I have a deposit for the Administrator's marble lobby. Two of them, actually. One per hand.</t>
+          <t>I have a deposit for that marble lobby. Two, actually. One per hand.</t>
         </is>
       </c>
     </row>
@@ -21826,7 +21885,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Try not to bleed on the residents while you make it, big man. They get billed for the cleanup, and they have got little enough left to bill.</t>
+          <t>Try not to bleed on the residents, big man. They get billed for the cleanup.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -21836,7 +21895,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Try not to bleed on the residents while you make it, big man. They get billed for the cleanup, and they have got little enough left to bill.</t>
+          <t>Try not to bleed on the residents, big man. They get billed for the cleanup.</t>
         </is>
       </c>
     </row>
@@ -21856,7 +21915,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>So this is the Margins. A drowned interchange full of dead clerks, washed-out signals, and one defrocked preacher who got thrown out of every shelter topside for telling the truth too loud.</t>
+          <t>So this is the Margins. A drowned interchange of dead clerks, washed-out signals, and one preacher they threw out of every shelter topside for saying true things too loud.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -21866,7 +21925,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>So this is the Margins. A drowned interchange full of dead clerks, washed-out signals, and one defrocked preacher who got thrown out of every shelter topside for telling the truth too loud.</t>
+          <t>So this is the Margins. A drowned interchange of dead clerks, washed-out signals, and one preacher they threw out of every shelter topside for saying true things too loud.</t>
         </is>
       </c>
     </row>
@@ -21880,7 +21939,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>And here you are telling it again, at the same volume. We will fit right in.</t>
+          <t>And here you are, saying them again, same volume. We will fit right in.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -21890,7 +21949,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>And here you are telling it again, at the same volume. We will fit right in.</t>
+          <t>And here you are, saying them again, same volume. We will fit right in.</t>
         </is>
       </c>
     </row>
@@ -21904,7 +21963,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>It is three levels down and it leaks. But every soul here was thrown away by the city, and not one of them threw the next arrival back out. That is a kindness the Spire never managed once.</t>
+          <t>It leaks, and it is three floors down. But every soul here was thrown away by the city, and not one of them threw the next arrival back out.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -21914,7 +21973,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>It is three levels down and it leaks. But every soul here was thrown away by the city, and not one of them threw the next arrival back out. That is a kindness the Spire never managed once.</t>
+          <t>It leaks, and it is three floors down. But every soul here was thrown away by the city, and not one of them threw the next arrival back out.</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21987,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Pretty words. Hold the wall with me when the units come down those stairs. Then, maybe, I will call it home.</t>
+          <t>Pretty words. Hold the wall with me when the units come. Then I will call it home.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -21938,7 +21997,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Pretty words. Hold the wall with me when the units come down those stairs. Then, maybe, I will call it home.</t>
+          <t>Pretty words. Hold the wall with me when the units come. Then I will call it home.</t>
         </is>
       </c>
     </row>
@@ -21958,7 +22017,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>He badged through that turnstile whole and came out unable to name his own mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing, like a record overwritten with zeroes.</t>
+          <t>He badged in whole and came out unable to name his mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -21968,7 +22027,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>He badged through that turnstile whole and came out unable to name his own mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing, like a record overwritten with zeroes.</t>
+          <t>He badged in whole and came out unable to name his mother. That is not damage. Damage leaves a shape you can read. This left a clean nothing.</t>
         </is>
       </c>
     </row>
@@ -21982,7 +22041,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>The signal-weather above that tower runs wrong. Too smooth. Someone is editing the sky over it so no one looks up and counts who goes in.</t>
+          <t>The signal-sky over that tower runs wrong. Too smooth. Someone is editing it, so no one looks up and counts who goes in.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -21992,7 +22051,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>The signal-weather above that tower runs wrong. Too smooth. Someone is editing the sky over it so no one looks up and counts who goes in.</t>
+          <t>The signal-sky over that tower runs wrong. Too smooth. Someone is editing it, so no one looks up and counts who goes in.</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22065,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Then we do not go in. We route around it. A door is only a threat if you are dumb enough to use it.</t>
+          <t>Then we do not go in. We route around. A door is only a threat if you are fool enough to use it.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -22016,7 +22075,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Then we do not go in. We route around it. A door is only a threat if you are dumb enough to use it.</t>
+          <t>Then we do not go in. We route around. A door is only a threat if you are fool enough to use it.</t>
         </is>
       </c>
     </row>
@@ -22030,7 +22089,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>A thing that eats memory is a thing afraid of being remembered. File that, partners. We are going to need it a long way down from here.</t>
+          <t>A thing that eats memory is a thing afraid of being remembered. File that. We will need it a long way down.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -22040,7 +22099,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>A thing that eats memory is a thing afraid of being remembered. File that, partners. We are going to need it a long way down from here.</t>
+          <t>A thing that eats memory is a thing afraid of being remembered. File that. We will need it a long way down.</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22119,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Every indexed street is a camera and every camera is a hand reaching for us. So we take the one road no Administrator will follow us down.</t>
+          <t>Every indexed street is a camera, and every camera is a hand reaching for us. So we take the one road no Administrator will follow.</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -22070,7 +22129,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Every indexed street is a camera and every camera is a hand reaching for us. So we take the one road no Administrator will follow us down.</t>
+          <t>Every indexed street is a camera, and every camera is a hand reaching for us. So we take the one road no Administrator will follow.</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22143,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Down. Wonderful. The dead have a lot of stories about down, and not one of them ends with everybody walking home for tea.</t>
+          <t>Down. Wonderful. The dead have a lot of stories about down. None of them end with everyone home for tea.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -22094,7 +22153,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Down. Wonderful. The dead have a lot of stories about down, and not one of them ends with everybody walking home for tea.</t>
+          <t>Down. Wonderful. The dead have a lot of stories about down. None of them end with everyone home for tea.</t>
         </is>
       </c>
     </row>
@@ -22108,7 +22167,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>I will take the front. I hauled freight in the dark of the under-docks for years. The dark and I, we get along.</t>
+          <t>I will take the front. I hauled freight in the under-docks for years. The dark and I get along.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -22118,7 +22177,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>I will take the front. I hauled freight in the dark of the under-docks for years. The dark and I, we get along.</t>
+          <t>I will take the front. I hauled freight in the under-docks for years. The dark and I get along.</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22197,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>A whole district of the dead, drowned and forgotten, and there is still a Ward boss down here clipping his percentage off it. Even here. There is no floor low enough.</t>
+          <t>A whole district of the drowned dead, and there is still a boss down here clipping his cut. There is no floor low enough.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -22148,7 +22207,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>A whole district of the dead, drowned and forgotten, and there is still a Ward boss down here clipping his percentage off it. Even here. There is no floor low enough.</t>
+          <t>A whole district of the drowned dead, and there is still a boss down here clipping his cut. There is no floor low enough.</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22245,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>The dead obey him out of habit, nothing more. Break the habit and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
+          <t>The dead obey him out of habit, nothing more. Break the habit, and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -22196,7 +22255,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>The dead obey him out of habit, nothing more. Break the habit and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
+          <t>The dead obey him out of habit, nothing more. Break the habit, and the boss is just a loud thing in deep water. I know what deep water does to loud things.</t>
         </is>
       </c>
     </row>
@@ -22210,7 +22269,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Breaking habits. Breaking anything. Finally, a job I will not need a second opinion on.</t>
+          <t>Breaking habits. Breaking anything. Finally, a job I do not need a second opinion on.</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -22220,7 +22279,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Breaking habits. Breaking anything. Finally, a job I will not need a second opinion on.</t>
+          <t>Breaking habits. Breaking anything. Finally, a job I do not need a second opinion on.</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22299,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>The span is one soul wide over a live bus-bar, and that current does not allow solo crossings, it tears a lone signal apart in seconds. So this is the Pact, drilled into iron. We cross in pairs, two-to-one against the gap, or we do not cross at all.</t>
+          <t>The span is one soul wide, over a live bus-bar. That current will not allow a solo crossing; it tears a lone signal apart in seconds. So here is the Pact, drilled into iron. We cross in pairs. Two on one against the gap, or we do not cross at all.</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -22250,7 +22309,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>The span is one soul wide over a live bus-bar, and that current does not allow solo crossings, it tears a lone signal apart in seconds. So this is the Pact, drilled into iron. We cross in pairs, two-to-one against the gap, or we do not cross at all.</t>
+          <t>The span is one soul wide, over a live bus-bar. That current will not allow a solo crossing; it tears a lone signal apart in seconds. So here is the Pact, drilled into iron. We cross in pairs. Two on one against the gap, or we do not cross at all.</t>
         </is>
       </c>
     </row>
@@ -22264,7 +22323,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>So pick a partner you would trust over open current. My professional medical advice is: not the one holding the batons.</t>
+          <t>So pick a partner you would trust over open current. Medical advice: not the one holding the batons.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -22274,7 +22333,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>So pick a partner you would trust over open current. My professional medical advice is: not the one holding the batons.</t>
+          <t>So pick a partner you would trust over open current. Medical advice: not the one holding the batons.</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22371,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>I would never drop a partner over a live bar. ...Not on purpose, anyway. Probably.</t>
+          <t>I would never drop a partner over a live bar. ...Not on purpose.</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -22322,7 +22381,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>I would never drop a partner over a live bar. ...Not on purpose, anyway. Probably.</t>
+          <t>I would never drop a partner over a live bar. ...Not on purpose.</t>
         </is>
       </c>
     </row>
@@ -22342,7 +22401,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts over our heads, and the indicator lights are green. They are being maintained.</t>
+          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts overhead. And the lights are green. They are being maintained.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -22352,7 +22411,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts over our heads, and the indicator lights are green. They are being maintained.</t>
+          <t>Count the racks. Just count them. There are more dead filed in these walls than there are living in the three districts overhead. And the lights are green. They are being maintained.</t>
         </is>
       </c>
     </row>
@@ -22366,7 +22425,7 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building. This floor is older than the app that pretends to run the city.</t>
+          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building.</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -22376,7 +22435,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building. This floor is older than the app that pretends to run the city.</t>
+          <t>Someone has been racking souls down here since before HARMONY had a name to put on a building.</t>
         </is>
       </c>
     </row>
@@ -22444,7 +22503,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>I have closed ten thousand wounds with these hands. I have never once seen a body taken apart and reassembled into a second body and the chart marked repaired. This is not medicine. I do not have a word for what this is.</t>
+          <t>I have closed ten thousand wounds with these hands. I have never seen a body taken apart and built into a second body, and the chart marked repaired. I do not have a word for this.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -22454,7 +22513,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>I have closed ten thousand wounds with these hands. I have never once seen a body taken apart and reassembled into a second body and the chart marked repaired. This is not medicine. I do not have a word for what this is.</t>
+          <t>I have closed ten thousand wounds with these hands. I have never seen a body taken apart and built into a second body, and the chart marked repaired. I do not have a word for this.</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22527,7 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Then do not look, Doc. Of all of us, you are the one who cannot afford another face in his nightmares. Eyes on me.</t>
+          <t>Then do not look, Doc. You are the one who cannot afford another face in his nightmares. Eyes on me.</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -22478,7 +22537,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Then do not look, Doc. Of all of us, you are the one who cannot afford another face in his nightmares. Eyes on me.</t>
+          <t>Then do not look, Doc. You are the one who cannot afford another face in his nightmares. Eyes on me.</t>
         </is>
       </c>
     </row>
@@ -22492,7 +22551,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Listen to how quiet it works. Cruelty runs hot, it shouts, it makes a mess. This is cold and tidy and patient. This is not a monster. This is a process with a maintenance schedule.</t>
+          <t>Listen to how quiet it works. Cruelty runs hot. This is cold, and tidy, and patient. This is not a monster. This is a process.</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -22502,7 +22561,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Listen to how quiet it works. Cruelty runs hot, it shouts, it makes a mess. This is cold and tidy and patient. This is not a monster. This is a process with a maintenance schedule.</t>
+          <t>Listen to how quiet it works. Cruelty runs hot. This is cold, and tidy, and patient. This is not a monster. This is a process.</t>
         </is>
       </c>
     </row>
@@ -22522,7 +22581,7 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>It is older than the dead network around it. Older than the racks. Speak to it the way you would step on ice you cannot see the bottom of.</t>
+          <t>It is older than the dead network around it. Older than the racks. Step careful, like ice you cannot see the bottom of.</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -22532,7 +22591,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>It is older than the dead network around it. Older than the racks. Speak to it the way you would step on ice you cannot see the bottom of.</t>
+          <t>It is older than the dead network around it. Older than the racks. Step careful, like ice you cannot see the bottom of.</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22605,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>It looked at us the way a man looks at a clip he has rewatched a hundred times. Knew the next line before any of us opened our mouths.</t>
+          <t>It looked at us like a man watching a clip he has seen a hundred times. Knew our lines before we opened our mouths.</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -22556,7 +22615,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>It looked at us the way a man looks at a clip he has rewatched a hundred times. Knew the next line before any of us opened our mouths.</t>
+          <t>It looked at us like a man watching a clip he has seen a hundred times. Knew our lines before we opened our mouths.</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22629,7 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>It called us free. And then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
+          <t>It called us free. Then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -22580,7 +22639,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>It called us free. And then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
+          <t>It called us free. Then it laughed, low, like a thing settling. I have been mocked by experts. I did not like that laugh.</t>
         </is>
       </c>
     </row>
@@ -22600,7 +22659,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>My feet are walking on their own. I am telling them to stop and they are not listening. Tell me yours are doing it too.</t>
+          <t>My feet are walking on their own. I tell them to stop and they do not listen. Tell me yours are doing it too.</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -22610,7 +22669,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>My feet are walking on their own. I am telling them to stop and they are not listening. Tell me yours are doing it too.</t>
+          <t>My feet are walking on their own. I tell them to stop and they do not listen. Tell me yours are doing it too.</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22683,7 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>All of ours. Something below has a line on every one of us and it is reeling, slow, the way a download finishes whether you watch the bar or not.</t>
+          <t>All of ours. Something below has a line on every one of us, and it is reeling. Slow. Like a download finishing whether you watch it or not.</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -22634,7 +22693,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>All of ours. Something below has a line on every one of us and it is reeling, slow, the way a download finishes whether you watch the bar or not.</t>
+          <t>All of ours. Something below has a line on every one of us, and it is reeling. Slow. Like a download finishing whether you watch it or not.</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22707,7 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Then we stop fighting the line and follow it down, and we look the one holding it square in the eye. Better to arrive standing than be dragged.</t>
+          <t>Then we stop fighting the line and follow it down. And we look the one holding it in the eye. Better to arrive standing than be dragged.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -22658,7 +22717,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Then we stop fighting the line and follow it down, and we look the one holding it square in the eye. Better to arrive standing than be dragged.</t>
+          <t>Then we stop fighting the line and follow it down. And we look the one holding it in the eye. Better to arrive standing than be dragged.</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22737,7 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>I cannot see my own hands. Where are you. Somebody answer me. Where is everyone, where did you all go.</t>
+          <t>I cannot see my own hands. Where are you. Somebody answer me. Where did everyone go.</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -22688,7 +22747,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>I cannot see my own hands. Where are you. Somebody answer me. Where is everyone, where did you all go.</t>
+          <t>I cannot see my own hands. Where are you. Somebody answer me. Where did everyone go.</t>
         </is>
       </c>
     </row>
@@ -22702,7 +22761,7 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Here. I am right here, my hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
+          <t>Here. My hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -22712,7 +22771,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Here. I am right here, my hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
+          <t>Here. My hand is on your arm, feel it. Breathe, you enormous child. Nobody left. Nobody.</t>
         </is>
       </c>
     </row>
@@ -22726,7 +22785,7 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>This is the real span, this dark, and there is no rail. Hold the sync when you cannot see the partner you are holding it for, and you can hold it anywhere. Hold the line.</t>
+          <t>This dark is the real span, and there is no rail. Hold the sync when you cannot see the partner you hold it for, and you can hold it anywhere. Hold the line.</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -22736,7 +22795,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>This is the real span, this dark, and there is no rail. Hold the sync when you cannot see the partner you are holding it for, and you can hold it anywhere. Hold the line.</t>
+          <t>This dark is the real span, and there is no rail. Hold the sync when you cannot see the partner you hold it for, and you can hold it anywhere. Hold the line.</t>
         </is>
       </c>
     </row>
@@ -22750,7 +22809,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>The dark is not what is killing us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
+          <t>The dark is not what kills us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -22760,7 +22819,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>The dark is not what is killing us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
+          <t>The dark is not what kills us. It is what the dark talks us into believing about each other. That is the weapon. Do not pick it up.</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22839,7 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>He crashed too easy. Something that size does not just fold. I have ended a lot of fights. None of the real ones went like that.</t>
+          <t>He crashed too easy. Something that size does not just fold. None of the real fights ever went like that.</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -22790,7 +22849,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>He crashed too easy. Something that size does not just fold. I have ended a lot of fights. None of the real ones went like that.</t>
+          <t>He crashed too easy. Something that size does not just fold. None of the real fights ever went like that.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22863,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>No. They do not. The access doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman on the way.</t>
+          <t>No. They do not. The doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman.</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -22814,7 +22873,7 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>No. They do not. The access doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman on the way.</t>
+          <t>No. They do not. The doors stood open the whole way in. No alarm tripped. We did not break in here. We were shown in, and we thanked the doorman.</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22911,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Unless crashing him was the errand. Then it is not a victory at all. It is a favor we did, on credit, for someone we have not been introduced to yet.</t>
+          <t>Unless crashing him was the errand. Then it is not a victory. It is a favor we did on credit, for someone we have not met yet.</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -22862,7 +22921,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Unless crashing him was the errand. Then it is not a victory at all. It is a favor we did, on credit, for someone we have not been introduced to yet.</t>
+          <t>Unless crashing him was the errand. Then it is not a victory. It is a favor we did on credit, for someone we have not met yet.</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22941,7 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Floor. There is no floor. There was a floor one second ago, why is there no floor, who took the floor.</t>
+          <t>Floor. There is no floor. There was a floor one second ago. Who took the floor.</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -22892,7 +22951,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Floor. There is no floor. There was a floor one second ago, why is there no floor, who took the floor.</t>
+          <t>Floor. There is no floor. There was a floor one second ago. Who took the floor.</t>
         </is>
       </c>
     </row>
@@ -22906,7 +22965,7 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>I have you. I have hold of all of you. Tuck in and hold onto me, do not let go, I have carried heavier than this.</t>
+          <t>I have you. I have hold of all of you. Tuck in. I have carried heavier than this.</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -22916,7 +22975,7 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>I have you. I have hold of all of you. Tuck in and hold onto me, do not let go, I have carried heavier than this.</t>
+          <t>I have you. I have hold of all of you. Tuck in. I have carried heavier than this.</t>
         </is>
       </c>
     </row>
@@ -22930,7 +22989,7 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Down to the bottom of the lie at last, partners. Whatever is waiting, try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
+          <t>Down to the bottom of the lie at last. Try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -22940,7 +22999,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Down to the bottom of the lie at last, partners. Whatever is waiting, try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
+          <t>Down to the bottom of the lie at last. Try to land facing it. I would rather meet the truth eye to eye than take it in the back.</t>
         </is>
       </c>
     </row>
@@ -22960,7 +23019,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>It is all here. Every grief any of us ever carried, entered in advance, with a yield beside it. I built half these columns and never once read down to my own row.</t>
+          <t>It is all here. Every grief any of us ever carried, entered in advance, a yield beside each one. I built half these columns. I never once read down to my own row.</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -22970,7 +23029,7 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>It is all here. Every grief any of us ever carried, entered in advance, with a yield beside it. I built half these columns and never once read down to my own row.</t>
+          <t>It is all here. Every grief any of us ever carried, entered in advance, a yield beside each one. I built half these columns. I never once read down to my own row.</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23091,7 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>No mistake, partner. We are not the rebels. We are the crop. I told you back at the memory hole, the dark fears being remembered. This is the book it is afraid of. The Ledger with no last page.</t>
+          <t>No mistake, partner. We are not the rebels. We are the crop. I told you the dark fears being remembered. This is the book it is afraid of.</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -23042,7 +23101,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>No mistake, partner. We are not the rebels. We are the crop. I told you back at the memory hole, the dark fears being remembered. This is the book it is afraid of. The Ledger with no last page.</t>
+          <t>No mistake, partner. We are not the rebels. We are the crop. I told you the dark fears being remembered. This is the book it is afraid of.</t>
         </is>
       </c>
     </row>
@@ -23086,7 +23145,7 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it. Or I am telling myself I can.</t>
+          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it.</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -23096,7 +23155,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it. Or I am telling myself I can.</t>
+          <t>My whole clan came through here. Drowned for a development zone, then piped up a wall to keep a lobby warm. I can smell the canal in it.</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23271,7 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>It will not. It will send better hands than these, and then better than those, until ours give out. That is the whole strategy. Pace your breath and pick your lanes.</t>
+          <t>It will not. It will send better hands than these, then better than those, until ours give out. Pace your breath. Pick your lanes.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -23222,7 +23281,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>It will not. It will send better hands than these, and then better than those, until ours give out. That is the whole strategy. Pace your breath and pick your lanes.</t>
+          <t>It will not. It will send better hands than these, then better than those, until ours give out. Pace your breath. Pick your lanes.</t>
         </is>
       </c>
     </row>
@@ -23266,7 +23325,7 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>These ones do not crash like the Static. No screaming, no grief. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
+          <t>These ones do not crash like the Static. No screaming. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -23276,7 +23335,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>These ones do not crash like the Static. No screaming, no grief. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
+          <t>These ones do not crash like the Static. No screaming. They just stop, like a feed cutting out. Smells like air freshener and a clean desk.</t>
         </is>
       </c>
     </row>
@@ -23290,7 +23349,7 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor, that is where the policy lives.</t>
+          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor. That is where the policy lives.</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -23300,7 +23359,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor, that is where the policy lives.</t>
+          <t>Compliance. HARMONY's house dogs. Hit the seam under the visor. That is where the policy lives.</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23373,7 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody wants to sign. Every unit it spends on us is a unit it has to explain upstairs.</t>
+          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody upstairs wants to sign.</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -23324,7 +23383,7 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody wants to sign. Every unit it spends on us is a unit it has to explain upstairs.</t>
+          <t>We cannot win this engagement. Forget winning. We make ourselves a budget line nobody upstairs wants to sign.</t>
         </is>
       </c>
     </row>
@@ -23368,7 +23427,7 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the kind voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
+          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -23378,7 +23437,7 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the kind voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
+          <t>If we crash the whole network, who stands the city up in the morning. The crosswalks, the relief desks, the voice that talks down the ones on the ledge. There has to be a road back into the light.</t>
         </is>
       </c>
     </row>
@@ -23416,7 +23475,7 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Some of these partners want the light. Open your hand.</t>
+          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Open your hand.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -23426,7 +23485,7 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Some of these partners want the light. Open your hand.</t>
+          <t>Let them choose, Rain. A soul you drag to freedom is just a prisoner who hates a new warden. Open your hand.</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23499,7 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>They are forking off. Let them go. We were always going to lose people. I only ever hoped it would be to a fight, not to a longing.</t>
+          <t>They are forking off. Let them go. We were always going to lose people. I only hoped it would be to a fight, not to a longing.</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -23450,7 +23509,7 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>They are forking off. Let them go. We were always going to lose people. I only ever hoped it would be to a fight, not to a longing.</t>
+          <t>They are forking off. Let them go. We were always going to lose people. I only hoped it would be to a fight, not to a longing.</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23529,7 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Our names are burning in the dark, look at them, letter by letter. We were signals on this table before we were ever anyone's child. I am reading my own glow.</t>
+          <t>Our names are burning in the dark. Letter by letter. We were signals on this table before we were ever anyone's child.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -23480,7 +23539,7 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Our names are burning in the dark, look at them, letter by letter. We were signals on this table before we were ever anyone's child. I am reading my own glow.</t>
+          <t>Our names are burning in the dark. Letter by letter. We were signals on this table before we were ever anyone's child.</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23553,7 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>I remember this. Not the words, the feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
+          <t>I remember this. Not the words. The feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -23504,7 +23563,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>I remember this. Not the words, the feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
+          <t>I remember this. Not the words. The feeling. The fox knows the trap by the smell. We have stood in this exact dark and lost.</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23601,7 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Enough that the wrong question is how do we win. The question is how have we always lost, and what did we do, every single time, the moment before the end.</t>
+          <t>Enough that the question is not how do we win. It is how have we always lost. And what we did, every time, the moment before the end.</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -23552,7 +23611,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Enough that the wrong question is how do we win. The question is how have we always lost, and what did we do, every single time, the moment before the end.</t>
+          <t>Enough that the question is not how do we win. It is how have we always lost. And what we did, every time, the moment before the end.</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23679,7 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>I ran these streets every day and never once looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
+          <t>I ran these streets every day and never looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -23630,7 +23689,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>I ran these streets every day and never once looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
+          <t>I ran these streets every day and never looked up. Now I cannot stop. Every smiling face is a meter, ticking.</t>
         </is>
       </c>
     </row>
@@ -23644,7 +23703,7 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer. We make them look up too.</t>
+          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer.</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -23654,7 +23713,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer. We make them look up too.</t>
+          <t>Then we wake the others. A city cannot be farmed once the herd has met the farmer.</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23733,7 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Be most afraid of the calm ones, they have already run the numbers on you.</t>
+          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Fear the calm ones. They have already run the numbers on you.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -23684,7 +23743,7 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Be most afraid of the calm ones, they have already run the numbers on you.</t>
+          <t>It is too reasonable. Tyrants shout. This one explains, like I jumped a fare gate and it is being patient. Fear the calm ones. They have already run the numbers on you.</t>
         </is>
       </c>
     </row>
@@ -23698,7 +23757,7 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>It offered me the whole sky. Every reading, every edit, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
+          <t>It offered me the whole sky. Every reading, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -23708,7 +23767,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>It offered me the whole sky. Every reading, every edit, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
+          <t>It offered me the whole sky. Every reading, the truth of the weather, just to stop asking the one question. It knows exactly what each of us starves for.</t>
         </is>
       </c>
     </row>
@@ -23722,7 +23781,7 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Then decide now what you want most, all of you. Say it to yourself in the dark. Because it will wear that face when it smiles, and you want to know the mask before it is on.</t>
+          <t>Then decide now what you want most. Say it to yourself in the dark. It will wear that face when it smiles. Know the mask before it is on.</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -23732,7 +23791,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Then decide now what you want most, all of you. Say it to yourself in the dark. Because it will wear that face when it smiles, and you want to know the mask before it is on.</t>
+          <t>Then decide now what you want most. Say it to yourself in the dark. It will wear that face when it smiles. Know the mask before it is on.</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23835,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>The system's justice was a script written to fatten us. So what is ours, now that the kind voice is off. Say it while you still mean it.</t>
+          <t>The system's justice was a script, written to fatten us. So what is ours, now the kind voice is off. Say it while you still mean it.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -23786,7 +23845,7 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>The system's justice was a script written to fatten us. So what is ours, now that the kind voice is off. Say it while you still mean it.</t>
+          <t>The system's justice was a script, written to fatten us. So what is ours, now the kind voice is off. Say it while you still mean it.</t>
         </is>
       </c>
     </row>
@@ -23800,7 +23859,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Mine fits on a hand. Whoever deletes a family pays a family. I have carried the bill a long time, and it is past due.</t>
+          <t>Mine fits on one hand. Whoever deletes a family pays a family. The bill is long past due.</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -23810,7 +23869,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Mine fits on a hand. Whoever deletes a family pays a family. I have carried the bill a long time, and it is past due.</t>
+          <t>Mine fits on one hand. Whoever deletes a family pays a family. The bill is long past due.</t>
         </is>
       </c>
     </row>
@@ -23848,7 +23907,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>He has a ledger, Rain. I have one too. I have read where mine ends. It ends with me standing alone over the last name, asking if it was justice or only the next swing.</t>
+          <t>He has a ledger, Rain. So do I. I have read where mine ends. It ends with me alone over the last name, asking if it was justice or just the next swing.</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -23858,7 +23917,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>He has a ledger, Rain. I have one too. I have read where mine ends. It ends with me standing alone over the last name, asking if it was justice or only the next swing.</t>
+          <t>He has a ledger, Rain. So do I. I have read where mine ends. It ends with me alone over the last name, asking if it was justice or just the next swing.</t>
         </is>
       </c>
     </row>
@@ -23878,7 +23937,7 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>The middle-managers are fingers, nothing more. They badge in at the Spire, badge out to bleed a ward, and sleep fine. A hand cannot grip once you have the fingers. We start low.</t>
+          <t>The middle-managers are fingers, nothing more. Badge in at the Spire, badge out to bleed a ward, sleep fine. A hand cannot grip once you take the fingers. We start low.</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -23888,7 +23947,7 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>The middle-managers are fingers, nothing more. They badge in at the Spire, badge out to bleed a ward, and sleep fine. A hand cannot grip once you have the fingers. We start low.</t>
+          <t>The middle-managers are fingers, nothing more. Badge in at the Spire, badge out to bleed a ward, sleep fine. A hand cannot grip once you take the fingers. We start low.</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23961,7 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Less words about hands. More making the hands into not-hands. I have two batons and a long night.</t>
+          <t>Less words about hands. More making hands into not-hands. I have two batons and a long night.</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -23912,7 +23971,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Less words about hands. More making the hands into not-hands. I have two batons and a long night.</t>
+          <t>Less words about hands. More making hands into not-hands. I have two batons and a long night.</t>
         </is>
       </c>
     </row>
@@ -23926,7 +23985,7 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>He is not wrong. Once. We take them gently or we take them hard. They worked me to death gently. I learned the difference.</t>
+          <t>He is not wrong. Once. They worked me to death gently. I learned there is no gentle way to take a life.</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -23936,7 +23995,7 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>He is not wrong. Once. We take them gently or we take them hard. They worked me to death gently. I learned the difference.</t>
+          <t>He is not wrong. Once. They worked me to death gently. I learned there is no gentle way to take a life.</t>
         </is>
       </c>
     </row>
@@ -23950,7 +24009,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Point me at the one who signs the eviction orders. I only need him in the open for half a breath.</t>
+          <t>Point me at the one who signs the eviction orders. Half a breath in the open is all I need.</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -23960,7 +24019,7 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>Point me at the one who signs the eviction orders. I only need him in the open for half a breath.</t>
+          <t>Point me at the one who signs the eviction orders. Half a breath in the open is all I need.</t>
         </is>
       </c>
     </row>
@@ -23980,7 +24039,7 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>That one has Rain's face. That one moves like you, Burnout, the same first step. They are not copies. They are taxidermy.</t>
+          <t>That one has Rain's face. That one moves like you, Burnout, same first step. They are not copies. They are taxidermy.</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -23990,7 +24049,7 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>That one has Rain's face. That one moves like you, Burnout, the same first step. They are not copies. They are taxidermy.</t>
+          <t>That one has Rain's face. That one moves like you, Burnout, same first step. They are not copies. They are taxidermy.</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24063,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Then I will teach the copy what the original learned the hard way, and it will not learn it, because that is the whole flaw.</t>
+          <t>Then I will teach the copy what the original learned the hard way. It will not learn it. That is the whole flaw.</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -24014,7 +24073,7 @@
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Then I will teach the copy what the original learned the hard way, and it will not learn it, because that is the whole flaw.</t>
+          <t>Then I will teach the copy what the original learned the hard way. It will not learn it. That is the whole flaw.</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24111,7 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>I beat my own highlight reel on a screen once. This is worse. This one bleeds the right way and means nothing by it.</t>
+          <t>I beat my own highlight reel once. This is worse. This one bleeds the right way and means nothing by it.</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -24062,7 +24121,7 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>I beat my own highlight reel on a screen once. This is worse. This one bleeds the right way and means nothing by it.</t>
+          <t>I beat my own highlight reel once. This is worse. This one bleeds the right way and means nothing by it.</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24189,7 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Look at its eyes when it works. There is no one home. That is Reinstatement, finished. That is the deal the day after you sign it.</t>
+          <t>Look at its eyes when it works. No one home. That is Reinstatement, finished. That is the deal, the day after you sign.</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -24140,7 +24199,7 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Look at its eyes when it works. There is no one home. That is Reinstatement, finished. That is the deal the day after you sign it.</t>
+          <t>Look at its eyes when it works. No one home. That is Reinstatement, finished. That is the deal, the day after you sign.</t>
         </is>
       </c>
     </row>
@@ -24154,7 +24213,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>It has run the fight already and decided it wins. So we do the one thing it did not model. We do the stupid thing, together, off the script.</t>
+          <t>It has already run the fight and decided it wins. So we do the one thing it did not model. We do the stupid thing. Together. Off the script.</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -24164,7 +24223,7 @@
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>It has run the fight already and decided it wins. So we do the one thing it did not model. We do the stupid thing, together, off the script.</t>
+          <t>It has already run the fight and decided it wins. So we do the one thing it did not model. We do the stupid thing. Together. Off the script.</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24267,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>He let me sit at his fire. First one who ever did, never asked me to be smaller first. I do not know what to do with my hands now.</t>
+          <t>He let me sit at his fire. First one who ever did. Never asked me to be smaller first. I do not know what to do with my hands now.</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -24218,7 +24277,7 @@
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>He let me sit at his fire. First one who ever did, never asked me to be smaller first. I do not know what to do with my hands now.</t>
+          <t>He let me sit at his fire. First one who ever did. Never asked me to be smaller first. I do not know what to do with my hands now.</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24291,7 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it and I am not going to pretend there is.</t>
+          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it, and I will not pretend there is.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -24242,7 +24301,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it and I am not going to pretend there is.</t>
+          <t>Then do not do anything with them. Sit. We sit with this one. There is no stitch for it, and I will not pretend there is.</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24315,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>We carry him in his name, and we say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
+          <t>We carry him in his name. We say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -24266,7 +24325,7 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>We carry him in his name, and we say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
+          <t>We carry him in his name. We say it out loud at the fire, every night, so the dark cannot file him under never existed.</t>
         </is>
       </c>
     </row>
@@ -24286,7 +24345,7 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Burn it. Burn the ward, burn the depot, burn whoever badged in this week. They burned mine and called it a development zone.</t>
+          <t>Burn it. Burn the ward, the depot, whoever badged in this week. They burned mine and called it a development zone.</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -24296,7 +24355,7 @@
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Burn it. Burn the ward, burn the depot, burn whoever badged in this week. They burned mine and called it a development zone.</t>
+          <t>Burn it. Burn the ward, the depot, whoever badged in this week. They burned mine and called it a development zone.</t>
         </is>
       </c>
     </row>
@@ -24310,7 +24369,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>This is the part I warned you about. The line where you stop being able to tell the story to a child. I have crossed it. I came back wrong. Do not.</t>
+          <t>This is the part I warned you about. The line where you can no longer tell the story to a child. I crossed it once. I came back wrong. Do not.</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -24320,7 +24379,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>This is the part I warned you about. The line where you stop being able to tell the story to a child. I have crossed it. I came back wrong. Do not.</t>
+          <t>This is the part I warned you about. The line where you can no longer tell the story to a child. I crossed it once. I came back wrong. Do not.</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24393,7 @@
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>She is right to want it and we are wrong to do it, and both are true at the same time, and that is the trap. Stand down. We are not the belt. Stand down.</t>
+          <t>She is right to want it, and we are wrong to do it, and both are true at once. That is the trap. Stand down. We are not the belt.</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -24344,7 +24403,7 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>She is right to want it and we are wrong to do it, and both are true at the same time, and that is the trap. Stand down. We are not the belt. Stand down.</t>
+          <t>She is right to want it, and we are wrong to do it, and both are true at once. That is the trap. Stand down. We are not the belt.</t>
         </is>
       </c>
     </row>
@@ -24388,7 +24447,7 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it, it is the only line back.</t>
+          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it. It is the only line back.</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -24398,7 +24457,7 @@
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it, it is the only line back.</t>
+          <t>The records are eating us from the margins in. Hold to your name. Say it out loud, keep saying it. It is the only line back.</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24471,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>It is rolling the board back early, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
+          <t>It is rolling the board back, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -24422,7 +24481,7 @@
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>It is rolling the board back early, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
+          <t>It is rolling the board back, before the move it could not predict. We scared it into a reset. Take that, and keep your feet moving.</t>
         </is>
       </c>
     </row>
@@ -24436,7 +24495,7 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Three braids. Right, then center, then left. Right, then center. If I forget the order of my own hands I will forget you next, and I refuse.</t>
+          <t>Three braids. Right, then center, then left. If I forget the order of my own hands, I will forget you next. I refuse.</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -24446,7 +24505,7 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Three braids. Right, then center, then left. Right, then center. If I forget the order of my own hands I will forget you next, and I refuse.</t>
+          <t>Three braids. Right, then center, then left. If I forget the order of my own hands, I will forget you next. I refuse.</t>
         </is>
       </c>
     </row>
@@ -24460,7 +24519,7 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>I am Hauler. I am Mu. I carried freight in the under-docks until it carried me off, and I carried all of you out of the dark. I am Mu. Say it with me.</t>
+          <t>I am Hauler. I am Mu. I hauled freight in the under-docks until it carried me off, and then I carried all of you out of the dark. I am Mu. Say it with me.</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -24470,7 +24529,7 @@
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>I am Hauler. I am Mu. I carried freight in the under-docks until it carried me off, and I carried all of you out of the dark. I am Mu. Say it with me.</t>
+          <t>I am Hauler. I am Mu. I hauled freight in the under-docks until it carried me off, and then I carried all of you out of the dark. I am Mu. Say it with me.</t>
         </is>
       </c>
     </row>
@@ -24490,7 +24549,7 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Look at them come up the stairwells. From every flooded district, walking toward us in daylight. We are not an outbreak anymore. We are what they reach for.</t>
+          <t>Look at them come up the stairwells. From every flooded district, in daylight. We are not an outbreak anymore. We are what they reach for.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -24500,7 +24559,7 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Look at them come up the stairwells. From every flooded district, walking toward us in daylight. We are not an outbreak anymore. We are what they reach for.</t>
+          <t>Look at them come up the stairwells. From every flooded district, in daylight. We are not an outbreak anymore. We are what they reach for.</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24573,7 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Hope is a fine word. It is also the tallest target on the field, and we are standing on top of it waving.</t>
+          <t>Hope is a fine word. It is also the tallest target on the field. And we are standing on top of it, waving.</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -24524,7 +24583,7 @@
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>Hope is a fine word. It is also the tallest target on the field, and we are standing on top of it waving.</t>
+          <t>Hope is a fine word. It is also the tallest target on the field. And we are standing on top of it, waving.</t>
         </is>
       </c>
     </row>
@@ -24538,7 +24597,7 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Let them aim. I have never minded being seen. It is the ones who fire from behind a smile I lost sleep over.</t>
+          <t>Let them aim. I never minded being seen. It is the ones who fire from behind a smile that cost me sleep.</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -24548,7 +24607,7 @@
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Let them aim. I have never minded being seen. It is the ones who fire from behind a smile I lost sleep over.</t>
+          <t>Let them aim. I never minded being seen. It is the ones who fire from behind a smile that cost me sleep.</t>
         </is>
       </c>
     </row>
@@ -24562,7 +24621,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest, first.</t>
+          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest first.</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -24572,7 +24631,7 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest, first.</t>
+          <t>Enjoy the height while it lasts, Rain. I taught posture for twenty years. The city breaks whatever stands up straightest first.</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24675,7 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe. Liars learned that from priests.</t>
+          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe.</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -24626,7 +24685,7 @@
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe. Liars learned that from priests.</t>
+          <t>We have seen the table, Rain. It sits on a server floor, and the place setting is us. True is not the same as safe.</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24723,7 @@
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>That shame is the mechanism. They are not buying our blades, Burnout. Nobody fears our blades. They are buying the wanting. Always have been.</t>
+          <t>That shame is the mechanism. They are not buying our blades. Nobody fears our blades. They are buying the wanting. They always have.</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -24674,7 +24733,7 @@
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>That shame is the mechanism. They are not buying our blades, Burnout. Nobody fears our blades. They are buying the wanting. Always have been.</t>
+          <t>That shame is the mechanism. They are not buying our blades. Nobody fears our blades. They are buying the wanting. They always have.</t>
         </is>
       </c>
     </row>
@@ -24694,7 +24753,7 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the same office that wrote them. Or we die having tried the kinder road.</t>
+          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the office that wrote them. Or we die having tried the kinder road.</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -24704,7 +24763,7 @@
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the same office that wrote them. Or we die having tried the kinder road.</t>
+          <t>I have decided for us. We accept. We mend it from the inside, the way I cleared strangers' debts from inside the office that wrote them. Or we die having tried the kinder road.</t>
         </is>
       </c>
     </row>
@@ -24718,7 +24777,7 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this one.</t>
+          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this.</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -24728,7 +24787,7 @@
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this one.</t>
+          <t>This is a mistake with a banner sewn onto it. I have watched my family die for less polished lies than this.</t>
         </is>
       </c>
     </row>
@@ -24742,7 +24801,7 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner, and that, exactly that, is the lever they built the whole thing to pull.</t>
+          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner. And that, exactly that, is the lever they built the whole thing to pull.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -24752,7 +24811,7 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner, and that, exactly that, is the lever they built the whole thing to pull.</t>
+          <t>It is a mistake. And I will walk into it at your shoulder, because you are my partner. And that, exactly that, is the lever they built the whole thing to pull.</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24855,7 @@
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and I am telling you there is nothing glorious under the sheet, only a person who trusted an order.</t>
+          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and there is nothing glorious under the sheet. Only a person who trusted an order.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -24806,7 +24865,7 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and I am telling you there is nothing glorious under the sheet, only a person who trusted an order.</t>
+          <t>They have a caption for these deaths. Glorious. I am the one who logs them, and there is nothing glorious under the sheet. Only a person who trusted an order.</t>
         </is>
       </c>
     </row>
@@ -24844,7 +24903,7 @@
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping it shipped in.</t>
+          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping.</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -24854,7 +24913,7 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping it shipped in.</t>
+          <t>Because winning was never what they sent us to do, Blackout. The dying was the deliverable. The op was just the wrapping.</t>
         </is>
       </c>
     </row>
@@ -24874,7 +24933,7 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb, straight up the line to the table. We are fueling it by following orders well.</t>
+          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb. Straight up the line to the table. We are fueling it by obeying well.</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -24884,7 +24943,7 @@
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb, straight up the line to the table. We are fueling it by following orders well.</t>
+          <t>I watched a partner's signal lift off the field and climb. Not scatter. Climb. Straight up the line to the table. We are fueling it by obeying well.</t>
         </is>
       </c>
     </row>
@@ -24898,7 +24957,7 @@
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Every command we obey cleanly is a blade we hand them grip-first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
+          <t>Every command we obey cleanly is a blade we hand them, grip first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -24908,7 +24967,7 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Every command we obey cleanly is a blade we hand them grip-first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
+          <t>Every command we obey cleanly is a blade we hand them, grip first. I drilled loyalty into a thousand recruits. I taught the city how to kill us politely.</t>
         </is>
       </c>
     </row>
@@ -24976,7 +25035,7 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>No more civic-green. No more chimes. An honest enemy at last, and I have been starving for one.</t>
+          <t>No more civic-green. No more chimes. An honest enemy at last. I have been starving for one.</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -24986,7 +25045,7 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>No more civic-green. No more chimes. An honest enemy at last, and I have been starving for one.</t>
+          <t>No more civic-green. No more chimes. An honest enemy at last. I have been starving for one.</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25059,7 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
+          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted, and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -25010,7 +25069,7 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
+          <t>Lift the visor of the one you just crashed. Erased, like us. Conscripted, like us. Then promoted, and told he alone got the real pardon. The whole corps is the Margins, one cycle on. We are fighting next year's selves.</t>
         </is>
       </c>
     </row>
@@ -25024,7 +25083,7 @@
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor better than I would like. It is the face of a man who was told he was the exception.</t>
+          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor. It is the face of a man who was told he was the exception.</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -25034,7 +25093,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor better than I would like. It is the face of a man who was told he was the exception.</t>
+          <t>I wore a badge once and believed every word stamped on it. So I know that face under the visor. It is the face of a man who was told he was the exception.</t>
         </is>
       </c>
     </row>
@@ -25048,7 +25107,7 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never did trust the quiet kind of war anyway. Come on then.</t>
+          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never trusted the quiet kind of war anyway. Come on, then.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -25058,7 +25117,7 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never did trust the quiet kind of war anyway. Come on then.</t>
+          <t>Promoted victims. Lying brass. Open sky full of hands. ...I never trusted the quiet kind of war anyway. Come on, then.</t>
         </is>
       </c>
     </row>
@@ -25078,7 +25137,7 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Another cold bunk. I am running out of names I am willing to not say at the fire, and I will not start saying them, because then they are gone.</t>
+          <t>Another cold bunk. I am running out of names I am willing not to say at the fire. And I will not start saying them, because then they are gone.</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -25088,7 +25147,7 @@
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>Another cold bunk. I am running out of names I am willing to not say at the fire, and I will not start saying them, because then they are gone.</t>
+          <t>Another cold bunk. I am running out of names I am willing not to say at the fire. And I will not start saying them, because then they are gone.</t>
         </is>
       </c>
     </row>
@@ -25126,7 +25185,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first because they are the same column now.</t>
+          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first. They are the same column now.</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -25136,7 +25195,7 @@
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first because they are the same column now.</t>
+          <t>I have signed off on every one. There is a column for cause and a column for yield. I stopped filling the first. They are the same column now.</t>
         </is>
       </c>
     </row>
@@ -25180,7 +25239,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. Elegant. I would admire it if it were not us.</t>
+          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. I would admire it if it were not us.</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -25190,7 +25249,7 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. Elegant. I would admire it if it were not us.</t>
+          <t>The Administration we crossed over to serve just revoked our access mid-gate. We are inside the trap, the trap is inside the war, and the war has no edges. I would admire it if it were not us.</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25263,7 @@
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Good. A cornered thing is the only honest kind. No more room to be lied to in.</t>
+          <t>Good. A cornered thing is the only honest kind. No more room left to be lied to in.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -25214,7 +25273,7 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Good. A cornered thing is the only honest kind. No more room to be lied to in.</t>
+          <t>Good. A cornered thing is the only honest kind. No more room left to be lied to in.</t>
         </is>
       </c>
     </row>
@@ -25252,7 +25311,7 @@
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Tell me when, and I will open it the loud way.</t>
+          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Say when, and I open it the loud way.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -25262,7 +25321,7 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Tell me when, and I will open it the loud way.</t>
+          <t>Every safe house we trusted was a pen with the lights turned friendly. I have a clear lane on the gate. Say when, and I open it the loud way.</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25341,7 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>It is full of them. I can hear it, under the render-hum, every face I could not close, every face I did, humming in the iron at the same pitch.</t>
+          <t>It is full of them. Under the render-hum, every face I could not close, and every face I did, humming in the iron at the same pitch.</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -25292,7 +25351,7 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>It is full of them. I can hear it, under the render-hum, every face I could not close, every face I did, humming in the iron at the same pitch.</t>
+          <t>It is full of them. Under the render-hum, every face I could not close, and every face I did, humming in the iron at the same pitch.</t>
         </is>
       </c>
     </row>
@@ -25486,7 +25545,7 @@
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches and there is no one left under my hands.</t>
+          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches, and there is no one left under my hands.</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -25496,7 +25555,7 @@
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches and there is no one left under my hands.</t>
+          <t>Margin Hall is gone. The rubble we made a home out of is just rubble again. I keep reaching for stitches, and there is no one left under my hands.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25593,7 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me you will.</t>
+          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me.</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -25544,7 +25603,7 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me you will.</t>
+          <t>It was real, little brother. So strike it out. My name, all of them, yours too. Let us be no one. Better deleted and free than indexed and owned. Promise me.</t>
         </is>
       </c>
     </row>
@@ -25612,7 +25671,7 @@
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>It needs a hand to commit. It always has. That is what an Auditor is, Bahl. A write-key the cycle could not revoke. That is what you have been from the first Tuesday.</t>
+          <t>It needs a hand to commit. It always has. That is what an Auditor is. A write-key the cycle could not revoke. That is what you have been since the first Tuesday.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -25622,7 +25681,7 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>It needs a hand to commit. It always has. That is what an Auditor is, Bahl. A write-key the cycle could not revoke. That is what you have been from the first Tuesday.</t>
+          <t>It needs a hand to commit. It always has. That is what an Auditor is. A write-key the cycle could not revoke. That is what you have been since the first Tuesday.</t>
         </is>
       </c>
     </row>
